--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1647">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -4769,6 +4769,717 @@
     <t>A partial payment leaves a correct outstanding balance that is visible on Receivables and on the receipt. Settling the remainder clears the balance, removes the patient from Receivables, and the final receipt lists both payments with their methods.</t>
   </si>
   <si>
+    <t>TC-WA-001</t>
+  </si>
+  <si>
+    <t>WhatsApp — Message log</t>
+  </si>
+  <si>
+    <t>The WhatsApp screen lists messages and is reachable by the right roles</t>
+  </si>
+  <si>
+    <t>Receptionist on default permissions. At least one message record exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sign in as the Receptionist.
+2. Confirm "WhatsApp" is present in the sidebar and open it.
+3. Confirm messages are listed with their direction, phone number, status and time.
+4. Sign in as the Clinic Admin and confirm the same screen is reachable.
+5. Sign in as the Manager and confirm the same.
+6. Sign in as the Doctor and confirm "WhatsApp" is ABSENT from the sidebar.
+7. As the Doctor, attempt /clinic/whatsapp directly.</t>
+  </si>
+  <si>
+    <t>Receptionist, Manager and Clinic Admin all reach the screen. The Doctor holds no WhatsApp permission by default, so the item is hidden and the direct URL redirects to /clinic.</t>
+  </si>
+  <si>
+    <t>TC-WA-002</t>
+  </si>
+  <si>
+    <t>WhatsApp — Outbound logging</t>
+  </si>
+  <si>
+    <t>An outbound message is recorded even when the provider is unconfigured</t>
+  </si>
+  <si>
+    <t>No AiSensy or Cloud API credentials are configured — the current state of this environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Perform an action that sends a patient message, for example booking an appointment for a patient with a phone number.
+2. Open "WhatsApp".
+3. Look for a record of the outbound message for that patient.
+4. Note its status and any error recorded against it.
+5. Confirm the booking itself completed successfully.</t>
+  </si>
+  <si>
+    <t>The message is RECORDED before any send is attempted, so it appears in the log with a status indicating it was not delivered. Critically, the failure to send must NOT break the booking — the appointment saves regardless. This is the designed behaviour when no provider is configured.</t>
+  </si>
+  <si>
+    <t>TC-WA-003</t>
+  </si>
+  <si>
+    <t>WhatsApp — Outbound triggers</t>
+  </si>
+  <si>
+    <t>Confirm which actions generate an outbound message</t>
+  </si>
+  <si>
+    <t>A patient with a valid phone number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book an appointment for the patient and check the WhatsApp log for a booking confirmation.
+2. Cancel that appointment and check for a cancellation message.
+3. Issue an invoice and use the send-on-WhatsApp control; check the log.
+4. Approve a clinical note that schedules a recall, then run the recall job, and check the log.
+5. For each, record the template or campaign name shown against the message.</t>
+  </si>
+  <si>
+    <t>Each action produces exactly one outbound record with an identifiable template. Record which triggers fire and which do not — a missing booking confirmation is a defect even though delivery itself cannot be tested here.</t>
+  </si>
+  <si>
+    <t>TC-WA-004</t>
+  </si>
+  <si>
+    <t>WhatsApp — Outbound</t>
+  </si>
+  <si>
+    <t>A patient with no phone number does not break the action</t>
+  </si>
+  <si>
+    <t>A patient record whose phone number has been cleared, if the form allows it, or a patient created before the phone became mandatory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Attempt to book an appointment for a patient with no usable phone number.
+2. Confirm the booking completes.
+3. Open the WhatsApp log and check whether a record was created.
+4. Confirm no error page or crash occurred.</t>
+  </si>
+  <si>
+    <t>The booking succeeds and the missing number does not raise an error to the user. Either no message record is created or one is created and marked as not sendable — record which, and confirm the clinical action was never blocked by the messaging layer.</t>
+  </si>
+  <si>
+    <t>TC-WA-005</t>
+  </si>
+  <si>
+    <t>WhatsApp — Inbound webhook auth</t>
+  </si>
+  <si>
+    <t>Inbound webhook rejects a request with no token</t>
+  </si>
+  <si>
+    <t>WHATSAPP_WEBHOOK_TOKEN is configured — it is set in this environment. An API client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST a minimal JSON body to /api/whatsapp/webhook with NO token in the query string and no token header.
+2. Record the status code and body.
+3. Repeat with a deliberately wrong token value.
+4. Record the status code and body.
+5. Confirm no message row was created for either attempt.</t>
+  </si>
+  <si>
+    <t>Both requests return HTTP 401 with the body error "Unauthorized." Nothing is stored. An unsigned payload that could drive patient self-service booking must never be accepted.</t>
+  </si>
+  <si>
+    <t>TC-WA-006</t>
+  </si>
+  <si>
+    <t>WhatsApp — Inbound webhook</t>
+  </si>
+  <si>
+    <t>A valid inbound message is stored and attributed to the patient</t>
+  </si>
+  <si>
+    <t>The configured webhook token. A patient whose stored phone number you know.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST a valid inbound-message payload to /api/whatsapp/webhook with the correct token in the query string, using that patient's phone number as the sender.
+2. Record the status code.
+3. Open "WhatsApp" in the clinic workspace.
+4. Confirm the inbound message appears with its text and the sender's number.
+5. Confirm it is attributed to the correct patient.
+6. Repeat with a phone number belonging to nobody.</t>
+  </si>
+  <si>
+    <t>A valid payload is accepted and stored. A message from a known number is linked to that patient; a message from an unknown number is still stored but left unattributed rather than discarded. Nothing is lost.</t>
+  </si>
+  <si>
+    <t>TC-WA-007</t>
+  </si>
+  <si>
+    <t>WhatsApp — Inbound idempotency</t>
+  </si>
+  <si>
+    <t>A redelivered inbound message is not stored or acted on twice</t>
+  </si>
+  <si>
+    <t>The configured webhook token. A valid inbound payload carrying a provider message ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST the inbound payload once with the correct token and confirm it is stored.
+2. POST the IDENTICAL payload again, with the same provider message ID.
+3. Record the status code of the second call.
+4. Open the WhatsApp log and count how many times the message appears.
+5. If the message text would trigger a booking or reschedule, confirm only ONE appointment action occurred.</t>
+  </si>
+  <si>
+    <t>The message appears exactly once and any self-service action it triggers happens exactly once. Provider redelivery is normal, so a duplicate must not double-book a patient or duplicate the log entry.</t>
+  </si>
+  <si>
+    <t>TC-WA-008</t>
+  </si>
+  <si>
+    <t>WhatsApp — Inbound</t>
+  </si>
+  <si>
+    <t>A malformed inbound payload does not crash the endpoint</t>
+  </si>
+  <si>
+    <t>The configured webhook token.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST invalid JSON to /api/whatsapp/webhook with the correct token.
+2. Record the status and body.
+3. POST valid JSON of an entirely unexpected shape.
+4. Record the status and body.
+5. POST an empty body.
+6. Confirm the application is still responsive afterwards and no error page was produced.</t>
+  </si>
+  <si>
+    <t>Malformed and unexpected payloads are handled without throwing. The endpoint answers rather than erroring, nothing nonsensical is stored, and the application remains healthy. Provider webhooks are untrusted input and must never be able to break the app.</t>
+  </si>
+  <si>
+    <t>TC-WA-009</t>
+  </si>
+  <si>
+    <t>WhatsApp — Meta Cloud verification</t>
+  </si>
+  <si>
+    <t>Meta webhook verification handshake</t>
+  </si>
+  <si>
+    <t>[BLOCKED: needs WHATSAPP_VERIFY_TOKEN] The Cloud API verify token must be configured; it is not set in this environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Call GET /api/whatsapp/cloud with hub.mode=subscribe, the correct hub.verify_token and a hub.challenge value.
+2. Confirm the response body is exactly the challenge string with status 200.
+3. Repeat with an incorrect verify token.
+4. Record the status and body.
+5. Repeat with no parameters at all.</t>
+  </si>
+  <si>
+    <t>With the correct token the raw challenge string is echoed back with HTTP 200, which is what Meta requires to complete subscription. A wrong or missing token returns HTTP 403 and no challenge. This cannot be exercised until the verify token is configured.</t>
+  </si>
+  <si>
+    <t>TC-WA-010</t>
+  </si>
+  <si>
+    <t>WhatsApp — Meta Cloud signature</t>
+  </si>
+  <si>
+    <t>Cloud webhook rejects an unsigned payload in production</t>
+  </si>
+  <si>
+    <t>[BLOCKED: needs WHATSAPP_APP_SECRET] The Cloud API app secret must be configured; it is not set in this environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST a valid Cloud API payload to /api/whatsapp/cloud with NO signature header.
+2. Record the status.
+3. POST the same payload with a deliberately incorrect signature header.
+4. Record the status.
+5. POST with a correctly computed signature and confirm acceptance.
+6. Confirm nothing was stored for the two rejected attempts.</t>
+  </si>
+  <si>
+    <t>An unsigned or wrongly signed payload is refused when the app secret is configured, and only a correctly signed payload is processed. Note the endpoint deliberately answers HTTP 200 on an accepted POST so Meta does not retry a payload already stored.</t>
+  </si>
+  <si>
+    <t>TC-WA-011</t>
+  </si>
+  <si>
+    <t>WhatsApp — Patient self-service</t>
+  </si>
+  <si>
+    <t>A patient reply can reschedule their appointment</t>
+  </si>
+  <si>
+    <t>The configured webhook token. A patient with a future appointment and a doctor with availability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the patient's existing appointment date and time.
+2. POST an inbound message from that patient's number asking to move the appointment to a specific future day.
+3. Open "Appointments" and inspect that appointment.
+4. Open "WhatsApp" and read the inbound message and any reply recorded.
+5. Repeat asking for a day the doctor is on leave.
+6. Confirm the appointment was not moved in that case.</t>
+  </si>
+  <si>
+    <t>A valid reschedule request moves the appointment and records a reply. A request for an unavailable day is refused by exactly the same availability rules as a staff booking, leaving the original appointment untouched. The patient is never silently ignored.</t>
+  </si>
+  <si>
+    <t>TC-WA-012</t>
+  </si>
+  <si>
+    <t>A patient cancellation respects the cancellation cut-off</t>
+  </si>
+  <si>
+    <t>The configured webhook token. A clinic with a cancellation cut-off configured. One appointment far in the future and one within the cut-off window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST an inbound cancellation request from the patient for the appointment that is FAR in the future.
+2. Confirm the appointment is cancelled.
+3. POST a cancellation request for the appointment INSIDE the cut-off window.
+4. Confirm the appointment is NOT cancelled automatically.
+5. Open WhatsApp and confirm the request is visible to the front desk.</t>
+  </si>
+  <si>
+    <t>A cancellation with enough notice is actioned. One inside the cut-off is not cancelled automatically — it is left for the front desk, because cancelling twenty minutes beforehand is a conversation rather than a rule. The request is still visible to staff either way.</t>
+  </si>
+  <si>
+    <t>TC-WA-013</t>
+  </si>
+  <si>
+    <t>A patient self-booking stays a request until staff confirm</t>
+  </si>
+  <si>
+    <t>The configured webhook token. A patient with no upcoming appointment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST an inbound booking request from that patient's number for an available slot.
+2. Open "Appointments" and locate the new appointment.
+3. Note its status and whether it is marked as patient-booked.
+4. Confirm it is visibly distinguishable from a staff booking.
+5. Confirm the appointment it created respects doctor availability.</t>
+  </si>
+  <si>
+    <t>A patient self-booking is created but marked as coming from WhatsApp and remains a request until staff confirm it. It cannot bypass the doctor's availability, leave or daily cap.</t>
+  </si>
+  <si>
+    <t>TC-WA-014</t>
+  </si>
+  <si>
+    <t>WhatsApp — Audit</t>
+  </si>
+  <si>
+    <t>Patient self-service actions are audited as the patient</t>
+  </si>
+  <si>
+    <t>The clinic has activity-log access granted. A self-service reschedule or cancellation has occurred.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Trigger a patient self-service action through the inbound webhook.
+2. Sign in as the Clinic Admin and open "Activity log".
+3. Locate the entry for that action.
+4. Confirm the actor is shown as the patient rather than as a staff member.
+5. Confirm the patient's NAME is not used as the actor name.</t>
+  </si>
+  <si>
+    <t>The action is recorded with the patient as the actor, not attributed to a staff account. The patient is identified by reference rather than by name in the actor field, which is the correct handling for patient data in an audit trail.</t>
+  </si>
+  <si>
+    <t>TC-WA-015</t>
+  </si>
+  <si>
+    <t>WhatsApp — Per-clinic sender</t>
+  </si>
+  <si>
+    <t>Each clinic can be given its own sending number</t>
+  </si>
+  <si>
+    <t>Super Admin access to a clinic's patient-facing settings. Two clinics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Clinic A in the admin panel and set its WhatsApp sender number and display name.
+2. Save.
+3. Attempt to set the SAME sender number on Clinic B.
+4. Record whether this is refused.
+5. Confirm Clinic A's outbound messages are recorded against its own sender.</t>
+  </si>
+  <si>
+    <t>A clinic can be given its own sending number, and the same number cannot be assigned to two clinics — the number is the routing key for inbound messages, so a duplicate would make inbound delivery ambiguous. A clinic with no number configured falls back to the platform sender or sends nothing.</t>
+  </si>
+  <si>
+    <t>TC-WA-016</t>
+  </si>
+  <si>
+    <t>WhatsApp — AI assistant feature</t>
+  </si>
+  <si>
+    <t>The WhatsApp AI assistant is off unless explicitly enabled</t>
+  </si>
+  <si>
+    <t>A test clinic. Super Admin access to the feature toggles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the clinic's features and confirm the WhatsApp AI assistant is OFF by default.
+2. Read the description shown to the super admin and note that it is marked as billable.
+3. Enable it and save.
+4. POST an inbound free-form message that the plain parser would not understand.
+5. Open the WhatsApp log and inspect whether an intent was recorded.
+6. Disable the feature again and repeat.</t>
+  </si>
+  <si>
+    <t>The assistant is opt-in and is clearly marked as costing money per message, unlike every other feature. With it off, an unparseable message is simply left for staff. With it on, the message is interpreted and an intent recorded. Confirm no AI call is made while the feature is off.</t>
+  </si>
+  <si>
+    <t>TC-WA-017</t>
+  </si>
+  <si>
+    <t>WhatsApp — Isolation</t>
+  </si>
+  <si>
+    <t>A clinic cannot see another clinic's messages</t>
+  </si>
+  <si>
+    <t>Two clinics, each with WhatsApp message records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sign in as a Clinic A user and open "WhatsApp".
+2. Record the messages listed.
+3. Sign in as a Clinic B user and open the same screen.
+4. Confirm the two lists are entirely distinct.
+5. Confirm no phone number or message body from the other clinic appears in either list.</t>
+  </si>
+  <si>
+    <t>Each clinic sees only its own inbound and outbound messages. Patient phone numbers and message bodies are confidential, so any cross-clinic visibility is a serious isolation defect.</t>
+  </si>
+  <si>
+    <t>TC-CRON-001</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Authentication</t>
+  </si>
+  <si>
+    <t>Every cron endpoint rejects a request with no secret</t>
+  </si>
+  <si>
+    <t>CRON_SECRET is configured — it is set in this environment. An API client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Call GET /api/cron/recalls with no Authorization header, no x-cron-token header and no token query parameter.
+2. Record the status code and body.
+3. Repeat for /api/cron/reminders, /api/cron/reconcile, /api/cron/expenses, /api/cron/company-expenses, /api/cron/log-retention, /api/cron/billing and /api/cron/scribe-recover.
+4. Confirm none of them performed any work by checking the data they would have changed.</t>
+  </si>
+  <si>
+    <t>Every endpoint returns HTTP 401 with the body error "Unauthorized." and does no work. These are publicly reachable URLs, so an unauthenticated caller must never be able to trigger a job.</t>
+  </si>
+  <si>
+    <t>TC-CRON-002</t>
+  </si>
+  <si>
+    <t>A wrong secret is rejected and the three accepted forms all work</t>
+  </si>
+  <si>
+    <t>The configured CRON_SECRET value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Call /api/cron/recalls with a deliberately wrong secret as a Bearer token. Record the status.
+2. Call it with the secret one character short. Record the status.
+3. Call it with the CORRECT secret as an Authorization Bearer header. Record the status.
+4. Call it with the correct secret in an x-cron-token header.
+5. Call it with the correct secret as a token query parameter.
+6. Confirm all three correct forms are accepted.</t>
+  </si>
+  <si>
+    <t>Any wrong value returns HTTP 401. The correct secret is accepted in all three forms: a Bearer header, an x-cron-token header, or a token query parameter. The comparison is constant-time, so response timing must not vary noticeably between a wrong secret and a correct one.</t>
+  </si>
+  <si>
+    <t>TC-CRON-003</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Recalls</t>
+  </si>
+  <si>
+    <t>The recalls job sends reminders for due recalls only</t>
+  </si>
+  <si>
+    <t>At least one recall due today or earlier, and one due well in the future.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the status of both recalls before running.
+2. Call GET /api/cron/recalls with the correct secret.
+3. Record the status code and the response body.
+4. Open "Recalls" and inspect both records.
+5. Open "WhatsApp" and look for an outbound message for the due patient.
+6. Confirm the future recall is untouched.</t>
+  </si>
+  <si>
+    <t>Only the due recall is actioned and its status advances. The future recall is left alone. An outbound message is recorded for the due patient even though it cannot be delivered without provider credentials.</t>
+  </si>
+  <si>
+    <t>TC-CRON-004</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Idempotency</t>
+  </si>
+  <si>
+    <t>Running a job twice does not duplicate its effect</t>
+  </si>
+  <si>
+    <t>The configured secret. A due recall and an appointment due a reminder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Call /api/cron/recalls with the correct secret and note what changed.
+2. Immediately call it a SECOND time.
+3. Compare the data after the second run with the first.
+4. Confirm no recall was advanced twice and no duplicate message was recorded.
+5. Repeat the same two-run test for /api/cron/reminders.
+6. Repeat for /api/cron/reconcile.</t>
+  </si>
+  <si>
+    <t>A second run is a no-op. Cron jobs can legitimately be invoked twice — by an overlapping schedule or a manual run — so a patient must never receive the same reminder twice and no ledger figure may be doubled.</t>
+  </si>
+  <si>
+    <t>TC-CRON-005</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Reminders</t>
+  </si>
+  <si>
+    <t>The reminder job messages tomorrow's appointments once</t>
+  </si>
+  <si>
+    <t>An appointment scheduled for tomorrow, and one for next week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Call GET /api/cron/reminders with the correct secret.
+2. Open "WhatsApp" and look for an outbound reminder for tomorrow's patient.
+3. Confirm no reminder was recorded for next week's appointment.
+4. Call the job again.
+5. Confirm tomorrow's patient did NOT receive a second reminder.
+6. Open the appointment and confirm it is marked as reminded.</t>
+  </si>
+  <si>
+    <t>Only appointments due tomorrow are reminded, exactly once. The appointment records that a reminder was sent, which is what stops a second run repeating it.</t>
+  </si>
+  <si>
+    <t>TC-CRON-006</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Reconciliation</t>
+  </si>
+  <si>
+    <t>The nightly reconciliation repairs a drifted sales ledger</t>
+  </si>
+  <si>
+    <t>A completed appointment whose derived sale record has been deliberately removed or altered directly in the database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete an appointment and confirm the sale appears in the Sales report.
+2. Directly in the database, delete or alter that derived sale row to simulate a failed write.
+3. Confirm the Sales report now disagrees with the appointment.
+4. Call GET /api/cron/reconcile with the correct secret.
+5. Re-check the Sales report and the doctor's revenue share.
+6. Run the job again and confirm nothing changes a second time.</t>
+  </si>
+  <si>
+    <t>The reconciliation re-derives the missing or wrong figures through the normal write path and the reports agree with the appointments again. This job is load-bearing: the payment path deliberately records money first and derives the ledger afterwards, on the basis that drift is repaired nightly. Skipping it leaves a failed ledger write wrong forever.</t>
+  </si>
+  <si>
+    <t>TC-CRON-007</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Recurring expenses</t>
+  </si>
+  <si>
+    <t>Recurring expenses are cloned when due</t>
+  </si>
+  <si>
+    <t>A clinic expense marked recurring with a next-run date of today or earlier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open "Expenses" and note the recurring template and its next-run date.
+2. Call GET /api/cron/expenses with the correct secret.
+3. Return to Expenses and confirm a new expense was created for this period.
+4. Confirm the template's next-run date has advanced.
+5. Call the job again immediately.
+6. Confirm a second copy was NOT created.
+7. Repeat the whole test against /api/cron/company-expenses for the company-side ledger.</t>
+  </si>
+  <si>
+    <t>A due recurring expense is cloned once and its next-run date advances, so a second run creates nothing. A duplicated expense would corrupt the profit and loss, so this idempotency matters.</t>
+  </si>
+  <si>
+    <t>TC-CRON-008</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Scribe recovery</t>
+  </si>
+  <si>
+    <t>The scribe recovery sweep fails stalled runs without re-running them</t>
+  </si>
+  <si>
+    <t>A scribe run that has been in the processing state for more than 15 minutes. The configured secret.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create or identify a run stuck in processing for over 15 minutes.
+2. Call GET /api/cron/scribe-recover with the correct secret.
+3. Record the response.
+4. Open "Voice scribe" as the owning clinician.
+5. Confirm the run now shows as failed with a message explaining the transcription stopped unexpectedly.
+6. Confirm the recording is still present and "Try again" is offered.
+7. Confirm the job did NOT automatically retry the transcription itself.</t>
+  </si>
+  <si>
+    <t>The stalled run is moved to failed with its recording kept, and a human must press "Try again". The job deliberately does not re-run the provider — spending money on a paid API unasked, in a loop, would be a worse failure than a note waiting for a click.</t>
+  </si>
+  <si>
+    <t>TC-CRON-009</t>
+  </si>
+  <si>
+    <t>A run that never started is still caught by the sweep</t>
+  </si>
+  <si>
+    <t>A scribe run created but whose background job never began, so it has no start time. May require simulating the condition directly in the database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create a visit in the processing state with no transcription start time recorded, dated more than 15 minutes ago.
+2. Call /api/cron/scribe-recover with the correct secret.
+3. Confirm the run is moved to failed.
+4. Confirm it was not skipped.</t>
+  </si>
+  <si>
+    <t>A run whose background work never fired is still caught. This is the exact case the sweep exists for, and a naive comparison against the start time alone would miss it forever — confirm it is not skipped.</t>
+  </si>
+  <si>
+    <t>TC-CRON-010</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Log retention</t>
+  </si>
+  <si>
+    <t>Log retention deletes nothing while the window is zero</t>
+  </si>
+  <si>
+    <t>Activity-log entries exist. The company retention setting is at its default of zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Confirm the company activity-log retention is set to zero, meaning keep everything.
+2. Note the oldest activity-log entry.
+3. Call GET /api/cron/log-retention with the correct secret.
+4. Confirm the oldest entry still exists.
+5. Set the retention window to a value such as 90 days.
+6. Run the job again.
+7. Confirm entries older than the window are removed and newer ones are not.
+8. Restore the setting to zero.</t>
+  </si>
+  <si>
+    <t>With the window at zero the job deliberately deletes nothing — how long an access log over patient data survives is a regulatory decision, not an engineering default. With a window set, only entries older than it are pruned. This is the only hard delete in the audit path, so test it carefully.</t>
+  </si>
+  <si>
+    <t>TC-CRON-011</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Billing sweep</t>
+  </si>
+  <si>
+    <t>The billing sweep moves overdue clinics and surfaces upcoming dues</t>
+  </si>
+  <si>
+    <t>Super Admin access. A clinic whose paid-through date has passed beyond its grace period, and one approaching its due date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the status of both clinics in the admin panel.
+2. Call GET /api/cron/billing with the correct secret.
+3. Re-check both clinics' statuses.
+4. Open the dues dashboard and confirm the overdue clinic is listed.
+5. Confirm the upcoming clinic appears under payments coming up rather than as overdue.
+6. Sign in as a user of the overdue clinic and confirm what they see.
+7. Run the job again and confirm nothing changes.</t>
+  </si>
+  <si>
+    <t>An overdue clinic is moved to the past-due state and appears on the dues dashboard; a clinic merely approaching its date is flagged as upcoming, not overdue. The clinic's own staff see the payment notice only if that notice is enabled for them. A second run changes nothing.</t>
+  </si>
+  <si>
+    <t>TC-CRON-012</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Isolation</t>
+  </si>
+  <si>
+    <t>Jobs process every clinic and keep their data separate</t>
+  </si>
+  <si>
+    <t>Two clinics each with due recalls and recurring expenses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create a due recall and a due recurring expense in Clinic A.
+2. Create the same in Clinic B.
+3. Run the recalls job and the expenses job with the correct secret.
+4. Sign in to each clinic and confirm its own recall advanced and its own expense was created.
+5. Confirm Clinic A received nothing belonging to Clinic B.
+6. Confirm no expense was written to the wrong clinic.</t>
+  </si>
+  <si>
+    <t>Cron jobs run across every clinic, which is correct, but each clinic's records stay separate. An expense or a recall landing in the wrong clinic is a serious isolation defect.</t>
+  </si>
+  <si>
+    <t>TC-CRON-013</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Failure handling</t>
+  </si>
+  <si>
+    <t>A failing job reports an error rather than appearing to succeed</t>
+  </si>
+  <si>
+    <t>Ability to induce a failure, for example by making the database briefly unreachable during a run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Induce a condition that will make a job fail.
+2. Call one of the cron endpoints with the correct secret.
+3. Record the status code and the response body.
+4. Inspect the server output for a reported error.
+5. Confirm the job did not leave data half-changed.</t>
+  </si>
+  <si>
+    <t>A failed job returns HTTP 500 with a plain error body and the failure is reported in the server logs. A cron failure has no user-visible surface at all, so that report is the only alarm — a job that fails silently while returning success is the worst possible outcome and must be raised.</t>
+  </si>
+  <si>
+    <t>TC-CRON-014</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Installation</t>
+  </si>
+  <si>
+    <t>Confirm whether the jobs are actually scheduled on the server</t>
+  </si>
+  <si>
+    <t>Access to the server where the application is deployed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On the server, check whether the cron entries for this application are installed.
+2. If an installer script is provided, run its check mode and record the output.
+3. Confirm the cron user exists and can read the file holding the secret.
+4. Compare the installed job list against the eight cron endpoints.
+5. Confirm each job has run recently by looking for its completion entries in the logs.</t>
+  </si>
+  <si>
+    <t>Every job the clinic depends on is installed and running. CRITICAL: a job that is never invoked raises no error at all, so an uninstalled crontab looks exactly like a healthy one from inside the application. Recalls, reminders and the nightly reconciliation all fail silently if missing. In this environment the jobs are NOT installed — the endpoints must be called manually to test them.</t>
+  </si>
+  <si>
+    <t>TC-CRON-015</t>
+  </si>
+  <si>
+    <t>Scheduled jobs — Security</t>
+  </si>
+  <si>
+    <t>Cron endpoints are not reachable with an ordinary user session</t>
+  </si>
+  <si>
+    <t>A signed-in clinic user session cookie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Using an ordinary clinic user's session cookie but NO cron secret, call GET /api/cron/reconcile.
+2. Record the status and body.
+3. Repeat with a Clinic Admin session cookie.
+4. Repeat with a Super Admin session cookie.
+5. Confirm no job ran in any case.</t>
+  </si>
+  <si>
+    <t>A user session is not a substitute for the cron secret — all three are refused with HTTP 401. Being signed in, even as a super admin, must not allow a user to trigger a billing sweep or a reconciliation from the browser.</t>
+  </si>
+  <si>
     <t>Grouping</t>
   </si>
   <si>
@@ -4814,9 +5525,15 @@
     <t>Patients</t>
   </si>
   <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
+    <t>Scheduled jobs</t>
+  </si>
+  <si>
     <t>End-to-end</t>
   </si>
   <si>
@@ -5273,28 +5990,28 @@
     <t>Editing a clinic admin's permission grid has no effect — they hold everything by short-circuit. The clinic can never be left with no active admin.</t>
   </si>
   <si>
-    <t>WhatsApp</t>
-  </si>
-  <si>
     <t>Outbound confirmations, reminders, recalls, inbound self-service</t>
   </si>
   <si>
-    <t>Implemented — provider not configured</t>
-  </si>
-  <si>
-    <t>NOT TESTABLE END TO END without provider credentials. Messages are recorded before sending, so the queue can be inspected, but nothing is delivered. Confirm the environment before writing delivery cases.</t>
-  </si>
-  <si>
-    <t>Scheduled jobs</t>
+    <t>Implemented — inbound testable, outbound not</t>
+  </si>
+  <si>
+    <t>TC-WA-001..017</t>
+  </si>
+  <si>
+    <t>WHATSAPP_WEBHOOK_TOKEN IS set, so the inbound webhook, patient self-service (reschedule, cancel, self-booking), idempotency and attribution are all testable now. Outbound DELIVERY is not — no AiSensy or Cloud API credentials. Messages are still recorded before sending, so the log and the triggers can be verified. The Meta verification and signature cases need WHATSAPP_VERIFY_TOKEN and WHATSAPP_APP_SECRET and are marked blocked.</t>
   </si>
   <si>
     <t>Recalls, reminders, reconciliation, scribe recovery, retention</t>
   </si>
   <si>
-    <t>Implemented — not installed</t>
-  </si>
-  <si>
-    <t>The cron jobs are NOT installed in this environment. A job that is never invoked raises no error, so these fail silently. To test the scribe stall sweep, call its endpoint manually with the configured secret.</t>
+    <t>Implemented — endpoints testable, not scheduled</t>
+  </si>
+  <si>
+    <t>TC-CRON-001..015</t>
+  </si>
+  <si>
+    <t>CRON_SECRET IS set, so every job can be invoked manually and fully tested: auth, idempotency, and each job effect. What is NOT done is INSTALLING the schedule on the server (TC-CRON-014). A job that is never invoked raises no error, so an uninstalled crontab is indistinguishable from a healthy one from inside the app — recalls, reminders and the nightly reconciliation all fail silently. Reconcile matters most: the payment path records money first and derives the ledger after, on the basis that drift is repaired nightly.</t>
   </si>
   <si>
     <t>Soft delete and restore</t>
@@ -5879,7 +6596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -11716,8 +12433,840 @@
         <v>15</v>
       </c>
     </row>
+    <row r="225" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="6" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H231" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="9" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E233" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F233" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H233" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="9" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E234" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H234" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="6" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H235" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="6" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H237" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H239" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H241" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H243" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H245" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H246" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H247" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H248" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H249" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H250" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H251" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H253" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="6" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G255" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H255" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H256" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H224"/>
+  <autoFilter ref="A1:H256"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -11725,7 +13274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -11735,62 +13284,62 @@
   <sheetData>
     <row r="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>1245</v>
+        <v>1433</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1246</v>
+        <v>1434</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>1247</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>1248</v>
+        <v>1436</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1249</v>
+        <v>1437</v>
       </c>
       <c r="C2" s="12">
-        <v>223</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1248</v>
+        <v>1436</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1250</v>
+        <v>1438</v>
       </c>
       <c r="C3" s="12">
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>1248</v>
+        <v>1436</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1251</v>
+        <v>1439</v>
       </c>
       <c r="C4" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>183</v>
       </c>
       <c r="C6" s="13">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>176</v>
@@ -11801,51 +13350,51 @@
     </row>
     <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="C8" s="13">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="13">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="C10" s="13">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>222</v>
+        <v>9</v>
       </c>
       <c r="C11" s="13">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>1252</v>
+        <v>1440</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>189</v>
@@ -11856,10 +13405,10 @@
     </row>
     <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="C14" s="13">
         <v>44</v>
@@ -11867,10 +13416,10 @@
     </row>
     <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="C15" s="13">
         <v>31</v>
@@ -11878,10 +13427,10 @@
     </row>
     <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1256</v>
+        <v>1444</v>
       </c>
       <c r="C16" s="13">
         <v>24</v>
@@ -11889,10 +13438,10 @@
     </row>
     <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1257</v>
+        <v>1445</v>
       </c>
       <c r="C17" s="13">
         <v>24</v>
@@ -11900,10 +13449,10 @@
     </row>
     <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1258</v>
+        <v>1446</v>
       </c>
       <c r="C18" s="13">
         <v>22</v>
@@ -11911,10 +13460,10 @@
     </row>
     <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1259</v>
+        <v>1447</v>
       </c>
       <c r="C19" s="13">
         <v>20</v>
@@ -11922,131 +13471,131 @@
     </row>
     <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1260</v>
+        <v>1448</v>
       </c>
       <c r="C20" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1261</v>
+        <v>1449</v>
       </c>
       <c r="C21" s="13">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1262</v>
+        <v>1450</v>
       </c>
       <c r="C22" s="13">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1263</v>
+        <v>1451</v>
       </c>
       <c r="C23" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1264</v>
+        <v>1452</v>
       </c>
       <c r="C24" s="13">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1265</v>
+        <v>1453</v>
       </c>
       <c r="C25" s="13">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1266</v>
+        <v>1454</v>
       </c>
       <c r="C26" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>1253</v>
+        <v>1441</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1267</v>
+        <v>1455</v>
       </c>
       <c r="C27" s="13">
-        <v>2</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C28" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>1268</v>
+        <v>1441</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>10</v>
+        <v>1457</v>
       </c>
       <c r="C29" s="13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>313</v>
+        <v>10</v>
       </c>
       <c r="C31" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>611</v>
+        <v>95</v>
       </c>
       <c r="C32" s="13">
         <v>5</v>
@@ -12054,32 +13603,32 @@
     </row>
     <row r="33" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>58</v>
+        <v>313</v>
       </c>
       <c r="C33" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>138</v>
+        <v>611</v>
       </c>
       <c r="C34" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>431</v>
+        <v>58</v>
       </c>
       <c r="C35" s="13">
         <v>4</v>
@@ -12087,10 +13636,10 @@
     </row>
     <row r="36" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>542</v>
+        <v>138</v>
       </c>
       <c r="C36" s="13">
         <v>4</v>
@@ -12098,10 +13647,10 @@
     </row>
     <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>590</v>
+        <v>431</v>
       </c>
       <c r="C37" s="13">
         <v>4</v>
@@ -12109,10 +13658,10 @@
     </row>
     <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>636</v>
+        <v>542</v>
       </c>
       <c r="C38" s="13">
         <v>4</v>
@@ -12120,10 +13669,10 @@
     </row>
     <row r="39" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>730</v>
+        <v>590</v>
       </c>
       <c r="C39" s="13">
         <v>4</v>
@@ -12131,10 +13680,10 @@
     </row>
     <row r="40" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>1018</v>
+        <v>636</v>
       </c>
       <c r="C40" s="13">
         <v>4</v>
@@ -12142,32 +13691,32 @@
     </row>
     <row r="41" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>42</v>
+        <v>730</v>
       </c>
       <c r="C41" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>80</v>
+        <v>1018</v>
       </c>
       <c r="C42" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="C43" s="13">
         <v>3</v>
@@ -12175,10 +13724,10 @@
     </row>
     <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="C44" s="13">
         <v>3</v>
@@ -12186,10 +13735,10 @@
     </row>
     <row r="45" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="C45" s="13">
         <v>3</v>
@@ -12197,10 +13746,10 @@
     </row>
     <row r="46" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>421</v>
+        <v>195</v>
       </c>
       <c r="C46" s="13">
         <v>3</v>
@@ -12208,10 +13757,10 @@
     </row>
     <row r="47" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>462</v>
+        <v>240</v>
       </c>
       <c r="C47" s="13">
         <v>3</v>
@@ -12219,10 +13768,10 @@
     </row>
     <row r="48" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="C48" s="13">
         <v>3</v>
@@ -12230,10 +13779,10 @@
     </row>
     <row r="49" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>574</v>
+        <v>462</v>
       </c>
       <c r="C49" s="13">
         <v>3</v>
@@ -12241,10 +13790,10 @@
     </row>
     <row r="50" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>662</v>
+        <v>502</v>
       </c>
       <c r="C50" s="13">
         <v>3</v>
@@ -12252,10 +13801,10 @@
     </row>
     <row r="51" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>689</v>
+        <v>574</v>
       </c>
       <c r="C51" s="13">
         <v>3</v>
@@ -12263,10 +13812,10 @@
     </row>
     <row r="52" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>715</v>
+        <v>662</v>
       </c>
       <c r="C52" s="13">
         <v>3</v>
@@ -12274,10 +13823,10 @@
     </row>
     <row r="53" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>876</v>
+        <v>689</v>
       </c>
       <c r="C53" s="13">
         <v>3</v>
@@ -12285,43 +13834,43 @@
     </row>
     <row r="54" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>127</v>
+        <v>715</v>
       </c>
       <c r="C54" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>159</v>
+        <v>876</v>
       </c>
       <c r="C55" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>211</v>
+        <v>1306</v>
       </c>
       <c r="C56" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>223</v>
+        <v>127</v>
       </c>
       <c r="C57" s="13">
         <v>2</v>
@@ -12329,10 +13878,10 @@
     </row>
     <row r="58" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>292</v>
+        <v>159</v>
       </c>
       <c r="C58" s="13">
         <v>2</v>
@@ -12340,10 +13889,10 @@
     </row>
     <row r="59" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>303</v>
+        <v>211</v>
       </c>
       <c r="C59" s="13">
         <v>2</v>
@@ -12351,10 +13900,10 @@
     </row>
     <row r="60" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>348</v>
+        <v>223</v>
       </c>
       <c r="C60" s="13">
         <v>2</v>
@@ -12362,10 +13911,10 @@
     </row>
     <row r="61" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="C61" s="13">
         <v>2</v>
@@ -12373,10 +13922,10 @@
     </row>
     <row r="62" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="C62" s="13">
         <v>2</v>
@@ -12384,10 +13933,10 @@
     </row>
     <row r="63" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>563</v>
+        <v>348</v>
       </c>
       <c r="C63" s="13">
         <v>2</v>
@@ -12395,10 +13944,10 @@
     </row>
     <row r="64" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>678</v>
+        <v>359</v>
       </c>
       <c r="C64" s="13">
         <v>2</v>
@@ -12406,10 +13955,10 @@
     </row>
     <row r="65" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>705</v>
+        <v>410</v>
       </c>
       <c r="C65" s="13">
         <v>2</v>
@@ -12417,10 +13966,10 @@
     </row>
     <row r="66" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>741</v>
+        <v>563</v>
       </c>
       <c r="C66" s="13">
         <v>2</v>
@@ -12428,10 +13977,10 @@
     </row>
     <row r="67" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>774</v>
+        <v>678</v>
       </c>
       <c r="C67" s="13">
         <v>2</v>
@@ -12439,10 +13988,10 @@
     </row>
     <row r="68" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>820</v>
+        <v>705</v>
       </c>
       <c r="C68" s="13">
         <v>2</v>
@@ -12450,10 +13999,10 @@
     </row>
     <row r="69" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>826</v>
+        <v>741</v>
       </c>
       <c r="C69" s="13">
         <v>2</v>
@@ -12461,10 +14010,10 @@
     </row>
     <row r="70" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>837</v>
+        <v>774</v>
       </c>
       <c r="C70" s="13">
         <v>2</v>
@@ -12472,10 +14021,10 @@
     </row>
     <row r="71" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>848</v>
+        <v>820</v>
       </c>
       <c r="C71" s="13">
         <v>2</v>
@@ -12483,10 +14032,10 @@
     </row>
     <row r="72" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>865</v>
+        <v>826</v>
       </c>
       <c r="C72" s="13">
         <v>2</v>
@@ -12494,10 +14043,10 @@
     </row>
     <row r="73" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>915</v>
+        <v>837</v>
       </c>
       <c r="C73" s="13">
         <v>2</v>
@@ -12505,10 +14054,10 @@
     </row>
     <row r="74" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="C74" s="13">
         <v>2</v>
@@ -12516,10 +14065,10 @@
     </row>
     <row r="75" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>943</v>
+        <v>865</v>
       </c>
       <c r="C75" s="13">
         <v>2</v>
@@ -12527,10 +14076,10 @@
     </row>
     <row r="76" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>966</v>
+        <v>915</v>
       </c>
       <c r="C76" s="13">
         <v>2</v>
@@ -12538,10 +14087,10 @@
     </row>
     <row r="77" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>989</v>
+        <v>926</v>
       </c>
       <c r="C77" s="13">
         <v>2</v>
@@ -12549,10 +14098,10 @@
     </row>
     <row r="78" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>1039</v>
+        <v>943</v>
       </c>
       <c r="C78" s="13">
         <v>2</v>
@@ -12560,10 +14109,10 @@
     </row>
     <row r="79" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>1199</v>
+        <v>966</v>
       </c>
       <c r="C79" s="13">
         <v>2</v>
@@ -12571,65 +14120,65 @@
     </row>
     <row r="80" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>121</v>
+        <v>989</v>
       </c>
       <c r="C80" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>170</v>
+        <v>1039</v>
       </c>
       <c r="C81" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>234</v>
+        <v>1199</v>
       </c>
       <c r="C82" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>256</v>
+        <v>1346</v>
       </c>
       <c r="C83" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>262</v>
+        <v>1387</v>
       </c>
       <c r="C84" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>268</v>
+        <v>121</v>
       </c>
       <c r="C85" s="13">
         <v>1</v>
@@ -12637,10 +14186,10 @@
     </row>
     <row r="86" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
       <c r="C86" s="13">
         <v>1</v>
@@ -12648,10 +14197,10 @@
     </row>
     <row r="87" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="C87" s="13">
         <v>1</v>
@@ -12659,10 +14208,10 @@
     </row>
     <row r="88" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="C88" s="13">
         <v>1</v>
@@ -12670,10 +14219,10 @@
     </row>
     <row r="89" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>336</v>
+        <v>262</v>
       </c>
       <c r="C89" s="13">
         <v>1</v>
@@ -12681,10 +14230,10 @@
     </row>
     <row r="90" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>342</v>
+        <v>268</v>
       </c>
       <c r="C90" s="13">
         <v>1</v>
@@ -12692,10 +14241,10 @@
     </row>
     <row r="91" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>369</v>
+        <v>274</v>
       </c>
       <c r="C91" s="13">
         <v>1</v>
@@ -12703,10 +14252,10 @@
     </row>
     <row r="92" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>375</v>
+        <v>280</v>
       </c>
       <c r="C92" s="13">
         <v>1</v>
@@ -12714,10 +14263,10 @@
     </row>
     <row r="93" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>381</v>
+        <v>286</v>
       </c>
       <c r="C93" s="13">
         <v>1</v>
@@ -12725,10 +14274,10 @@
     </row>
     <row r="94" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="C94" s="13">
         <v>1</v>
@@ -12736,10 +14285,10 @@
     </row>
     <row r="95" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
       <c r="C95" s="13">
         <v>1</v>
@@ -12747,10 +14296,10 @@
     </row>
     <row r="96" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="C96" s="13">
         <v>1</v>
@@ -12758,10 +14307,10 @@
     </row>
     <row r="97" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="C97" s="13">
         <v>1</v>
@@ -12769,10 +14318,10 @@
     </row>
     <row r="98" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="C98" s="13">
         <v>1</v>
@@ -12780,10 +14329,10 @@
     </row>
     <row r="99" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="C99" s="13">
         <v>1</v>
@@ -12791,10 +14340,10 @@
     </row>
     <row r="100" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>484</v>
+        <v>393</v>
       </c>
       <c r="C100" s="13">
         <v>1</v>
@@ -12802,10 +14351,10 @@
     </row>
     <row r="101" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>490</v>
+        <v>398</v>
       </c>
       <c r="C101" s="13">
         <v>1</v>
@@ -12813,10 +14362,10 @@
     </row>
     <row r="102" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>496</v>
+        <v>404</v>
       </c>
       <c r="C102" s="13">
         <v>1</v>
@@ -12824,10 +14373,10 @@
     </row>
     <row r="103" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>518</v>
+        <v>457</v>
       </c>
       <c r="C103" s="13">
         <v>1</v>
@@ -12835,10 +14384,10 @@
     </row>
     <row r="104" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>524</v>
+        <v>478</v>
       </c>
       <c r="C104" s="13">
         <v>1</v>
@@ -12846,10 +14395,10 @@
     </row>
     <row r="105" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>530</v>
+        <v>484</v>
       </c>
       <c r="C105" s="13">
         <v>1</v>
@@ -12857,10 +14406,10 @@
     </row>
     <row r="106" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>536</v>
+        <v>490</v>
       </c>
       <c r="C106" s="13">
         <v>1</v>
@@ -12868,10 +14417,10 @@
     </row>
     <row r="107" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>656</v>
+        <v>496</v>
       </c>
       <c r="C107" s="13">
         <v>1</v>
@@ -12879,10 +14428,10 @@
     </row>
     <row r="108" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>762</v>
+        <v>518</v>
       </c>
       <c r="C108" s="13">
         <v>1</v>
@@ -12890,10 +14439,10 @@
     </row>
     <row r="109" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>768</v>
+        <v>524</v>
       </c>
       <c r="C109" s="13">
         <v>1</v>
@@ -12901,10 +14450,10 @@
     </row>
     <row r="110" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>785</v>
+        <v>530</v>
       </c>
       <c r="C110" s="13">
         <v>1</v>
@@ -12912,10 +14461,10 @@
     </row>
     <row r="111" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>791</v>
+        <v>536</v>
       </c>
       <c r="C111" s="13">
         <v>1</v>
@@ -12923,10 +14472,10 @@
     </row>
     <row r="112" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>797</v>
+        <v>656</v>
       </c>
       <c r="C112" s="13">
         <v>1</v>
@@ -12934,10 +14483,10 @@
     </row>
     <row r="113" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>803</v>
+        <v>762</v>
       </c>
       <c r="C113" s="13">
         <v>1</v>
@@ -12945,10 +14494,10 @@
     </row>
     <row r="114" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>808</v>
+        <v>768</v>
       </c>
       <c r="C114" s="13">
         <v>1</v>
@@ -12956,10 +14505,10 @@
     </row>
     <row r="115" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="C115" s="13">
         <v>1</v>
@@ -12967,10 +14516,10 @@
     </row>
     <row r="116" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>859</v>
+        <v>791</v>
       </c>
       <c r="C116" s="13">
         <v>1</v>
@@ -12978,10 +14527,10 @@
     </row>
     <row r="117" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>892</v>
+        <v>797</v>
       </c>
       <c r="C117" s="13">
         <v>1</v>
@@ -12989,10 +14538,10 @@
     </row>
     <row r="118" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>903</v>
+        <v>803</v>
       </c>
       <c r="C118" s="13">
         <v>1</v>
@@ -13000,10 +14549,10 @@
     </row>
     <row r="119" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>909</v>
+        <v>808</v>
       </c>
       <c r="C119" s="13">
         <v>1</v>
@@ -13011,10 +14560,10 @@
     </row>
     <row r="120" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>937</v>
+        <v>814</v>
       </c>
       <c r="C120" s="13">
         <v>1</v>
@@ -13022,10 +14571,10 @@
     </row>
     <row r="121" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>954</v>
+        <v>859</v>
       </c>
       <c r="C121" s="13">
         <v>1</v>
@@ -13033,10 +14582,10 @@
     </row>
     <row r="122" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>960</v>
+        <v>892</v>
       </c>
       <c r="C122" s="13">
         <v>1</v>
@@ -13044,10 +14593,10 @@
     </row>
     <row r="123" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>977</v>
+        <v>903</v>
       </c>
       <c r="C123" s="13">
         <v>1</v>
@@ -13055,10 +14604,10 @@
     </row>
     <row r="124" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>983</v>
+        <v>909</v>
       </c>
       <c r="C124" s="13">
         <v>1</v>
@@ -13066,10 +14615,10 @@
     </row>
     <row r="125" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>1000</v>
+        <v>937</v>
       </c>
       <c r="C125" s="13">
         <v>1</v>
@@ -13077,10 +14626,10 @@
     </row>
     <row r="126" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>1006</v>
+        <v>954</v>
       </c>
       <c r="C126" s="13">
         <v>1</v>
@@ -13088,10 +14637,10 @@
     </row>
     <row r="127" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>1012</v>
+        <v>960</v>
       </c>
       <c r="C127" s="13">
         <v>1</v>
@@ -13099,10 +14648,10 @@
     </row>
     <row r="128" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>1050</v>
+        <v>977</v>
       </c>
       <c r="C128" s="13">
         <v>1</v>
@@ -13110,10 +14659,10 @@
     </row>
     <row r="129" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>1056</v>
+        <v>983</v>
       </c>
       <c r="C129" s="13">
         <v>1</v>
@@ -13121,10 +14670,10 @@
     </row>
     <row r="130" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>1062</v>
+        <v>1000</v>
       </c>
       <c r="C130" s="13">
         <v>1</v>
@@ -13132,10 +14681,10 @@
     </row>
     <row r="131" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>1068</v>
+        <v>1006</v>
       </c>
       <c r="C131" s="13">
         <v>1</v>
@@ -13143,10 +14692,10 @@
     </row>
     <row r="132" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>1074</v>
+        <v>1012</v>
       </c>
       <c r="C132" s="13">
         <v>1</v>
@@ -13154,10 +14703,10 @@
     </row>
     <row r="133" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="C133" s="13">
         <v>1</v>
@@ -13165,10 +14714,10 @@
     </row>
     <row r="134" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>1086</v>
+        <v>1056</v>
       </c>
       <c r="C134" s="13">
         <v>1</v>
@@ -13176,10 +14725,10 @@
     </row>
     <row r="135" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>1092</v>
+        <v>1062</v>
       </c>
       <c r="C135" s="13">
         <v>1</v>
@@ -13187,10 +14736,10 @@
     </row>
     <row r="136" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>1097</v>
+        <v>1068</v>
       </c>
       <c r="C136" s="13">
         <v>1</v>
@@ -13198,10 +14747,10 @@
     </row>
     <row r="137" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>1103</v>
+        <v>1074</v>
       </c>
       <c r="C137" s="13">
         <v>1</v>
@@ -13209,10 +14758,10 @@
     </row>
     <row r="138" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>1109</v>
+        <v>1080</v>
       </c>
       <c r="C138" s="13">
         <v>1</v>
@@ -13220,10 +14769,10 @@
     </row>
     <row r="139" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>1115</v>
+        <v>1086</v>
       </c>
       <c r="C139" s="13">
         <v>1</v>
@@ -13231,10 +14780,10 @@
     </row>
     <row r="140" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>1121</v>
+        <v>1092</v>
       </c>
       <c r="C140" s="13">
         <v>1</v>
@@ -13242,10 +14791,10 @@
     </row>
     <row r="141" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>1127</v>
+        <v>1097</v>
       </c>
       <c r="C141" s="13">
         <v>1</v>
@@ -13253,10 +14802,10 @@
     </row>
     <row r="142" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>1133</v>
+        <v>1103</v>
       </c>
       <c r="C142" s="13">
         <v>1</v>
@@ -13264,10 +14813,10 @@
     </row>
     <row r="143" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>1139</v>
+        <v>1109</v>
       </c>
       <c r="C143" s="13">
         <v>1</v>
@@ -13275,10 +14824,10 @@
     </row>
     <row r="144" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>1145</v>
+        <v>1115</v>
       </c>
       <c r="C144" s="13">
         <v>1</v>
@@ -13286,10 +14835,10 @@
     </row>
     <row r="145" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>1151</v>
+        <v>1121</v>
       </c>
       <c r="C145" s="13">
         <v>1</v>
@@ -13297,10 +14846,10 @@
     </row>
     <row r="146" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>1157</v>
+        <v>1127</v>
       </c>
       <c r="C146" s="13">
         <v>1</v>
@@ -13308,10 +14857,10 @@
     </row>
     <row r="147" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>1163</v>
+        <v>1133</v>
       </c>
       <c r="C147" s="13">
         <v>1</v>
@@ -13319,10 +14868,10 @@
     </row>
     <row r="148" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>1169</v>
+        <v>1139</v>
       </c>
       <c r="C148" s="13">
         <v>1</v>
@@ -13330,10 +14879,10 @@
     </row>
     <row r="149" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>1175</v>
+        <v>1145</v>
       </c>
       <c r="C149" s="13">
         <v>1</v>
@@ -13341,10 +14890,10 @@
     </row>
     <row r="150" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>1181</v>
+        <v>1151</v>
       </c>
       <c r="C150" s="13">
         <v>1</v>
@@ -13352,10 +14901,10 @@
     </row>
     <row r="151" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>1187</v>
+        <v>1157</v>
       </c>
       <c r="C151" s="13">
         <v>1</v>
@@ -13363,10 +14912,10 @@
     </row>
     <row r="152" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>1193</v>
+        <v>1163</v>
       </c>
       <c r="C152" s="13">
         <v>1</v>
@@ -13374,10 +14923,10 @@
     </row>
     <row r="153" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>1210</v>
+        <v>1169</v>
       </c>
       <c r="C153" s="13">
         <v>1</v>
@@ -13385,10 +14934,10 @@
     </row>
     <row r="154" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>1216</v>
+        <v>1175</v>
       </c>
       <c r="C154" s="13">
         <v>1</v>
@@ -13396,10 +14945,10 @@
     </row>
     <row r="155" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>1222</v>
+        <v>1181</v>
       </c>
       <c r="C155" s="13">
         <v>1</v>
@@ -13407,10 +14956,10 @@
     </row>
     <row r="156" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>1228</v>
+        <v>1187</v>
       </c>
       <c r="C156" s="13">
         <v>1</v>
@@ -13418,10 +14967,10 @@
     </row>
     <row r="157" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>1234</v>
+        <v>1193</v>
       </c>
       <c r="C157" s="13">
         <v>1</v>
@@ -13429,12 +14978,342 @@
     </row>
     <row r="158" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
-        <v>1268</v>
+        <v>1458</v>
       </c>
       <c r="B158" s="13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C158" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B159" s="13" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C159" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C160" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C161" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C162" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B163" s="13" t="s">
         <v>1240</v>
       </c>
-      <c r="C158" s="13">
+      <c r="C163" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C164" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C165" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C166" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C167" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C168" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C169" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C170" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C171" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C172" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C173" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B174" s="13" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C174" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C175" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B176" s="13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C176" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B177" s="13" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C177" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C178" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C179" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C180" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C181" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C182" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C183" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C184" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C185" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C186" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C187" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C188" s="13">
         <v>1</v>
       </c>
     </row>
@@ -13463,10 +15342,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>1269</v>
+        <v>1459</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>1270</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13474,13 +15353,13 @@
         <v>74</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1271</v>
+        <v>1461</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1272</v>
+        <v>1462</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1273</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13488,13 +15367,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1266</v>
+        <v>1456</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1274</v>
+        <v>1464</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1275</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13502,13 +15381,13 @@
         <v>74</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1276</v>
+        <v>1466</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1277</v>
+        <v>1467</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1278</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13516,13 +15395,13 @@
         <v>74</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1280</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13530,13 +15409,13 @@
         <v>189</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1281</v>
+        <v>1471</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1282</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13544,13 +15423,13 @@
         <v>189</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1283</v>
+        <v>1473</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1285</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13558,13 +15437,13 @@
         <v>189</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1286</v>
+        <v>1476</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1287</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13572,13 +15451,13 @@
         <v>176</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1288</v>
+        <v>1478</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1289</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13586,13 +15465,13 @@
         <v>176</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1290</v>
+        <v>1480</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1291</v>
+        <v>1481</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1292</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13600,13 +15479,13 @@
         <v>176</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1293</v>
+        <v>1483</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1294</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13614,13 +15493,13 @@
         <v>176</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1295</v>
+        <v>1485</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1296</v>
+        <v>1486</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1297</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13628,13 +15507,13 @@
         <v>183</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1298</v>
+        <v>1488</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1299</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13642,13 +15521,13 @@
         <v>183</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>1300</v>
+        <v>1490</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1301</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13656,13 +15535,13 @@
         <v>183</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1302</v>
+        <v>1492</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1303</v>
+        <v>1493</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1304</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13670,13 +15549,13 @@
         <v>183</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1305</v>
+        <v>1495</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1306</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13684,13 +15563,13 @@
         <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1307</v>
+        <v>1497</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1308</v>
+        <v>1498</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>1309</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13698,13 +15577,13 @@
         <v>57</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1310</v>
+        <v>1500</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1311</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -13712,55 +15591,55 @@
         <v>57</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1312</v>
+        <v>1502</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1313</v>
+        <v>1503</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>1314</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>1315</v>
+        <v>1505</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>1267</v>
+        <v>1457</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1316</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>1315</v>
+        <v>1505</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>1317</v>
+        <v>1507</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1279</v>
+        <v>1469</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>1318</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>1319</v>
+        <v>1509</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>1320</v>
+        <v>1510</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1284</v>
+        <v>1474</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1321</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>
@@ -13786,424 +15665,424 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1322</v>
+        <v>1512</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>1323</v>
+        <v>1513</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>1324</v>
+        <v>1514</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>1325</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1326</v>
+        <v>1516</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>1328</v>
+        <v>1518</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1329</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1330</v>
+        <v>1520</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1331</v>
+        <v>1521</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1332</v>
+        <v>1522</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1333</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1334</v>
+        <v>1524</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1335</v>
+        <v>1525</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1336</v>
+        <v>1526</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1337</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1338</v>
+        <v>1528</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1339</v>
+        <v>1529</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1340</v>
+        <v>1530</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1341</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>1255</v>
+        <v>1443</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1342</v>
+        <v>1532</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1343</v>
+        <v>1533</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>148</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1344</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>1345</v>
+        <v>1535</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1346</v>
+        <v>1536</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1347</v>
+        <v>1537</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1348</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>1345</v>
+        <v>1535</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1349</v>
+        <v>1539</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1350</v>
+        <v>1540</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1351</v>
+        <v>1541</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1352</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>1259</v>
+        <v>1447</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1353</v>
+        <v>1543</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1354</v>
+        <v>1544</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1355</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>1259</v>
+        <v>1447</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>1356</v>
+        <v>1546</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1357</v>
+        <v>1547</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>341</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1358</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>1256</v>
+        <v>1444</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1359</v>
+        <v>1549</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1360</v>
+        <v>1550</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1361</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>1256</v>
+        <v>1444</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1362</v>
+        <v>1552</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1363</v>
+        <v>1553</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1364</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>1256</v>
+        <v>1444</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1365</v>
+        <v>1555</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1366</v>
+        <v>1556</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1367</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>1368</v>
+        <v>1558</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1369</v>
+        <v>1559</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1370</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>1371</v>
+        <v>1561</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1357</v>
+        <v>1547</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>672</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1372</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1373</v>
+        <v>1563</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1374</v>
+        <v>1564</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1375</v>
+        <v>1565</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1376</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1377</v>
+        <v>1567</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1378</v>
+        <v>1568</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>1379</v>
+        <v>1569</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1380</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1381</v>
+        <v>1571</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1357</v>
+        <v>1547</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>694</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1382</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1383</v>
+        <v>1573</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1357</v>
+        <v>1547</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1384</v>
+        <v>1574</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1385</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1386</v>
+        <v>1576</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1357</v>
+        <v>1547</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>677</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>1387</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>1254</v>
+        <v>1442</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>1388</v>
+        <v>1578</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>1389</v>
+        <v>1579</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>1390</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>1257</v>
+        <v>1445</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>1391</v>
+        <v>1581</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1392</v>
+        <v>1582</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1393</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>1257</v>
+        <v>1445</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1394</v>
+        <v>1584</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>1395</v>
+        <v>1585</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>1396</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>1257</v>
+        <v>1445</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>1397</v>
+        <v>1587</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1398</v>
+        <v>1588</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>1399</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>1400</v>
+        <v>1590</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>1401</v>
+        <v>1591</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1402</v>
+        <v>1592</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>1403</v>
+        <v>1593</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>1404</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14211,16 +16090,16 @@
         <v>57</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>1405</v>
+        <v>1595</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>1406</v>
+        <v>1596</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>1407</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14228,118 +16107,118 @@
         <v>57</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>1408</v>
+        <v>1598</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>1044</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>1409</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>1266</v>
+        <v>1456</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>1410</v>
+        <v>1600</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1411</v>
+        <v>1601</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1412</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>1413</v>
+        <v>1448</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>1414</v>
+        <v>1603</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>1415</v>
+        <v>1604</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>1384</v>
+        <v>1605</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>1416</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>1417</v>
+        <v>1450</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>1418</v>
+        <v>1607</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1419</v>
+        <v>1608</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>625</v>
+        <v>1609</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1420</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>1317</v>
+        <v>1507</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>1421</v>
+        <v>1611</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>1422</v>
+        <v>1612</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>1423</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>1263</v>
+        <v>1453</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>1424</v>
+        <v>1614</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>1327</v>
+        <v>1517</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1425</v>
+        <v>1615</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1426</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>1263</v>
+        <v>1453</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>1427</v>
+        <v>1617</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>1428</v>
+        <v>1618</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>1180</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>1429</v>
+        <v>1619</v>
       </c>
     </row>
   </sheetData>
@@ -14363,12 +16242,12 @@
     </row>
     <row r="2" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>1430</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>1431</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14378,17 +16257,17 @@
     </row>
     <row r="5" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>1432</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>1433</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>1434</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14398,22 +16277,22 @@
     </row>
     <row r="9" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>1435</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>1436</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>1437</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="12" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>1438</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14423,17 +16302,17 @@
     </row>
     <row r="14" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>1439</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="15" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>1440</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>1441</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14443,17 +16322,17 @@
     </row>
     <row r="18" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>1442</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>1443</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>1444</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14463,32 +16342,32 @@
     </row>
     <row r="22" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>1445</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>1446</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>1447</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>1448</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>1449</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>1450</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14498,22 +16377,22 @@
     </row>
     <row r="29" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>1451</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>1452</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>1453</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>1454</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="33" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -14523,12 +16402,12 @@
     </row>
     <row r="34" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>1455</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="35" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>1456</v>
+        <v>1646</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1718">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -3446,6 +3446,52 @@
     <t>The export contains only Clinic A data and the totals match the screen. A single Clinic B row appearing in the export is a serious tenant-isolation defect and must be raised immediately.</t>
   </si>
   <si>
+    <t>TC-BILL-025</t>
+  </si>
+  <si>
+    <t>Billing — Bill arithmetic</t>
+  </si>
+  <si>
+    <t>Gross minus discount always equals net, and net never leaves its bounds</t>
+  </si>
+  <si>
+    <t>A clinic with the sales feature, a doctor with a consultation fee, and at least one priced procedure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book an appointment and note the consultation fee shown.
+2. Add a procedure with a quantity greater than one.
+3. Apply a per-line discount to that procedure.
+4. Apply an appointment-level discount as a flat amount.
+5. Record the gross, the total discount and the net from the bill.
+6. Confirm gross minus discount equals net exactly.
+7. Repeat with the appointment discount as a percentage.
+8. Repeat with a 100 percent discount and confirm the net is zero, never negative.
+9. Repeat with no discount at all and confirm gross equals net.</t>
+  </si>
+  <si>
+    <t>For every combination the printed gross minus the printed discount equals the printed net to the rupee, the net is never below zero, and the net never exceeds the gross. A bill that fails this is showing the patient one number and the report another.</t>
+  </si>
+  <si>
+    <t>TC-BILL-026</t>
+  </si>
+  <si>
+    <t>A per-line discount applies before the appointment discount</t>
+  </si>
+  <si>
+    <t>A clinic with the sales feature and a procedure priced at 1000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book an appointment with NO consultation fee charged.
+2. Add the procedure priced at 1000, quantity 1.
+3. Apply a per-line discount of 200 to that procedure.
+4. Apply an appointment-level discount of 10 percent.
+5. Read the net from the running total and from the saved bill.
+6. Compare it against the two possible orders: 720 if the line discount applies first, 700 if the appointment discount were applied to the gross.</t>
+  </si>
+  <si>
+    <t>The net is 720. The line is discounted first to 800, that becomes the subtotal, and the 10 percent appointment discount applies to the SUBTOTAL — never to the gross. A net of 700 would mean the order is reversed, which would understate every bill carrying both kinds of discount.</t>
+  </si>
+  <si>
     <t>TC-CLIN-001</t>
   </si>
   <si>
@@ -4194,6 +4240,67 @@
   </si>
   <si>
     <t>Every clinic role reaches Settings, because it holds their own profile and password. Only the Clinic Admin additionally sees the clinic-wide cards such as clinic details, printing and the account manager. The personal cards are identical for everyone.</t>
+  </si>
+  <si>
+    <t>TC-SUPER-021</t>
+  </si>
+  <si>
+    <t>Admin — Price history</t>
+  </si>
+  <si>
+    <t>Recording a price that never changes alters nothing</t>
+  </si>
+  <si>
+    <t>Two clinics on the same monthly price and the same billing start. One has its price recorded explicitly; the other has never been re-priced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the monthly price and billing start date for both clinics.
+2. Open each clinic's billing card and record the accrued total, the balance and the paid-through date.
+3. Open the payment scorecard for each and record the rating and the month-by-month history.
+4. Compare the two clinics field by field.</t>
+  </si>
+  <si>
+    <t>The two clinics agree on every figure. Recording a price that never moved is a no-op. This is the safety property the whole price-history feature rests on: it had to be provably invisible to every clinic it does not concern before it could be trusted on the few it does.</t>
+  </si>
+  <si>
+    <t>TC-SUPER-022</t>
+  </si>
+  <si>
+    <t>A price rise applies only from its own date forward</t>
+  </si>
+  <si>
+    <t>A clinic billed for six months, priced at 5000 for the first five and raised to 8000 for the most recent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the clinic's billing start date and its original monthly price.
+2. Raise the monthly price and save, so the change is recorded from today.
+3. Open the clinic's billing card and read the total accrued across all six months.
+4. Calculate the expected figure by hand: five months at the old price plus one at the new.
+5. Compare the two.
+6. Open the month-by-month history and confirm each month shows the price in force at the time.</t>
+  </si>
+  <si>
+    <t>The accrued total equals five months at the old price plus one at the new, not six at the new price. Each month in the history is charged at the price that was in force on its own due date.</t>
+  </si>
+  <si>
+    <t>TC-SUPER-023</t>
+  </si>
+  <si>
+    <t>Months covered are walked, not divided</t>
+  </si>
+  <si>
+    <t>A clinic whose price changed partway through its billing history, with a known total paid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the clinic's price history and the total amount it has paid.
+2. Open the billing card and read how many months are recorded as covered.
+3. Work the figure out by hand by walking the months in order, deducting each month's own price from the amount paid until the money runs out.
+4. Compare with a naive calculation of total paid divided by the CURRENT price.
+5. Confirm the application agrees with the walk and not with the division.
+6. Record a partial payment that does not complete a month and confirm that month is simply not counted.</t>
+  </si>
+  <si>
+    <t>The months covered match the walk, where each month is deducted at the price it actually cost. A figure matching total divided by today's price would mean the early months were re-priced. A partial payment leaves its month uncounted rather than partially counted.</t>
   </si>
   <si>
     <t>TC-LIST-001</t>
@@ -5517,24 +5624,24 @@
     <t>Authentication</t>
   </si>
   <si>
+    <t>Billing</t>
+  </si>
+  <si>
     <t>Appointments</t>
   </si>
   <si>
-    <t>Billing</t>
-  </si>
-  <si>
     <t>RBAC</t>
   </si>
   <si>
     <t>Patients</t>
   </si>
   <si>
+    <t>Admin</t>
+  </si>
+  <si>
     <t>WhatsApp</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
     <t>Scheduled jobs</t>
   </si>
   <si>
@@ -6201,10 +6308,58 @@
     <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
   </si>
   <si>
+    <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
+  </si>
+  <si>
+    <t>with fee Rs 5,000, without Rs 2,000 — difference Rs 3,000 equals the consultation fee exactly</t>
+  </si>
+  <si>
+    <t>amount 500 -&gt; Rs 4,500; percent 20 of subtotal 5000 -&gt; discount Rs 1,000, net Rs 4,000; percent 150 clamped to 100 giving net Rs 0; negative rejected: "Discount can't be negative."</t>
+  </si>
+  <si>
+    <t>across 48 fee/line/discount combinations, gross minus discount equals net every time and net never goes below zero or above gross</t>
+  </si>
+  <si>
+    <t>line 1000 less 200 = Rs 800, then 10% of the SUBTOTAL = Rs 80, net Rs 720 (Rs 720 proves the line discount applies first; Rs 700 would mean the order is wrong)</t>
+  </si>
+  <si>
+    <t>partial Rs 1,000 then Rs 2,000 recorded as 2 rows totalling Rs 3,000 against a Rs 3,000 bill</t>
+  </si>
+  <si>
+    <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
+  </si>
+  <si>
+    <t>zero -&gt; "Enter an amount greater than zero.", negative -&gt; refused, NaN -&gt; refused; none created a payment row</t>
+  </si>
+  <si>
+    <t>paid Rs 2,500 against a Rs 2,000 bill — patient credit is now Rs 500, so the excess is retained rather than discarded</t>
+  </si>
+  <si>
+    <t>payment voided; the row is SOFT-deleted (recoverable from Trash) rather than erased, so the audit trail survives</t>
+  </si>
+  <si>
+    <t>refund of Rs 5,000 against Rs 2,000 collected refused ("Can't refund more than collected (Rs 2000)."); a Rs 500 refund succeeded</t>
+  </si>
+  <si>
+    <t>three invoices issued -&gt; numbers 1, 2, 3 (unique: true, sequential: true)</t>
+  </si>
+  <si>
+    <t>a month four months ago is still priced at Rs 5,000 after a rise to Rs 8,000 — history is NOT re-priced (the clinic whose price never moved reads Rs 5,000 for the same month)</t>
+  </si>
+  <si>
+    <t>six months accrue to Rs 30,000 whether the unchanged price is recorded or absent (Rs 30,000) — recording a price that never moved is a no-op, which is the safety property the whole feature rests on</t>
+  </si>
+  <si>
+    <t>the re-priced clinic accrues Rs 33,000 over six months — five at Rs 5,000 plus one at Rs 8,000 (Rs 33,000 expected); the rise applies only from its own date forward</t>
+  </si>
+  <si>
+    <t>Rs 15,000 covers 3 months at a flat Rs 5,000 and 3 on the re-priced clinic — the early months are charged at what they actually cost, not at today's figure</t>
+  </si>
+  <si>
     <t>SCOPE</t>
   </si>
   <si>
-    <t>23 of 255 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 232 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
+    <t>39 of 260 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 221 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
   </si>
 </sst>
 </file>
@@ -6708,7 +6863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9035,7 +9190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>490</v>
       </c>
@@ -9058,10 +9213,10 @@
         <v>495</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>496</v>
       </c>
@@ -9084,10 +9239,10 @@
         <v>501</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>502</v>
       </c>
@@ -9110,7 +9265,7 @@
         <v>507</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -10413,7 +10568,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>774</v>
       </c>
@@ -10436,10 +10591,10 @@
         <v>779</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>780</v>
       </c>
@@ -10462,10 +10617,10 @@
         <v>784</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>785</v>
       </c>
@@ -10488,10 +10643,10 @@
         <v>790</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>791</v>
       </c>
@@ -10514,7 +10669,7 @@
         <v>796</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -10569,7 +10724,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>808</v>
       </c>
@@ -10592,10 +10747,10 @@
         <v>813</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>814</v>
       </c>
@@ -10618,7 +10773,7 @@
         <v>819</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -10725,7 +10880,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="155" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>843</v>
       </c>
@@ -10748,7 +10903,7 @@
         <v>847</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -11037,12 +11192,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="167" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>909</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>910</v>
@@ -11060,44 +11215,44 @@
         <v>914</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>915</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="C168" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="E168" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="E168" s="2" t="s">
+      <c r="F168" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="F168" s="2" t="s">
+      <c r="G168" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="G168" s="2" t="s">
-        <v>920</v>
-      </c>
       <c r="H168" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>922</v>
@@ -11172,7 +11327,7 @@
         <v>937</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>938</v>
@@ -11201,19 +11356,19 @@
         <v>177</v>
       </c>
       <c r="C173" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="D173" s="2" t="s">
+      <c r="E173" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="F173" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="G173" s="2" t="s">
         <v>947</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>948</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>41</v>
@@ -11221,13 +11376,13 @@
     </row>
     <row r="174" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>950</v>
@@ -11279,19 +11434,19 @@
         <v>177</v>
       </c>
       <c r="C176" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="E176" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="E176" s="2" t="s">
+      <c r="F176" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="F176" s="2" t="s">
+      <c r="G176" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>965</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>41</v>
@@ -11299,25 +11454,25 @@
     </row>
     <row r="177" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C177" s="2" t="s">
+      <c r="D177" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="E177" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="E177" s="2" t="s">
+      <c r="F177" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="F177" s="2" t="s">
+      <c r="G177" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>41</v>
@@ -11325,13 +11480,13 @@
     </row>
     <row r="178" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>967</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>973</v>
@@ -11354,7 +11509,7 @@
         <v>977</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>978</v>
@@ -11380,22 +11535,22 @@
         <v>983</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="C180" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="D180" s="2" t="s">
+      <c r="E180" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="E180" s="2" t="s">
+      <c r="F180" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="F180" s="2" t="s">
+      <c r="G180" s="2" t="s">
         <v>987</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>988</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>41</v>
@@ -11403,25 +11558,25 @@
     </row>
     <row r="181" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C181" s="2" t="s">
+      <c r="D181" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="E181" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="E181" s="2" t="s">
+      <c r="F181" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="F181" s="2" t="s">
+      <c r="G181" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>41</v>
@@ -11429,13 +11584,13 @@
     </row>
     <row r="182" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>990</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>996</v>
@@ -11487,19 +11642,19 @@
         <v>58</v>
       </c>
       <c r="C184" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D184" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="E184" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="E184" s="2" t="s">
+      <c r="F184" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="F184" s="2" t="s">
+      <c r="G184" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>1011</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>41</v>
@@ -11507,25 +11662,25 @@
     </row>
     <row r="185" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C185" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="E185" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="E185" s="2" t="s">
+      <c r="F185" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="F185" s="2" t="s">
+      <c r="G185" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>1017</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>41</v>
@@ -11533,25 +11688,25 @@
     </row>
     <row r="186" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D186" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="E186" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="F186" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="G186" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>1023</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>41</v>
@@ -11559,13 +11714,13 @@
     </row>
     <row r="187" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>1025</v>
@@ -11591,19 +11746,19 @@
         <v>58</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>41</v>
@@ -11611,25 +11766,25 @@
     </row>
     <row r="189" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>41</v>
@@ -11637,13 +11792,13 @@
     </row>
     <row r="190" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>1041</v>
@@ -11669,7 +11824,7 @@
         <v>58</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>1046</v>
@@ -11713,7 +11868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="193" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>1056</v>
       </c>
@@ -11721,45 +11876,45 @@
         <v>58</v>
       </c>
       <c r="C193" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D193" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="D193" s="2" t="s">
+      <c r="E193" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="E193" s="2" t="s">
+      <c r="F193" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="F193" s="2" t="s">
+      <c r="G193" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="G193" s="2" t="s">
-        <v>1061</v>
-      </c>
       <c r="H193" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D194" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="E194" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="F194" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="F194" s="2" t="s">
+      <c r="G194" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>1067</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>41</v>
@@ -11767,25 +11922,25 @@
     </row>
     <row r="195" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C195" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="E195" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="E195" s="2" t="s">
+      <c r="F195" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="F195" s="2" t="s">
+      <c r="G195" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>1073</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>41</v>
@@ -11793,25 +11948,25 @@
     </row>
     <row r="196" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C196" s="2" t="s">
+      <c r="D196" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="E196" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="E196" s="2" t="s">
+      <c r="F196" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="F196" s="2" t="s">
+      <c r="G196" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>41</v>
@@ -11819,25 +11974,25 @@
     </row>
     <row r="197" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C197" s="2" t="s">
+      <c r="D197" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="E197" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="E197" s="2" t="s">
+      <c r="F197" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="F197" s="2" t="s">
+      <c r="G197" s="2" t="s">
         <v>1084</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>1085</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>41</v>
@@ -11845,25 +12000,25 @@
     </row>
     <row r="198" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C198" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="E198" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="E198" s="2" t="s">
+      <c r="F198" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="F198" s="2" t="s">
+      <c r="G198" s="2" t="s">
         <v>1090</v>
-      </c>
-      <c r="G198" s="2" t="s">
-        <v>1091</v>
       </c>
       <c r="H198" s="4" t="s">
         <v>41</v>
@@ -11871,19 +12026,19 @@
     </row>
     <row r="199" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C199" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="E199" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>1095</v>
@@ -11900,7 +12055,7 @@
         <v>1097</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>1098</v>
@@ -11926,7 +12081,7 @@
         <v>1103</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>1104</v>
@@ -11935,13 +12090,13 @@
         <v>1105</v>
       </c>
       <c r="E201" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="F201" s="2" t="s">
+      <c r="G201" s="2" t="s">
         <v>1107</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>1108</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>41</v>
@@ -11949,129 +12104,129 @@
     </row>
     <row r="202" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C202" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="E202" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="E202" s="2" t="s">
+      <c r="F202" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="F202" s="2" t="s">
+      <c r="G202" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="H202" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="H202" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="3" t="s">
+      <c r="B203" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C203" s="2" t="s">
+      <c r="D203" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="E203" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="E203" s="2" t="s">
+      <c r="F203" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="F203" s="2" t="s">
+      <c r="G203" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="H203" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="H203" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
+      <c r="B204" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D204" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C204" s="2" t="s">
+      <c r="E204" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="F204" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="E204" s="2" t="s">
+      <c r="G204" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="F204" s="2" t="s">
+      <c r="H204" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="B205" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D205" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="H204" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
+      <c r="E205" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C205" s="2" t="s">
+      <c r="F205" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="G205" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="E205" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G205" s="2" t="s">
-        <v>1132</v>
-      </c>
       <c r="H205" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C206" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="G206" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G206" s="2" t="s">
-        <v>1138</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>41</v>
@@ -12079,25 +12234,25 @@
     </row>
     <row r="207" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C207" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="G207" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>1144</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>41</v>
@@ -12105,25 +12260,25 @@
     </row>
     <row r="208" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C208" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="G208" s="2" t="s">
         <v>1147</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G208" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>41</v>
@@ -12131,25 +12286,25 @@
     </row>
     <row r="209" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C209" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="G209" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>1156</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>41</v>
@@ -12157,25 +12312,25 @@
     </row>
     <row r="210" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C210" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="G210" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>1162</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>41</v>
@@ -12183,25 +12338,25 @@
     </row>
     <row r="211" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C211" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="G211" s="2" t="s">
         <v>1165</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>1168</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>41</v>
@@ -12209,25 +12364,25 @@
     </row>
     <row r="212" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C212" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="G212" s="2" t="s">
         <v>1171</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>1174</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>41</v>
@@ -12235,77 +12390,77 @@
     </row>
     <row r="213" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C213" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="G213" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="E213" s="2" t="s">
+      <c r="H213" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
         <v>1178</v>
       </c>
-      <c r="F213" s="2" t="s">
+      <c r="B214" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="G213" s="2" t="s">
+      <c r="D214" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="H213" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="3" t="s">
+      <c r="E214" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C214" s="2" t="s">
+      <c r="F214" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="G214" s="2" t="s">
         <v>1183</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>1186</v>
-      </c>
       <c r="H214" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C215" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="G215" s="2" t="s">
         <v>1189</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G215" s="2" t="s">
-        <v>1192</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>41</v>
@@ -12313,129 +12468,129 @@
     </row>
     <row r="216" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C216" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F216" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="G216" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="E216" s="2" t="s">
+      <c r="H216" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
         <v>1196</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="B217" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="G216" s="2" t="s">
+      <c r="D217" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="H216" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="8" t="s">
+      <c r="E217" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="B217" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C217" s="7" t="s">
+      <c r="F217" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="D217" s="7" t="s">
+      <c r="G217" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="E217" s="7" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F217" s="7" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G217" s="7" t="s">
-        <v>1204</v>
-      </c>
-      <c r="H217" s="9" t="s">
+      <c r="H217" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="218" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D218" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="G218" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="H218" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
         <v>1208</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="B219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="H218" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="3" t="s">
+      <c r="D219" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C219" s="2" t="s">
+      <c r="E219" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="F219" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="E219" s="2" t="s">
+      <c r="G219" s="2" t="s">
         <v>1213</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>1215</v>
-      </c>
       <c r="H219" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="F220" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="E220" s="2" t="s">
+      <c r="G220" s="2" t="s">
         <v>1219</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>1221</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>41</v>
@@ -12443,77 +12598,77 @@
     </row>
     <row r="221" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C221" s="2" t="s">
+      <c r="E221" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="F221" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="E221" s="2" t="s">
+      <c r="G221" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="F221" s="2" t="s">
+      <c r="H221" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="G221" s="2" t="s">
+      <c r="B222" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C222" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="H221" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="3" t="s">
+      <c r="D222" s="7" t="s">
         <v>1228</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C222" s="2" t="s">
+      <c r="E222" s="7" t="s">
         <v>1229</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="F222" s="7" t="s">
         <v>1230</v>
       </c>
-      <c r="E222" s="2" t="s">
+      <c r="G222" s="7" t="s">
         <v>1231</v>
       </c>
-      <c r="F222" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G222" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="H222" s="4" t="s">
+      <c r="H222" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="223" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C223" s="2" t="s">
+      <c r="F223" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="G223" s="2" t="s">
         <v>1236</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G223" s="2" t="s">
-        <v>1239</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>41</v>
@@ -12521,25 +12676,25 @@
     </row>
     <row r="224" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="G224" s="2" t="s">
         <v>1242</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>1245</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>41</v>
@@ -12547,25 +12702,25 @@
     </row>
     <row r="225" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C225" s="2" t="s">
+      <c r="F225" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="G225" s="2" t="s">
         <v>1248</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G225" s="2" t="s">
-        <v>1251</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>41</v>
@@ -12573,25 +12728,25 @@
     </row>
     <row r="226" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C226" s="2" t="s">
+      <c r="F226" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="G226" s="2" t="s">
         <v>1254</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>1257</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>41</v>
@@ -12599,25 +12754,25 @@
     </row>
     <row r="227" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C227" s="2" t="s">
+      <c r="F227" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="G227" s="2" t="s">
         <v>1260</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>1263</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>41</v>
@@ -12625,25 +12780,25 @@
     </row>
     <row r="228" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C228" s="2" t="s">
+      <c r="F228" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="G228" s="2" t="s">
         <v>1266</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>1269</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>41</v>
@@ -12651,25 +12806,25 @@
     </row>
     <row r="229" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C229" s="2" t="s">
+      <c r="F229" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="G229" s="2" t="s">
         <v>1272</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G229" s="2" t="s">
-        <v>1275</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>41</v>
@@ -12677,25 +12832,25 @@
     </row>
     <row r="230" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C230" s="2" t="s">
+      <c r="F230" s="2" t="s">
         <v>1277</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="G230" s="2" t="s">
         <v>1278</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1280</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>1281</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>41</v>
@@ -12703,25 +12858,25 @@
     </row>
     <row r="231" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C231" s="2" t="s">
+      <c r="F231" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="G231" s="2" t="s">
         <v>1284</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="G231" s="2" t="s">
-        <v>1287</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>41</v>
@@ -12729,103 +12884,103 @@
     </row>
     <row r="232" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="F232" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H233" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C232" s="2" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>1290</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1292</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="H232" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="8" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C233" s="7" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D233" s="7" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E233" s="7" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F233" s="7" t="s">
+      <c r="C234" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="G233" s="7" t="s">
+      <c r="D234" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="H233" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="8" t="s">
+      <c r="E234" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="B234" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C234" s="7" t="s">
+      <c r="F234" s="2" t="s">
         <v>1301</v>
       </c>
-      <c r="D234" s="7" t="s">
+      <c r="G234" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="E234" s="7" t="s">
-        <v>1303</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="G234" s="7" t="s">
-        <v>1305</v>
-      </c>
-      <c r="H234" s="9" t="s">
+      <c r="H234" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="235" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C235" s="2" t="s">
+      <c r="F235" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="G235" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>1310</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>1311</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>41</v>
@@ -12833,25 +12988,25 @@
     </row>
     <row r="236" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D236" s="2" t="s">
+      <c r="F236" s="2" t="s">
         <v>1313</v>
       </c>
-      <c r="E236" s="2" t="s">
+      <c r="G236" s="2" t="s">
         <v>1314</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>1316</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>41</v>
@@ -12859,103 +13014,103 @@
     </row>
     <row r="237" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D237" s="2" t="s">
+      <c r="E237" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="E237" s="2" t="s">
+      <c r="F237" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="F237" s="2" t="s">
+      <c r="G237" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="G237" s="2" t="s">
+      <c r="H237" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="8" t="s">
         <v>1321</v>
       </c>
-      <c r="H237" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="3" t="s">
+      <c r="B238" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C238" s="7" t="s">
         <v>1322</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C238" s="2" t="s">
+      <c r="D238" s="7" t="s">
         <v>1323</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="E238" s="7" t="s">
         <v>1324</v>
       </c>
-      <c r="E238" s="2" t="s">
+      <c r="F238" s="7" t="s">
         <v>1325</v>
       </c>
-      <c r="F238" s="2" t="s">
+      <c r="G238" s="7" t="s">
         <v>1326</v>
       </c>
-      <c r="G238" s="2" t="s">
+      <c r="H238" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="8" t="s">
         <v>1327</v>
       </c>
-      <c r="H238" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="3" t="s">
+      <c r="B239" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C239" s="7" t="s">
         <v>1328</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C239" s="2" t="s">
+      <c r="D239" s="7" t="s">
         <v>1329</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="E239" s="7" t="s">
         <v>1330</v>
       </c>
-      <c r="E239" s="2" t="s">
+      <c r="F239" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="F239" s="2" t="s">
+      <c r="G239" s="7" t="s">
         <v>1332</v>
       </c>
-      <c r="G239" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="H239" s="4" t="s">
+      <c r="H239" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="240" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C240" s="2" t="s">
+      <c r="D240" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="E240" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="E240" s="2" t="s">
+      <c r="F240" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="G240" s="2" t="s">
         <v>1338</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>1339</v>
       </c>
       <c r="H240" s="4" t="s">
         <v>41</v>
@@ -12963,25 +13118,25 @@
     </row>
     <row r="241" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="D241" s="2" t="s">
+      <c r="F241" s="2" t="s">
         <v>1342</v>
       </c>
-      <c r="E241" s="2" t="s">
+      <c r="G241" s="2" t="s">
         <v>1343</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G241" s="2" t="s">
-        <v>1345</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>41</v>
@@ -12989,25 +13144,25 @@
     </row>
     <row r="242" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C242" s="2" t="s">
+      <c r="F242" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="G242" s="2" t="s">
         <v>1348</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>1349</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G242" s="2" t="s">
-        <v>1351</v>
       </c>
       <c r="H242" s="4" t="s">
         <v>41</v>
@@ -13015,25 +13170,25 @@
     </row>
     <row r="243" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="D243" s="2" t="s">
+      <c r="F243" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="E243" s="2" t="s">
+      <c r="G243" s="2" t="s">
         <v>1354</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>1356</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>41</v>
@@ -13041,25 +13196,25 @@
     </row>
     <row r="244" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D244" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C244" s="2" t="s">
+      <c r="E244" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="F244" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="E244" s="2" t="s">
+      <c r="G244" s="2" t="s">
         <v>1360</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G244" s="2" t="s">
-        <v>1362</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>41</v>
@@ -13067,25 +13222,25 @@
     </row>
     <row r="245" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C245" s="2" t="s">
+      <c r="E245" s="2" t="s">
         <v>1364</v>
       </c>
-      <c r="D245" s="2" t="s">
+      <c r="F245" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="E245" s="2" t="s">
+      <c r="G245" s="2" t="s">
         <v>1366</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G245" s="2" t="s">
-        <v>1368</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>41</v>
@@ -13093,25 +13248,25 @@
     </row>
     <row r="246" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C246" s="2" t="s">
+      <c r="E246" s="2" t="s">
         <v>1370</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="F246" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="E246" s="2" t="s">
+      <c r="G246" s="2" t="s">
         <v>1372</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G246" s="2" t="s">
-        <v>1374</v>
       </c>
       <c r="H246" s="4" t="s">
         <v>41</v>
@@ -13119,25 +13274,25 @@
     </row>
     <row r="247" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="D247" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="E247" s="2" t="s">
+      <c r="G247" s="2" t="s">
         <v>1378</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G247" s="2" t="s">
-        <v>1380</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>41</v>
@@ -13145,25 +13300,25 @@
     </row>
     <row r="248" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C248" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="D248" s="2" t="s">
+      <c r="G248" s="2" t="s">
         <v>1383</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>1384</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G248" s="2" t="s">
-        <v>1386</v>
       </c>
       <c r="H248" s="4" t="s">
         <v>41</v>
@@ -13171,25 +13326,25 @@
     </row>
     <row r="249" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="G249" s="2" t="s">
         <v>1389</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>1391</v>
-      </c>
-      <c r="G249" s="2" t="s">
-        <v>1392</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>41</v>
@@ -13197,25 +13352,25 @@
     </row>
     <row r="250" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="D250" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>1394</v>
       </c>
-      <c r="E250" s="2" t="s">
+      <c r="G250" s="2" t="s">
         <v>1395</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G250" s="2" t="s">
-        <v>1397</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>41</v>
@@ -13223,25 +13378,25 @@
     </row>
     <row r="251" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="F251" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="E251" s="2" t="s">
+      <c r="G251" s="2" t="s">
         <v>1401</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>1402</v>
-      </c>
-      <c r="G251" s="2" t="s">
-        <v>1403</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>41</v>
@@ -13249,25 +13404,25 @@
     </row>
     <row r="252" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="F252" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="E252" s="2" t="s">
+      <c r="G252" s="2" t="s">
         <v>1407</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>1408</v>
-      </c>
-      <c r="G252" s="2" t="s">
-        <v>1409</v>
       </c>
       <c r="H252" s="4" t="s">
         <v>41</v>
@@ -13275,25 +13430,25 @@
     </row>
     <row r="253" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>1411</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="F253" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="E253" s="2" t="s">
+      <c r="G253" s="2" t="s">
         <v>1413</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="G253" s="2" t="s">
-        <v>1415</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>41</v>
@@ -13301,25 +13456,25 @@
     </row>
     <row r="254" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D254" s="2" t="s">
+      <c r="F254" s="2" t="s">
         <v>1418</v>
       </c>
-      <c r="E254" s="2" t="s">
+      <c r="G254" s="2" t="s">
         <v>1419</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G254" s="2" t="s">
-        <v>1421</v>
       </c>
       <c r="H254" s="4" t="s">
         <v>41</v>
@@ -13327,25 +13482,25 @@
     </row>
     <row r="255" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C255" s="2" t="s">
+      <c r="F255" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="D255" s="2" t="s">
+      <c r="G255" s="2" t="s">
         <v>1424</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>1426</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>1427</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>41</v>
@@ -13353,32 +13508,162 @@
     </row>
     <row r="256" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C256" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="D256" s="2" t="s">
+      <c r="G256" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="E256" s="2" t="s">
+      <c r="H256" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
         <v>1431</v>
       </c>
-      <c r="F256" s="2" t="s">
+      <c r="B257" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="G256" s="2" t="s">
+      <c r="D257" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="H256" s="4" t="s">
+      <c r="E257" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H261" s="4" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H256"/>
+  <autoFilter ref="A1:H261"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -13386,7 +13671,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -13396,43 +13681,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1434</v>
+        <v>1461</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1435</v>
+        <v>1462</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1436</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="C2" s="11">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1439</v>
+        <v>1466</v>
       </c>
       <c r="C3" s="11">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1440</v>
+        <v>1467</v>
       </c>
       <c r="C4" s="11">
         <v>11</v>
@@ -13440,7 +13725,7 @@
     </row>
     <row r="6" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>184</v>
@@ -13451,7 +13736,7 @@
     </row>
     <row r="7" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>177</v>
@@ -13462,29 +13747,29 @@
     </row>
     <row r="8" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>223</v>
+        <v>58</v>
       </c>
       <c r="C8" s="12">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="C9" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>75</v>
@@ -13495,18 +13780,18 @@
     </row>
     <row r="11" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="12">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>190</v>
@@ -13517,10 +13802,10 @@
     </row>
     <row r="14" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="C14" s="12">
         <v>44</v>
@@ -13528,10 +13813,10 @@
     </row>
     <row r="15" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="C15" s="12">
         <v>31</v>
@@ -13539,21 +13824,21 @@
     </row>
     <row r="16" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1445</v>
+        <v>1472</v>
       </c>
       <c r="C16" s="12">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="C17" s="12">
         <v>24</v>
@@ -13561,10 +13846,10 @@
     </row>
     <row r="18" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="C18" s="12">
         <v>22</v>
@@ -13572,10 +13857,10 @@
     </row>
     <row r="19" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="C19" s="12">
         <v>20</v>
@@ -13583,32 +13868,32 @@
     </row>
     <row r="20" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="C20" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="C21" s="12">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="C22" s="12">
         <v>15</v>
@@ -13616,10 +13901,10 @@
     </row>
     <row r="23" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1452</v>
+        <v>1479</v>
       </c>
       <c r="C23" s="12">
         <v>10</v>
@@ -13627,10 +13912,10 @@
     </row>
     <row r="24" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="C24" s="12">
         <v>9</v>
@@ -13638,10 +13923,10 @@
     </row>
     <row r="25" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="C25" s="12">
         <v>9</v>
@@ -13649,10 +13934,10 @@
     </row>
     <row r="26" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1455</v>
+        <v>1482</v>
       </c>
       <c r="C26" s="12">
         <v>5</v>
@@ -13660,10 +13945,10 @@
     </row>
     <row r="27" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1456</v>
+        <v>1483</v>
       </c>
       <c r="C27" s="12">
         <v>5</v>
@@ -13671,10 +13956,10 @@
     </row>
     <row r="28" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="C28" s="12">
         <v>3</v>
@@ -13682,10 +13967,10 @@
     </row>
     <row r="29" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="C29" s="12">
         <v>2</v>
@@ -13693,7 +13978,7 @@
     </row>
     <row r="31" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>10</v>
@@ -13704,7 +13989,7 @@
     </row>
     <row r="32" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>96</v>
@@ -13715,7 +14000,7 @@
     </row>
     <row r="33" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>314</v>
@@ -13726,7 +14011,7 @@
     </row>
     <row r="34" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>612</v>
@@ -13737,7 +14022,7 @@
     </row>
     <row r="35" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>59</v>
@@ -13748,7 +14033,7 @@
     </row>
     <row r="36" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>139</v>
@@ -13759,7 +14044,7 @@
     </row>
     <row r="37" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>432</v>
@@ -13770,7 +14055,7 @@
     </row>
     <row r="38" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>543</v>
@@ -13781,7 +14066,7 @@
     </row>
     <row r="39" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>591</v>
@@ -13792,7 +14077,7 @@
     </row>
     <row r="40" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>637</v>
@@ -13803,7 +14088,7 @@
     </row>
     <row r="41" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>731</v>
@@ -13814,10 +14099,10 @@
     </row>
     <row r="42" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="C42" s="12">
         <v>4</v>
@@ -13825,7 +14110,7 @@
     </row>
     <row r="43" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>43</v>
@@ -13836,7 +14121,7 @@
     </row>
     <row r="44" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>81</v>
@@ -13847,7 +14132,7 @@
     </row>
     <row r="45" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>178</v>
@@ -13858,7 +14143,7 @@
     </row>
     <row r="46" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>196</v>
@@ -13869,7 +14154,7 @@
     </row>
     <row r="47" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>241</v>
@@ -13880,7 +14165,7 @@
     </row>
     <row r="48" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>422</v>
@@ -13891,7 +14176,7 @@
     </row>
     <row r="49" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>463</v>
@@ -13902,7 +14187,7 @@
     </row>
     <row r="50" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>503</v>
@@ -13913,7 +14198,7 @@
     </row>
     <row r="51" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>575</v>
@@ -13924,7 +14209,7 @@
     </row>
     <row r="52" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>663</v>
@@ -13935,7 +14220,7 @@
     </row>
     <row r="53" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>690</v>
@@ -13946,7 +14231,7 @@
     </row>
     <row r="54" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>716</v>
@@ -13957,7 +14242,7 @@
     </row>
     <row r="55" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>877</v>
@@ -13968,10 +14253,10 @@
     </row>
     <row r="56" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>1307</v>
+        <v>1115</v>
       </c>
       <c r="C56" s="12">
         <v>3</v>
@@ -13979,21 +14264,21 @@
     </row>
     <row r="57" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>128</v>
+        <v>1334</v>
       </c>
       <c r="C57" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="C58" s="12">
         <v>2</v>
@@ -14001,10 +14286,10 @@
     </row>
     <row r="59" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="C59" s="12">
         <v>2</v>
@@ -14012,10 +14297,10 @@
     </row>
     <row r="60" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C60" s="12">
         <v>2</v>
@@ -14023,10 +14308,10 @@
     </row>
     <row r="61" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
       <c r="C61" s="12">
         <v>2</v>
@@ -14034,10 +14319,10 @@
     </row>
     <row r="62" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C62" s="12">
         <v>2</v>
@@ -14045,10 +14330,10 @@
     </row>
     <row r="63" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="C63" s="12">
         <v>2</v>
@@ -14056,10 +14341,10 @@
     </row>
     <row r="64" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C64" s="12">
         <v>2</v>
@@ -14067,10 +14352,10 @@
     </row>
     <row r="65" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="C65" s="12">
         <v>2</v>
@@ -14078,10 +14363,10 @@
     </row>
     <row r="66" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>564</v>
+        <v>411</v>
       </c>
       <c r="C66" s="12">
         <v>2</v>
@@ -14089,10 +14374,10 @@
     </row>
     <row r="67" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>679</v>
+        <v>564</v>
       </c>
       <c r="C67" s="12">
         <v>2</v>
@@ -14100,10 +14385,10 @@
     </row>
     <row r="68" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>706</v>
+        <v>679</v>
       </c>
       <c r="C68" s="12">
         <v>2</v>
@@ -14111,10 +14396,10 @@
     </row>
     <row r="69" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="C69" s="12">
         <v>2</v>
@@ -14122,10 +14407,10 @@
     </row>
     <row r="70" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>775</v>
+        <v>742</v>
       </c>
       <c r="C70" s="12">
         <v>2</v>
@@ -14133,10 +14418,10 @@
     </row>
     <row r="71" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>821</v>
+        <v>775</v>
       </c>
       <c r="C71" s="12">
         <v>2</v>
@@ -14144,10 +14429,10 @@
     </row>
     <row r="72" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="C72" s="12">
         <v>2</v>
@@ -14155,10 +14440,10 @@
     </row>
     <row r="73" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="C73" s="12">
         <v>2</v>
@@ -14166,10 +14451,10 @@
     </row>
     <row r="74" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="C74" s="12">
         <v>2</v>
@@ -14177,10 +14462,10 @@
     </row>
     <row r="75" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="C75" s="12">
         <v>2</v>
@@ -14188,10 +14473,10 @@
     </row>
     <row r="76" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>916</v>
+        <v>866</v>
       </c>
       <c r="C76" s="12">
         <v>2</v>
@@ -14199,10 +14484,10 @@
     </row>
     <row r="77" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>927</v>
+        <v>910</v>
       </c>
       <c r="C77" s="12">
         <v>2</v>
@@ -14210,10 +14495,10 @@
     </row>
     <row r="78" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>944</v>
+        <v>927</v>
       </c>
       <c r="C78" s="12">
         <v>2</v>
@@ -14221,10 +14506,10 @@
     </row>
     <row r="79" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>967</v>
+        <v>938</v>
       </c>
       <c r="C79" s="12">
         <v>2</v>
@@ -14232,10 +14517,10 @@
     </row>
     <row r="80" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>990</v>
+        <v>955</v>
       </c>
       <c r="C80" s="12">
         <v>2</v>
@@ -14243,10 +14528,10 @@
     </row>
     <row r="81" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>1040</v>
+        <v>978</v>
       </c>
       <c r="C81" s="12">
         <v>2</v>
@@ -14254,10 +14539,10 @@
     </row>
     <row r="82" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>1200</v>
+        <v>1001</v>
       </c>
       <c r="C82" s="12">
         <v>2</v>
@@ -14265,10 +14550,10 @@
     </row>
     <row r="83" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>1347</v>
+        <v>1051</v>
       </c>
       <c r="C83" s="12">
         <v>2</v>
@@ -14276,10 +14561,10 @@
     </row>
     <row r="84" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>1388</v>
+        <v>1227</v>
       </c>
       <c r="C84" s="12">
         <v>2</v>
@@ -14287,32 +14572,32 @@
     </row>
     <row r="85" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>122</v>
+        <v>1374</v>
       </c>
       <c r="C85" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>171</v>
+        <v>1415</v>
       </c>
       <c r="C86" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="C87" s="12">
         <v>1</v>
@@ -14320,10 +14605,10 @@
     </row>
     <row r="88" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="C88" s="12">
         <v>1</v>
@@ -14331,10 +14616,10 @@
     </row>
     <row r="89" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C89" s="12">
         <v>1</v>
@@ -14342,10 +14627,10 @@
     </row>
     <row r="90" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C90" s="12">
         <v>1</v>
@@ -14353,10 +14638,10 @@
     </row>
     <row r="91" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C91" s="12">
         <v>1</v>
@@ -14364,10 +14649,10 @@
     </row>
     <row r="92" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C92" s="12">
         <v>1</v>
@@ -14375,10 +14660,10 @@
     </row>
     <row r="93" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C93" s="12">
         <v>1</v>
@@ -14386,10 +14671,10 @@
     </row>
     <row r="94" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>337</v>
+        <v>281</v>
       </c>
       <c r="C94" s="12">
         <v>1</v>
@@ -14397,10 +14682,10 @@
     </row>
     <row r="95" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="C95" s="12">
         <v>1</v>
@@ -14408,10 +14693,10 @@
     </row>
     <row r="96" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>370</v>
+        <v>337</v>
       </c>
       <c r="C96" s="12">
         <v>1</v>
@@ -14419,10 +14704,10 @@
     </row>
     <row r="97" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="C97" s="12">
         <v>1</v>
@@ -14430,10 +14715,10 @@
     </row>
     <row r="98" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C98" s="12">
         <v>1</v>
@@ -14441,10 +14726,10 @@
     </row>
     <row r="99" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C99" s="12">
         <v>1</v>
@@ -14452,10 +14737,10 @@
     </row>
     <row r="100" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C100" s="12">
         <v>1</v>
@@ -14463,10 +14748,10 @@
     </row>
     <row r="101" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C101" s="12">
         <v>1</v>
@@ -14474,10 +14759,10 @@
     </row>
     <row r="102" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C102" s="12">
         <v>1</v>
@@ -14485,10 +14770,10 @@
     </row>
     <row r="103" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>458</v>
+        <v>399</v>
       </c>
       <c r="C103" s="12">
         <v>1</v>
@@ -14496,10 +14781,10 @@
     </row>
     <row r="104" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>479</v>
+        <v>405</v>
       </c>
       <c r="C104" s="12">
         <v>1</v>
@@ -14507,10 +14792,10 @@
     </row>
     <row r="105" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="C105" s="12">
         <v>1</v>
@@ -14518,10 +14803,10 @@
     </row>
     <row r="106" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C106" s="12">
         <v>1</v>
@@ -14529,10 +14814,10 @@
     </row>
     <row r="107" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C107" s="12">
         <v>1</v>
@@ -14540,10 +14825,10 @@
     </row>
     <row r="108" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="C108" s="12">
         <v>1</v>
@@ -14551,10 +14836,10 @@
     </row>
     <row r="109" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="C109" s="12">
         <v>1</v>
@@ -14562,10 +14847,10 @@
     </row>
     <row r="110" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C110" s="12">
         <v>1</v>
@@ -14573,10 +14858,10 @@
     </row>
     <row r="111" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C111" s="12">
         <v>1</v>
@@ -14584,10 +14869,10 @@
     </row>
     <row r="112" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>657</v>
+        <v>531</v>
       </c>
       <c r="C112" s="12">
         <v>1</v>
@@ -14595,10 +14880,10 @@
     </row>
     <row r="113" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>763</v>
+        <v>537</v>
       </c>
       <c r="C113" s="12">
         <v>1</v>
@@ -14606,10 +14891,10 @@
     </row>
     <row r="114" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>769</v>
+        <v>657</v>
       </c>
       <c r="C114" s="12">
         <v>1</v>
@@ -14617,10 +14902,10 @@
     </row>
     <row r="115" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="C115" s="12">
         <v>1</v>
@@ -14628,10 +14913,10 @@
     </row>
     <row r="116" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="C116" s="12">
         <v>1</v>
@@ -14639,10 +14924,10 @@
     </row>
     <row r="117" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C117" s="12">
         <v>1</v>
@@ -14650,10 +14935,10 @@
     </row>
     <row r="118" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="C118" s="12">
         <v>1</v>
@@ -14661,10 +14946,10 @@
     </row>
     <row r="119" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="C119" s="12">
         <v>1</v>
@@ -14672,10 +14957,10 @@
     </row>
     <row r="120" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="C120" s="12">
         <v>1</v>
@@ -14683,10 +14968,10 @@
     </row>
     <row r="121" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>860</v>
+        <v>809</v>
       </c>
       <c r="C121" s="12">
         <v>1</v>
@@ -14694,10 +14979,10 @@
     </row>
     <row r="122" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>893</v>
+        <v>815</v>
       </c>
       <c r="C122" s="12">
         <v>1</v>
@@ -14705,10 +14990,10 @@
     </row>
     <row r="123" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>904</v>
+        <v>860</v>
       </c>
       <c r="C123" s="12">
         <v>1</v>
@@ -14716,10 +15001,10 @@
     </row>
     <row r="124" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="C124" s="12">
         <v>1</v>
@@ -14727,10 +15012,10 @@
     </row>
     <row r="125" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
       <c r="C125" s="12">
         <v>1</v>
@@ -14738,10 +15023,10 @@
     </row>
     <row r="126" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>955</v>
+        <v>921</v>
       </c>
       <c r="C126" s="12">
         <v>1</v>
@@ -14749,10 +15034,10 @@
     </row>
     <row r="127" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="C127" s="12">
         <v>1</v>
@@ -14760,10 +15045,10 @@
     </row>
     <row r="128" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C128" s="12">
         <v>1</v>
@@ -14771,10 +15056,10 @@
     </row>
     <row r="129" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="C129" s="12">
         <v>1</v>
@@ -14782,10 +15067,10 @@
     </row>
     <row r="130" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="C130" s="12">
         <v>1</v>
@@ -14793,10 +15078,10 @@
     </row>
     <row r="131" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="C131" s="12">
         <v>1</v>
@@ -14804,10 +15089,10 @@
     </row>
     <row r="132" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C132" s="12">
         <v>1</v>
@@ -14815,10 +15100,10 @@
     </row>
     <row r="133" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>1051</v>
+        <v>1018</v>
       </c>
       <c r="C133" s="12">
         <v>1</v>
@@ -14826,10 +15111,10 @@
     </row>
     <row r="134" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="C134" s="12">
         <v>1</v>
@@ -14837,10 +15122,10 @@
     </row>
     <row r="135" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C135" s="12">
         <v>1</v>
@@ -14848,10 +15133,10 @@
     </row>
     <row r="136" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C136" s="12">
         <v>1</v>
@@ -14859,10 +15144,10 @@
     </row>
     <row r="137" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C137" s="12">
         <v>1</v>
@@ -14870,10 +15155,10 @@
     </row>
     <row r="138" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C138" s="12">
         <v>1</v>
@@ -14881,10 +15166,10 @@
     </row>
     <row r="139" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C139" s="12">
         <v>1</v>
@@ -14892,10 +15177,10 @@
     </row>
     <row r="140" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C140" s="12">
         <v>1</v>
@@ -14903,7 +15188,7 @@
     </row>
     <row r="141" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B141" s="12" t="s">
         <v>1098</v>
@@ -14914,7 +15199,7 @@
     </row>
     <row r="142" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>1104</v>
@@ -14925,10 +15210,10 @@
     </row>
     <row r="143" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C143" s="12">
         <v>1</v>
@@ -14936,10 +15221,10 @@
     </row>
     <row r="144" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="C144" s="12">
         <v>1</v>
@@ -14947,10 +15232,10 @@
     </row>
     <row r="145" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="C145" s="12">
         <v>1</v>
@@ -14958,10 +15243,10 @@
     </row>
     <row r="146" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="C146" s="12">
         <v>1</v>
@@ -14969,10 +15254,10 @@
     </row>
     <row r="147" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
       <c r="C147" s="12">
         <v>1</v>
@@ -14980,10 +15265,10 @@
     </row>
     <row r="148" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>1140</v>
+        <v>1155</v>
       </c>
       <c r="C148" s="12">
         <v>1</v>
@@ -14991,10 +15276,10 @@
     </row>
     <row r="149" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>1146</v>
+        <v>1161</v>
       </c>
       <c r="C149" s="12">
         <v>1</v>
@@ -15002,10 +15287,10 @@
     </row>
     <row r="150" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="C150" s="12">
         <v>1</v>
@@ -15013,10 +15298,10 @@
     </row>
     <row r="151" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>1158</v>
+        <v>1173</v>
       </c>
       <c r="C151" s="12">
         <v>1</v>
@@ -15024,10 +15309,10 @@
     </row>
     <row r="152" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>1164</v>
+        <v>1179</v>
       </c>
       <c r="C152" s="12">
         <v>1</v>
@@ -15035,10 +15320,10 @@
     </row>
     <row r="153" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>1170</v>
+        <v>1185</v>
       </c>
       <c r="C153" s="12">
         <v>1</v>
@@ -15046,10 +15331,10 @@
     </row>
     <row r="154" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>1176</v>
+        <v>1191</v>
       </c>
       <c r="C154" s="12">
         <v>1</v>
@@ -15057,10 +15342,10 @@
     </row>
     <row r="155" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>1182</v>
+        <v>1197</v>
       </c>
       <c r="C155" s="12">
         <v>1</v>
@@ -15068,10 +15353,10 @@
     </row>
     <row r="156" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>1188</v>
+        <v>1203</v>
       </c>
       <c r="C156" s="12">
         <v>1</v>
@@ -15079,10 +15364,10 @@
     </row>
     <row r="157" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>1194</v>
+        <v>1209</v>
       </c>
       <c r="C157" s="12">
         <v>1</v>
@@ -15090,10 +15375,10 @@
     </row>
     <row r="158" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="C158" s="12">
         <v>1</v>
@@ -15101,10 +15386,10 @@
     </row>
     <row r="159" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="C159" s="12">
         <v>1</v>
@@ -15112,10 +15397,10 @@
     </row>
     <row r="160" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>1223</v>
+        <v>1238</v>
       </c>
       <c r="C160" s="12">
         <v>1</v>
@@ -15123,10 +15408,10 @@
     </row>
     <row r="161" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>1229</v>
+        <v>1244</v>
       </c>
       <c r="C161" s="12">
         <v>1</v>
@@ -15134,10 +15419,10 @@
     </row>
     <row r="162" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>1235</v>
+        <v>1250</v>
       </c>
       <c r="C162" s="12">
         <v>1</v>
@@ -15145,10 +15430,10 @@
     </row>
     <row r="163" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>1241</v>
+        <v>1256</v>
       </c>
       <c r="C163" s="12">
         <v>1</v>
@@ -15156,10 +15441,10 @@
     </row>
     <row r="164" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1247</v>
+        <v>1262</v>
       </c>
       <c r="C164" s="12">
         <v>1</v>
@@ -15167,10 +15452,10 @@
     </row>
     <row r="165" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>1253</v>
+        <v>1268</v>
       </c>
       <c r="C165" s="12">
         <v>1</v>
@@ -15178,10 +15463,10 @@
     </row>
     <row r="166" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>1259</v>
+        <v>1274</v>
       </c>
       <c r="C166" s="12">
         <v>1</v>
@@ -15189,10 +15474,10 @@
     </row>
     <row r="167" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>1265</v>
+        <v>1280</v>
       </c>
       <c r="C167" s="12">
         <v>1</v>
@@ -15200,10 +15485,10 @@
     </row>
     <row r="168" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>1271</v>
+        <v>1286</v>
       </c>
       <c r="C168" s="12">
         <v>1</v>
@@ -15211,10 +15496,10 @@
     </row>
     <row r="169" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>1277</v>
+        <v>1292</v>
       </c>
       <c r="C169" s="12">
         <v>1</v>
@@ -15222,10 +15507,10 @@
     </row>
     <row r="170" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>1283</v>
+        <v>1298</v>
       </c>
       <c r="C170" s="12">
         <v>1</v>
@@ -15233,10 +15518,10 @@
     </row>
     <row r="171" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>1289</v>
+        <v>1304</v>
       </c>
       <c r="C171" s="12">
         <v>1</v>
@@ -15244,10 +15529,10 @@
     </row>
     <row r="172" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>1295</v>
+        <v>1310</v>
       </c>
       <c r="C172" s="12">
         <v>1</v>
@@ -15255,10 +15540,10 @@
     </row>
     <row r="173" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>1301</v>
+        <v>1316</v>
       </c>
       <c r="C173" s="12">
         <v>1</v>
@@ -15266,10 +15551,10 @@
     </row>
     <row r="174" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C174" s="12">
         <v>1</v>
@@ -15277,10 +15562,10 @@
     </row>
     <row r="175" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C175" s="12">
         <v>1</v>
@@ -15288,10 +15573,10 @@
     </row>
     <row r="176" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>1335</v>
+        <v>1350</v>
       </c>
       <c r="C176" s="12">
         <v>1</v>
@@ -15299,10 +15584,10 @@
     </row>
     <row r="177" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>1341</v>
+        <v>1356</v>
       </c>
       <c r="C177" s="12">
         <v>1</v>
@@ -15310,10 +15595,10 @@
     </row>
     <row r="178" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="C178" s="12">
         <v>1</v>
@@ -15321,10 +15606,10 @@
     </row>
     <row r="179" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="C179" s="12">
         <v>1</v>
@@ -15332,10 +15617,10 @@
     </row>
     <row r="180" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1370</v>
+        <v>1385</v>
       </c>
       <c r="C180" s="12">
         <v>1</v>
@@ -15343,10 +15628,10 @@
     </row>
     <row r="181" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>1376</v>
+        <v>1391</v>
       </c>
       <c r="C181" s="12">
         <v>1</v>
@@ -15354,10 +15639,10 @@
     </row>
     <row r="182" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>1382</v>
+        <v>1397</v>
       </c>
       <c r="C182" s="12">
         <v>1</v>
@@ -15365,10 +15650,10 @@
     </row>
     <row r="183" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C183" s="12">
         <v>1</v>
@@ -15376,10 +15661,10 @@
     </row>
     <row r="184" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="C184" s="12">
         <v>1</v>
@@ -15387,10 +15672,10 @@
     </row>
     <row r="185" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>1411</v>
+        <v>1426</v>
       </c>
       <c r="C185" s="12">
         <v>1</v>
@@ -15398,10 +15683,10 @@
     </row>
     <row r="186" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>1417</v>
+        <v>1432</v>
       </c>
       <c r="C186" s="12">
         <v>1</v>
@@ -15409,10 +15694,10 @@
     </row>
     <row r="187" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>1423</v>
+        <v>1438</v>
       </c>
       <c r="C187" s="12">
         <v>1</v>
@@ -15420,12 +15705,34 @@
     </row>
     <row r="188" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>1429</v>
+        <v>1444</v>
       </c>
       <c r="C188" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C189" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C190" s="12">
         <v>1</v>
       </c>
     </row>
@@ -15454,10 +15761,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1461</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15465,13 +15772,13 @@
         <v>75</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1463</v>
+        <v>1490</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1464</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15479,13 +15786,13 @@
         <v>75</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1465</v>
+        <v>1492</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15493,13 +15800,13 @@
         <v>75</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1468</v>
+        <v>1495</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1469</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15507,13 +15814,13 @@
         <v>75</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1471</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15521,13 +15828,13 @@
         <v>190</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1472</v>
+        <v>1499</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1473</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15535,13 +15842,13 @@
         <v>190</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1474</v>
+        <v>1501</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1476</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15549,13 +15856,13 @@
         <v>190</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1477</v>
+        <v>1504</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1478</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15563,13 +15870,13 @@
         <v>177</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1479</v>
+        <v>1506</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1480</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15577,13 +15884,13 @@
         <v>177</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1481</v>
+        <v>1508</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1482</v>
+        <v>1509</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1483</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15591,13 +15898,13 @@
         <v>177</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1484</v>
+        <v>1511</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1485</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15605,13 +15912,13 @@
         <v>177</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1487</v>
+        <v>1514</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>1488</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15619,13 +15926,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1489</v>
+        <v>1516</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1490</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15633,13 +15940,13 @@
         <v>184</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1491</v>
+        <v>1518</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1492</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15647,13 +15954,13 @@
         <v>184</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1493</v>
+        <v>1520</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1494</v>
+        <v>1521</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>1495</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15661,13 +15968,13 @@
         <v>184</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1496</v>
+        <v>1523</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1497</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15675,13 +15982,13 @@
         <v>58</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1498</v>
+        <v>1525</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1500</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15689,13 +15996,13 @@
         <v>58</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1501</v>
+        <v>1528</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1502</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15703,55 +16010,55 @@
         <v>58</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1505</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>1506</v>
+        <v>1533</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>1506</v>
+        <v>1533</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1511</v>
+        <v>1538</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
     </row>
   </sheetData>
@@ -15777,424 +16084,424 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1513</v>
+        <v>1540</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1514</v>
+        <v>1541</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1515</v>
+        <v>1542</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1516</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1519</v>
+        <v>1546</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1520</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1521</v>
+        <v>1548</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1523</v>
+        <v>1550</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1524</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1525</v>
+        <v>1552</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1526</v>
+        <v>1553</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1527</v>
+        <v>1554</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1528</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1530</v>
+        <v>1557</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1532</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1533</v>
+        <v>1560</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1534</v>
+        <v>1561</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>149</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1535</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>1536</v>
+        <v>1563</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1537</v>
+        <v>1564</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1539</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>1536</v>
+        <v>1563</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1540</v>
+        <v>1567</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1541</v>
+        <v>1568</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1542</v>
+        <v>1569</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>1543</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1544</v>
+        <v>1571</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1545</v>
+        <v>1572</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>1546</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1547</v>
+        <v>1574</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>342</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1549</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>1445</v>
+        <v>1473</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1550</v>
+        <v>1577</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1551</v>
+        <v>1578</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>1552</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>1445</v>
+        <v>1473</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1553</v>
+        <v>1580</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>1554</v>
+        <v>1581</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>1555</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>1445</v>
+        <v>1473</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1556</v>
+        <v>1583</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1557</v>
+        <v>1584</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>1558</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1559</v>
+        <v>1586</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1560</v>
+        <v>1587</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>1561</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1562</v>
+        <v>1589</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>673</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1563</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1564</v>
+        <v>1591</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1566</v>
+        <v>1593</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1567</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1568</v>
+        <v>1595</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1569</v>
+        <v>1596</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1570</v>
+        <v>1597</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>1571</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>695</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1573</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1574</v>
+        <v>1601</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>1575</v>
+        <v>1602</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>1576</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>1577</v>
+        <v>1604</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>678</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1578</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1579</v>
+        <v>1606</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1580</v>
+        <v>1607</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1581</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1582</v>
+        <v>1609</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1583</v>
+        <v>1610</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>1584</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1585</v>
+        <v>1612</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>1586</v>
+        <v>1613</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>1587</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1588</v>
+        <v>1615</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1589</v>
+        <v>1616</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>1590</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>1591</v>
+        <v>1618</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1592</v>
+        <v>1619</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1593</v>
+        <v>1620</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1594</v>
+        <v>1621</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1595</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16202,16 +16509,16 @@
         <v>58</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1596</v>
+        <v>1623</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1597</v>
+        <v>1624</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1598</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16219,118 +16526,118 @@
         <v>58</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1599</v>
+        <v>1626</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>1045</v>
+        <v>1056</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1600</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1601</v>
+        <v>1628</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>1602</v>
+        <v>1629</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1603</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>1449</v>
+        <v>1477</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1604</v>
+        <v>1631</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1605</v>
+        <v>1632</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>1606</v>
+        <v>1633</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1607</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>1608</v>
+        <v>1635</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1609</v>
+        <v>1636</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>1610</v>
+        <v>1637</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>1611</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1612</v>
+        <v>1639</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1613</v>
+        <v>1640</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1614</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>1615</v>
+        <v>1642</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>1616</v>
+        <v>1643</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1617</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1618</v>
+        <v>1645</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>1619</v>
+        <v>1646</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1620</v>
+        <v>1647</v>
       </c>
     </row>
   </sheetData>
@@ -16354,12 +16661,12 @@
     </row>
     <row r="2" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>1621</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>1622</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16369,17 +16676,17 @@
     </row>
     <row r="5" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>1623</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>1624</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>1625</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16389,22 +16696,22 @@
     </row>
     <row r="9" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1626</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>1627</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>1628</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="12" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>1629</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16414,17 +16721,17 @@
     </row>
     <row r="14" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1630</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="15" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>1631</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>1632</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16434,17 +16741,17 @@
     </row>
     <row r="18" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1633</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>1634</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>1635</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16454,32 +16761,32 @@
     </row>
     <row r="22" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>1636</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>1637</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1638</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>1639</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>1640</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>1641</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16489,22 +16796,22 @@
     </row>
     <row r="29" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>1642</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>1643</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>1644</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>1645</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="33" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16514,12 +16821,12 @@
     </row>
     <row r="34" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>1646</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="35" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>1647</v>
+        <v>1674</v>
       </c>
     </row>
   </sheetData>
@@ -16530,7 +16837,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16543,10 +16850,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1648</v>
+        <v>1675</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1649</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16557,7 +16864,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1650</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16568,7 +16875,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>1651</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16579,7 +16886,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1652</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16590,7 +16897,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1653</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16601,7 +16908,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1654</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16612,7 +16919,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1655</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16623,7 +16930,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1656</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16634,7 +16941,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1657</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16645,7 +16952,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1658</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16656,7 +16963,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1659</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16667,7 +16974,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1660</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16678,7 +16985,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1661</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16689,7 +16996,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1662</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16700,7 +17007,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1663</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16711,7 +17018,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1664</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16722,7 +17029,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1665</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16733,7 +17040,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1666</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16744,7 +17051,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>1667</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16755,7 +17062,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1668</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16766,7 +17073,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>1669</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16777,7 +17084,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1670</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16788,29 +17095,205 @@
         <v>15</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>1671</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>1673</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>1674</v>
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>909</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
+        <v>915</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>808</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>1717</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1742">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -2057,6 +2057,46 @@
     <t>The appointment is not found and no Clinic B information is rendered anywhere on the page, including in the page title.</t>
   </si>
   <si>
+    <t>TC-APPT-025</t>
+  </si>
+  <si>
+    <t>A rejected discount leaves the patient charged in full</t>
+  </si>
+  <si>
+    <t>A clinic configured to require discount approval, and an appointment carrying a discount awaiting a decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Confirm the appointment's discount is pending and the bill shows the full amount.
+2. Open "Discount approvals" as a user who may decide.
+3. REJECT the discount, adding a reason.
+4. Return to the appointment and read the bill.
+5. Confirm the discount is still not applied.
+6. Open the Discounts report and confirm the rejection is visible there.</t>
+  </si>
+  <si>
+    <t>After rejection the bill remains at the full amount — the patient is charged in full. A rejected discount must never quietly apply; charging less than the clinic authorised is the failure this workflow exists to prevent.</t>
+  </si>
+  <si>
+    <t>TC-APPT-026</t>
+  </si>
+  <si>
+    <t>With approval switched off a discount applies immediately</t>
+  </si>
+  <si>
+    <t>A clinic whose discount-approval requirement is OFF, and whose doctors do not individually require approval.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Confirm the clinic does not require discount approval.
+2. Book an appointment with a doctor who has a consultation fee.
+3. Apply a flat discount.
+4. Save and open the bill.
+5. Confirm the discount has already been deducted.
+6. Open "Discount approvals" and confirm nothing is waiting there for this appointment.</t>
+  </si>
+  <si>
+    <t>The discount applies at once with no approval step and nothing appears in the approvals queue. A clinic that never turned the workflow on must behave exactly as it did before the feature existed — the gate must not become a tax on everyone.</t>
+  </si>
+  <si>
     <t>TC-AI-001</t>
   </si>
   <si>
@@ -3490,6 +3530,29 @@
   </si>
   <si>
     <t>The net is 720. The line is discounted first to 800, that becomes the subtotal, and the 10 percent appointment discount applies to the SUBTOTAL — never to the gross. A net of 700 would mean the order is reversed, which would understate every bill carrying both kinds of discount.</t>
+  </si>
+  <si>
+    <t>TC-BILL-027</t>
+  </si>
+  <si>
+    <t>Billing — Numbering</t>
+  </si>
+  <si>
+    <t>Receipt and invoice numbers come from separate counters</t>
+  </si>
+  <si>
+    <t>A completed appointment with a billable total. Clinic has the sales feature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the appointment and collect a payment.
+2. Note the receipt number that appears automatically.
+3. Click the control that issues an invoice number.
+4. Note the invoice number.
+5. Compare the two numbers and their prefixes.
+6. Repeat on a second appointment and confirm each series advances independently of the other.</t>
+  </si>
+  <si>
+    <t>The visit carries a receipt number and an invoice number drawn from two SEPARATE sequences with different prefixes. They must never share a counter: a bill is what is owed and a receipt is proof of payment, and an auditor reading either series needs it to be complete on its own.</t>
   </si>
   <si>
     <t>TC-CLIN-001</t>
@@ -6356,10 +6419,34 @@
     <t>Rs 15,000 covers 3 months at a flat Rs 5,000 and 3 on the re-priced clinic — the early months are charged at what they actually cost, not at today's figure</t>
   </si>
   <si>
+    <t>before any collection the visit has NO receipt number; after Rs 1,000 was collected it has one (RCP-2026-0000001) — the receipt is proof of payment, so it cannot predate one</t>
+  </si>
+  <si>
+    <t>receipt number 2 allocated on the first payment and UNCHANGED after a second (2); both payments (2) are listed against the one receipt — a visit has one receipt, not one per payment</t>
+  </si>
+  <si>
+    <t>a paid visit had NO invoice until one was requested, then got INV-2026-0000001. The receipt number appears automatically on payment; the invoice number only when someone asks — which is why "where is the invoice number" is usually "nobody pressed the button"</t>
+  </si>
+  <si>
+    <t>the same visit carries receipt #4 and invoice #2 from two SEPARATE counters — a bill is what is owed, a receipt is proof of payment, and they must never share a sequence</t>
+  </si>
+  <si>
+    <t>a Rs 1,000 discount on a Rs 3,000 visit is HELD: status "pending", 1 approval row(s), and the bill still reads Rs 3,000 — the full amount. This is the workflow working, not a calculation error</t>
+  </si>
+  <si>
+    <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
+  </si>
+  <si>
+    <t>a REJECTED discount leaves the bill at Rs 3,000 — the patient is charged in full, which is the only safe reading of a refusal</t>
+  </si>
+  <si>
+    <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
+  </si>
+  <si>
     <t>SCOPE</t>
   </si>
   <si>
-    <t>39 of 260 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 221 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
+    <t>47 of 263 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 216 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
   </si>
 </sst>
 </file>
@@ -6863,7 +6950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9268,7 +9355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>508</v>
       </c>
@@ -9291,7 +9378,7 @@
         <v>512</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -9424,67 +9511,67 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>542</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="G99" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>547</v>
-      </c>
       <c r="H99" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>543</v>
+        <v>503</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="F100" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>554</v>
@@ -9499,18 +9586,18 @@
         <v>557</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>558</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>559</v>
@@ -9525,56 +9612,56 @@
         <v>562</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>563</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>568</v>
-      </c>
       <c r="H103" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="F104" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="G104" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>41</v>
@@ -9582,25 +9669,25 @@
     </row>
     <row r="105" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="F105" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F105" s="2" t="s">
+      <c r="G105" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>41</v>
@@ -9608,25 +9695,25 @@
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="F106" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="G106" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>41</v>
@@ -9634,13 +9721,13 @@
     </row>
     <row r="107" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>586</v>
@@ -9666,19 +9753,19 @@
         <v>177</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="F108" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="F108" s="2" t="s">
+      <c r="G108" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>41</v>
@@ -9686,25 +9773,25 @@
     </row>
     <row r="109" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="F109" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>41</v>
@@ -9712,13 +9799,13 @@
     </row>
     <row r="110" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>602</v>
@@ -9744,7 +9831,7 @@
         <v>177</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>607</v>
@@ -9770,19 +9857,19 @@
         <v>177</v>
       </c>
       <c r="C112" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="E112" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="F112" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="G112" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>41</v>
@@ -9790,25 +9877,25 @@
     </row>
     <row r="113" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="G113" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>41</v>
@@ -9816,25 +9903,25 @@
     </row>
     <row r="114" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>623</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>41</v>
@@ -9842,25 +9929,25 @@
     </row>
     <row r="115" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>41</v>
@@ -9868,19 +9955,19 @@
     </row>
     <row r="116" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>634</v>
@@ -9897,22 +9984,22 @@
         <v>636</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F117" s="2" t="s">
+      <c r="G117" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>41</v>
@@ -9920,19 +10007,19 @@
     </row>
     <row r="118" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="D118" s="2" t="s">
+      <c r="E118" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>644</v>
@@ -9952,19 +10039,19 @@
         <v>223</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>41</v>
@@ -9972,19 +10059,19 @@
     </row>
     <row r="120" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>653</v>
+        <v>231</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>654</v>
@@ -10004,19 +10091,19 @@
         <v>223</v>
       </c>
       <c r="C121" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="E121" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="F121" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="G121" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>41</v>
@@ -10024,25 +10111,25 @@
     </row>
     <row r="122" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C122" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="F122" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="G122" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>41</v>
@@ -10050,25 +10137,25 @@
     </row>
     <row r="123" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="F123" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="G123" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>41</v>
@@ -10076,13 +10163,13 @@
     </row>
     <row r="124" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>674</v>
@@ -10105,22 +10192,22 @@
         <v>678</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="C125" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>41</v>
@@ -10128,91 +10215,91 @@
     </row>
     <row r="126" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="E126" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="8" t="s">
+      <c r="C127" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="D127" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C127" s="7" t="s">
-        <v>690</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>693</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="8" t="s">
+      <c r="C128" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="B128" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>690</v>
-      </c>
-      <c r="D128" s="7" t="s">
+      <c r="E128" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="F128" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="F128" s="7" t="s">
+      <c r="G128" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="G128" s="7" t="s">
-        <v>699</v>
-      </c>
-      <c r="H128" s="9" t="s">
+      <c r="H128" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="129" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>177</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>701</v>
@@ -10238,13 +10325,13 @@
         <v>177</v>
       </c>
       <c r="C130" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="E130" s="7" t="s">
         <v>707</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>697</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>708</v>
@@ -10264,7 +10351,7 @@
         <v>177</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>711</v>
@@ -10296,13 +10383,13 @@
         <v>717</v>
       </c>
       <c r="E132" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="F132" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="G132" s="7" t="s">
         <v>719</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>720</v>
       </c>
       <c r="H132" s="9" t="s">
         <v>41</v>
@@ -10310,7 +10397,7 @@
     </row>
     <row r="133" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>177</v>
@@ -10319,16 +10406,16 @@
         <v>716</v>
       </c>
       <c r="D133" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="E133" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="F133" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="F133" s="7" t="s">
+      <c r="G133" s="7" t="s">
         <v>724</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>725</v>
       </c>
       <c r="H133" s="9" t="s">
         <v>41</v>
@@ -10336,103 +10423,103 @@
     </row>
     <row r="134" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>177</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>727</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H134" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B135" s="2" t="s">
+    <row r="135" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D135" s="2" t="s">
+      <c r="C135" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D135" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="E135" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="F135" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="G135" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="H135" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
+      <c r="H135" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D136" s="2" t="s">
+      <c r="C136" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D136" s="7" t="s">
         <v>737</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="F136" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="G136" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="G136" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="H136" s="4" t="s">
+      <c r="H136" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="137" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="E137" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="F137" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="G137" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>41</v>
@@ -10440,25 +10527,25 @@
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>41</v>
@@ -10466,13 +10553,13 @@
     </row>
     <row r="139" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>753</v>
@@ -10495,10 +10582,10 @@
         <v>757</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>758</v>
@@ -10521,22 +10608,22 @@
         <v>762</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="C141" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="E141" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="F141" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="F141" s="2" t="s">
+      <c r="G141" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>41</v>
@@ -10544,103 +10631,103 @@
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="E142" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="G143" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H143" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
+      <c r="D144" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="D144" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="F144" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="G144" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="G144" s="2" t="s">
-        <v>784</v>
-      </c>
       <c r="H144" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="F145" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="F145" s="2" t="s">
+      <c r="G145" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>15</v>
@@ -10648,337 +10735,337 @@
     </row>
     <row r="146" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C146" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="F146" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="G146" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>796</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C147" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="F147" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="G147" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="H147" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
-        <v>803</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C148" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="F148" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="F148" s="2" t="s">
+      <c r="G148" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="H148" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="H148" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="s">
+      <c r="B149" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="D149" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H149" s="4" t="s">
+      <c r="C151" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="H151" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B150" s="2" t="s">
+    <row r="152" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="H150" s="4" t="s">
+      <c r="C152" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="153" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D153" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="E153" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="H153" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
         <v>836</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
-        <v>837</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="E154" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="E154" s="2" t="s">
+      <c r="F154" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="F154" s="2" t="s">
+      <c r="G154" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>842</v>
-      </c>
       <c r="H154" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D155" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="F155" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="G155" s="2" t="s">
         <v>846</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>847</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C156" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="E156" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="F156" s="2" t="s">
+      <c r="G156" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="H156" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>854</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D157" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="E157" s="2" t="s">
+      <c r="F157" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>858</v>
-      </c>
       <c r="H157" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="E158" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="E158" s="2" t="s">
+      <c r="F158" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="G158" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>864</v>
       </c>
       <c r="H158" s="4" t="s">
         <v>41</v>
@@ -10986,25 +11073,25 @@
     </row>
     <row r="159" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D159" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="E159" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="F159" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="E159" s="2" t="s">
+      <c r="G159" s="2" t="s">
         <v>868</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>41</v>
@@ -11012,25 +11099,25 @@
     </row>
     <row r="160" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D160" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="D160" s="2" t="s">
+      <c r="E160" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="E160" s="2" t="s">
+      <c r="F160" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="F160" s="2" t="s">
+      <c r="G160" s="2" t="s">
         <v>874</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>875</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>41</v>
@@ -11038,25 +11125,25 @@
     </row>
     <row r="161" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C161" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="E161" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E161" s="2" t="s">
+      <c r="F161" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="G161" s="2" t="s">
         <v>880</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>881</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>41</v>
@@ -11064,25 +11151,25 @@
     </row>
     <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D162" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="E162" s="2" t="s">
+      <c r="F162" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="G162" s="2" t="s">
         <v>885</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>886</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>41</v>
@@ -11090,13 +11177,13 @@
     </row>
     <row r="163" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>877</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>888</v>
@@ -11122,19 +11209,19 @@
         <v>75</v>
       </c>
       <c r="C164" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D164" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="E164" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="E164" s="2" t="s">
+      <c r="F164" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="G164" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>41</v>
@@ -11142,25 +11229,25 @@
     </row>
     <row r="165" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="D165" s="2" t="s">
+      <c r="E165" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="E165" s="2" t="s">
+      <c r="F165" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="F165" s="2" t="s">
+      <c r="G165" s="2" t="s">
         <v>901</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>902</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>41</v>
@@ -11168,181 +11255,181 @@
     </row>
     <row r="166" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C166" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="E166" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="E166" s="2" t="s">
+      <c r="F166" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="F166" s="2" t="s">
+      <c r="G166" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="H166" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="H166" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
+      <c r="B167" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="E167" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="H167" s="4" t="s">
+      <c r="C169" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="H169" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="B168" s="2" t="s">
+    <row r="170" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="H168" s="4" t="s">
+      <c r="C170" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="H170" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="H169" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="B170" s="2" t="s">
+    <row r="171" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="G170" s="2" t="s">
+      <c r="C171" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="H170" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
+      <c r="D171" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="D171" s="2" t="s">
+      <c r="E171" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="E171" s="2" t="s">
+      <c r="F171" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="F171" s="2" t="s">
+      <c r="G171" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>936</v>
-      </c>
       <c r="H171" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E172" s="2" t="s">
+      <c r="F172" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="F172" s="2" t="s">
+      <c r="G172" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>942</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>41</v>
@@ -11350,13 +11437,13 @@
     </row>
     <row r="173" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>938</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>944</v>
@@ -11382,19 +11469,19 @@
         <v>177</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="E174" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="E174" s="2" t="s">
+      <c r="F174" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="F174" s="2" t="s">
+      <c r="G174" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>41</v>
@@ -11402,25 +11489,25 @@
     </row>
     <row r="175" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="D175" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="E175" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="E175" s="2" t="s">
+      <c r="F175" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="F175" s="2" t="s">
+      <c r="G175" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>41</v>
@@ -11428,25 +11515,25 @@
     </row>
     <row r="176" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D176" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="E176" s="2" t="s">
+      <c r="F176" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="F176" s="2" t="s">
+      <c r="G176" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>41</v>
@@ -11454,25 +11541,25 @@
     </row>
     <row r="177" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C177" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="E177" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="E177" s="2" t="s">
+      <c r="F177" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="F177" s="2" t="s">
+      <c r="G177" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>41</v>
@@ -11480,25 +11567,25 @@
     </row>
     <row r="178" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C178" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D178" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="E178" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="E178" s="2" t="s">
+      <c r="F178" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="F178" s="2" t="s">
+      <c r="G178" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="G178" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>41</v>
@@ -11506,25 +11593,25 @@
     </row>
     <row r="179" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D179" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C179" s="2" t="s">
+      <c r="E179" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="F179" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="E179" s="2" t="s">
+      <c r="G179" s="2" t="s">
         <v>980</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="G179" s="2" t="s">
-        <v>982</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>41</v>
@@ -11532,25 +11619,25 @@
     </row>
     <row r="180" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D180" s="2" t="s">
+      <c r="E180" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="E180" s="2" t="s">
+      <c r="F180" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="F180" s="2" t="s">
+      <c r="G180" s="2" t="s">
         <v>986</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>987</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>41</v>
@@ -11558,25 +11645,25 @@
     </row>
     <row r="181" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C181" s="2" t="s">
+      <c r="D181" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="E181" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="E181" s="2" t="s">
+      <c r="F181" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="F181" s="2" t="s">
+      <c r="G181" s="2" t="s">
         <v>992</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>993</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>41</v>
@@ -11584,25 +11671,25 @@
     </row>
     <row r="182" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C182" s="2" t="s">
+      <c r="D182" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="E182" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="F182" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="F182" s="2" t="s">
+      <c r="G182" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>999</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>41</v>
@@ -11610,25 +11697,25 @@
     </row>
     <row r="183" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="D183" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="E183" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="F183" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="G183" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>1005</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>41</v>
@@ -11636,25 +11723,25 @@
     </row>
     <row r="184" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D184" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D184" s="2" t="s">
+      <c r="E184" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="E184" s="2" t="s">
+      <c r="F184" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="F184" s="2" t="s">
+      <c r="G184" s="2" t="s">
         <v>1009</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>1010</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>41</v>
@@ -11662,25 +11749,25 @@
     </row>
     <row r="185" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C185" s="2" t="s">
+      <c r="D185" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="E185" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="E185" s="2" t="s">
+      <c r="F185" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="F185" s="2" t="s">
+      <c r="G185" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>1016</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>41</v>
@@ -11688,25 +11775,25 @@
     </row>
     <row r="186" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D186" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="E186" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="F186" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="G186" s="2" t="s">
         <v>1021</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>1022</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>41</v>
@@ -11714,25 +11801,25 @@
     </row>
     <row r="187" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="F187" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="G187" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>1028</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>41</v>
@@ -11740,25 +11827,25 @@
     </row>
     <row r="188" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="D188" s="2" t="s">
+      <c r="F188" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="E188" s="2" t="s">
+      <c r="G188" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G188" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>41</v>
@@ -11766,25 +11853,25 @@
     </row>
     <row r="189" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>1036</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="F189" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="F189" s="2" t="s">
+      <c r="G189" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>1039</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>41</v>
@@ -11792,13 +11879,13 @@
     </row>
     <row r="190" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>1041</v>
@@ -11824,19 +11911,19 @@
         <v>58</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1030</v>
+        <v>1046</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>41</v>
@@ -11844,13 +11931,13 @@
     </row>
     <row r="192" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>1052</v>
@@ -11868,7 +11955,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="193" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>1056</v>
       </c>
@@ -11876,7 +11963,7 @@
         <v>58</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>1057</v>
@@ -11891,7 +11978,7 @@
         <v>1060</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="194" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -11902,19 +11989,19 @@
         <v>58</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D194" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="E194" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="F194" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="F194" s="2" t="s">
+      <c r="G194" s="2" t="s">
         <v>1065</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>1066</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>41</v>
@@ -11922,77 +12009,77 @@
     </row>
     <row r="195" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C195" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="E195" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="E195" s="2" t="s">
+      <c r="F195" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="F195" s="2" t="s">
+      <c r="G195" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="H195" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
         <v>1072</v>
-      </c>
-      <c r="H195" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="s">
-        <v>1073</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C196" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="F196" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="E196" s="2" t="s">
+      <c r="G196" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="F196" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>1078</v>
-      </c>
       <c r="H196" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C197" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="F197" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="E197" s="2" t="s">
+      <c r="G197" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>1084</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>41</v>
@@ -12000,25 +12087,25 @@
     </row>
     <row r="198" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C198" s="2" t="s">
+      <c r="E198" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="F198" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="E198" s="2" t="s">
+      <c r="G198" s="2" t="s">
         <v>1088</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G198" s="2" t="s">
-        <v>1090</v>
       </c>
       <c r="H198" s="4" t="s">
         <v>41</v>
@@ -12026,25 +12113,25 @@
     </row>
     <row r="199" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C199" s="2" t="s">
+      <c r="E199" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="F199" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="E199" s="2" t="s">
+      <c r="G199" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>1096</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>41</v>
@@ -12052,25 +12139,25 @@
     </row>
     <row r="200" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C200" s="2" t="s">
+      <c r="E200" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="F200" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="E200" s="2" t="s">
+      <c r="G200" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>1102</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>41</v>
@@ -12078,25 +12165,25 @@
     </row>
     <row r="201" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C201" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="F201" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="E201" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F201" s="2" t="s">
+      <c r="G201" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>1107</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>41</v>
@@ -12104,91 +12191,91 @@
     </row>
     <row r="202" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C202" s="2" t="s">
+      <c r="D202" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="E202" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="E202" s="2" t="s">
+      <c r="F202" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="F202" s="2" t="s">
+      <c r="G202" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="H202" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="H202" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="3" t="s">
+      <c r="B203" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C203" s="2" t="s">
+      <c r="D203" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="E203" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="E203" s="2" t="s">
+      <c r="F203" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="F203" s="2" t="s">
+      <c r="G203" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="H203" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="H203" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
+      <c r="B204" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>1115</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>1121</v>
       </c>
       <c r="E204" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="F204" s="2" t="s">
+      <c r="G204" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="H204" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="H204" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
+      <c r="B205" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>1115</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>1126</v>
@@ -12203,15 +12290,15 @@
         <v>1129</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>1130</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>1131</v>
@@ -12229,82 +12316,82 @@
         <v>1135</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>1136</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="C207" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="E207" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="E207" s="2" t="s">
+      <c r="F207" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="F207" s="2" t="s">
+      <c r="G207" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="G207" s="2" t="s">
+      <c r="H207" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="H207" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="3" t="s">
+      <c r="B208" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D208" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C208" s="2" t="s">
+      <c r="E208" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="F208" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="E208" s="2" t="s">
+      <c r="G208" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="F208" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G208" s="2" t="s">
-        <v>1147</v>
-      </c>
       <c r="H208" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C209" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="F209" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="E209" s="2" t="s">
+      <c r="G209" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>1153</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>41</v>
@@ -12312,25 +12399,25 @@
     </row>
     <row r="210" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C210" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="F210" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="E210" s="2" t="s">
+      <c r="G210" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>1159</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>41</v>
@@ -12338,25 +12425,25 @@
     </row>
     <row r="211" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C211" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="F211" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="E211" s="2" t="s">
+      <c r="G211" s="2" t="s">
         <v>1163</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>1165</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>41</v>
@@ -12364,25 +12451,25 @@
     </row>
     <row r="212" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C212" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="F212" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="E212" s="2" t="s">
+      <c r="G212" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>1171</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>41</v>
@@ -12390,25 +12477,25 @@
     </row>
     <row r="213" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C213" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="F213" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="E213" s="2" t="s">
+      <c r="G213" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>1177</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>41</v>
@@ -12416,25 +12503,25 @@
     </row>
     <row r="214" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C214" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="F214" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="E214" s="2" t="s">
+      <c r="G214" s="2" t="s">
         <v>1181</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>1183</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>41</v>
@@ -12442,25 +12529,25 @@
     </row>
     <row r="215" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C215" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="E215" s="2" t="s">
+      <c r="G215" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G215" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>41</v>
@@ -12468,25 +12555,25 @@
     </row>
     <row r="216" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C216" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="F216" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="E216" s="2" t="s">
+      <c r="G216" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G216" s="2" t="s">
-        <v>1195</v>
       </c>
       <c r="H216" s="4" t="s">
         <v>41</v>
@@ -12494,25 +12581,25 @@
     </row>
     <row r="217" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C217" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="F217" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="E217" s="2" t="s">
+      <c r="G217" s="2" t="s">
         <v>1199</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G217" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>41</v>
@@ -12520,77 +12607,77 @@
     </row>
     <row r="218" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C218" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="G218" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="H218" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
         <v>1206</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="B219" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="H218" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="3" t="s">
+      <c r="D219" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C219" s="2" t="s">
+      <c r="E219" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="F219" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="E219" s="2" t="s">
+      <c r="G219" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>1213</v>
-      </c>
       <c r="H219" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D220" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C220" s="2" t="s">
+      <c r="E220" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="F220" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="E220" s="2" t="s">
+      <c r="G220" s="2" t="s">
         <v>1217</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>1219</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>41</v>
@@ -12598,77 +12685,77 @@
     </row>
     <row r="221" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="F221" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="E221" s="2" t="s">
+      <c r="G221" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="F221" s="2" t="s">
+      <c r="H221" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="G221" s="2" t="s">
+      <c r="B222" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="H221" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="8" t="s">
+      <c r="D222" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="B222" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C222" s="7" t="s">
+      <c r="E222" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="D222" s="7" t="s">
+      <c r="F222" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="E222" s="7" t="s">
+      <c r="G222" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="F222" s="7" t="s">
-        <v>1230</v>
-      </c>
-      <c r="G222" s="7" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H222" s="9" t="s">
-        <v>41</v>
+      <c r="H222" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="223" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D223" s="2" t="s">
+      <c r="E223" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="E223" s="2" t="s">
+      <c r="F223" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="F223" s="2" t="s">
+      <c r="G223" s="2" t="s">
         <v>1235</v>
-      </c>
-      <c r="G223" s="2" t="s">
-        <v>1236</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>41</v>
@@ -12676,77 +12763,77 @@
     </row>
     <row r="224" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="E224" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="E224" s="2" t="s">
+      <c r="F224" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="F224" s="2" t="s">
+      <c r="G224" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="G224" s="2" t="s">
+      <c r="H224" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="8" t="s">
         <v>1242</v>
       </c>
-      <c r="H224" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="3" t="s">
+      <c r="B225" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C225" s="7" t="s">
         <v>1243</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C225" s="2" t="s">
+      <c r="D225" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="E225" s="7" t="s">
         <v>1245</v>
       </c>
-      <c r="E225" s="2" t="s">
+      <c r="F225" s="7" t="s">
         <v>1246</v>
       </c>
-      <c r="F225" s="2" t="s">
+      <c r="G225" s="7" t="s">
         <v>1247</v>
       </c>
-      <c r="G225" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H225" s="4" t="s">
+      <c r="H225" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="226" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D226" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C226" s="2" t="s">
+      <c r="E226" s="2" t="s">
         <v>1250</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="F226" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="E226" s="2" t="s">
+      <c r="G226" s="2" t="s">
         <v>1252</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>1254</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>41</v>
@@ -12754,77 +12841,77 @@
     </row>
     <row r="227" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="E227" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C227" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G227" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="H227" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="s">
+      <c r="D228" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C228" s="2" t="s">
+      <c r="E228" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="F228" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="G228" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="F228" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>1266</v>
-      </c>
       <c r="H228" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="229" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C229" s="2" t="s">
+      <c r="E229" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="F229" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="E229" s="2" t="s">
+      <c r="G229" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G229" s="2" t="s">
-        <v>1272</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>41</v>
@@ -12832,25 +12919,25 @@
     </row>
     <row r="230" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C230" s="2" t="s">
+      <c r="E230" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="F230" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="E230" s="2" t="s">
+      <c r="G230" s="2" t="s">
         <v>1276</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>1278</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>41</v>
@@ -12858,25 +12945,25 @@
     </row>
     <row r="231" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D231" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C231" s="2" t="s">
+      <c r="E231" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="F231" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="E231" s="2" t="s">
+      <c r="G231" s="2" t="s">
         <v>1282</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>1283</v>
-      </c>
-      <c r="G231" s="2" t="s">
-        <v>1284</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>41</v>
@@ -12884,25 +12971,25 @@
     </row>
     <row r="232" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="F232" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="G232" s="2" t="s">
         <v>1288</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>1290</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>41</v>
@@ -12910,25 +12997,25 @@
     </row>
     <row r="233" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>1292</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="F233" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="E233" s="2" t="s">
+      <c r="G233" s="2" t="s">
         <v>1294</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G233" s="2" t="s">
-        <v>1296</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>41</v>
@@ -12936,25 +13023,25 @@
     </row>
     <row r="234" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>1297</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C234" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="F234" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="E234" s="2" t="s">
+      <c r="G234" s="2" t="s">
         <v>1300</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>1302</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>41</v>
@@ -12962,25 +13049,25 @@
     </row>
     <row r="235" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>1303</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C235" s="2" t="s">
+      <c r="E235" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="F235" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="E235" s="2" t="s">
+      <c r="G235" s="2" t="s">
         <v>1306</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>1308</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>41</v>
@@ -12988,25 +13075,25 @@
     </row>
     <row r="236" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C236" s="2" t="s">
+      <c r="E236" s="2" t="s">
         <v>1310</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="F236" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="E236" s="2" t="s">
+      <c r="G236" s="2" t="s">
         <v>1312</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>1314</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>41</v>
@@ -13014,157 +13101,157 @@
     </row>
     <row r="237" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="D237" s="2" t="s">
+      <c r="F237" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="E237" s="2" t="s">
+      <c r="G237" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="F237" s="2" t="s">
+      <c r="H237" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
         <v>1319</v>
       </c>
-      <c r="G237" s="2" t="s">
+      <c r="B238" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="H237" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="8" t="s">
+      <c r="D238" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="E238" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C238" s="7" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D238" s="7" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E238" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F238" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="G238" s="7" t="s">
+      <c r="C239" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="H238" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
+      <c r="D239" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="B239" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C239" s="7" t="s">
+      <c r="E239" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="D239" s="7" t="s">
+      <c r="F239" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="E239" s="7" t="s">
+      <c r="G239" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="F239" s="7" t="s">
-        <v>1331</v>
-      </c>
-      <c r="G239" s="7" t="s">
-        <v>1332</v>
-      </c>
-      <c r="H239" s="9" t="s">
+      <c r="H239" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="240" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C240" s="2" t="s">
+      <c r="E240" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="F240" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="E240" s="2" t="s">
+      <c r="G240" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="H240" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="G240" s="2" t="s">
+      <c r="B241" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C241" s="7" t="s">
         <v>1338</v>
       </c>
-      <c r="H240" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="3" t="s">
+      <c r="D241" s="7" t="s">
         <v>1339</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D241" s="2" t="s">
+      <c r="E241" s="7" t="s">
         <v>1340</v>
       </c>
-      <c r="E241" s="2" t="s">
+      <c r="F241" s="7" t="s">
         <v>1341</v>
       </c>
-      <c r="F241" s="2" t="s">
+      <c r="G241" s="7" t="s">
         <v>1342</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="H241" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="8" t="s">
         <v>1343</v>
       </c>
-      <c r="H241" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="3" t="s">
+      <c r="B242" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C242" s="7" t="s">
         <v>1344</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D242" s="2" t="s">
+      <c r="D242" s="7" t="s">
         <v>1345</v>
       </c>
-      <c r="E242" s="2" t="s">
+      <c r="E242" s="7" t="s">
         <v>1346</v>
       </c>
-      <c r="F242" s="2" t="s">
+      <c r="F242" s="7" t="s">
         <v>1347</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" s="7" t="s">
         <v>1348</v>
       </c>
-      <c r="H242" s="4" t="s">
+      <c r="H242" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -13173,7 +13260,7 @@
         <v>1349</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>1350</v>
@@ -13199,22 +13286,22 @@
         <v>1355</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D244" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="E244" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="E244" s="2" t="s">
+      <c r="F244" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="F244" s="2" t="s">
+      <c r="G244" s="2" t="s">
         <v>1359</v>
-      </c>
-      <c r="G244" s="2" t="s">
-        <v>1360</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>41</v>
@@ -13222,25 +13309,25 @@
     </row>
     <row r="245" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C245" s="2" t="s">
+      <c r="E245" s="2" t="s">
         <v>1362</v>
       </c>
-      <c r="D245" s="2" t="s">
+      <c r="F245" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="E245" s="2" t="s">
+      <c r="G245" s="2" t="s">
         <v>1364</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>1365</v>
-      </c>
-      <c r="G245" s="2" t="s">
-        <v>1366</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>41</v>
@@ -13248,25 +13335,25 @@
     </row>
     <row r="246" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C246" s="2" t="s">
+      <c r="E246" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="F246" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="E246" s="2" t="s">
+      <c r="G246" s="2" t="s">
         <v>1370</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G246" s="2" t="s">
-        <v>1372</v>
       </c>
       <c r="H246" s="4" t="s">
         <v>41</v>
@@ -13274,25 +13361,25 @@
     </row>
     <row r="247" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>1373</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C247" s="2" t="s">
+      <c r="E247" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="D247" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="E247" s="2" t="s">
+      <c r="G247" s="2" t="s">
         <v>1376</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G247" s="2" t="s">
-        <v>1378</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>41</v>
@@ -13300,25 +13387,25 @@
     </row>
     <row r="248" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D248" s="2" t="s">
+      <c r="E248" s="2" t="s">
         <v>1380</v>
       </c>
-      <c r="E248" s="2" t="s">
+      <c r="F248" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="F248" s="2" t="s">
+      <c r="G248" s="2" t="s">
         <v>1382</v>
-      </c>
-      <c r="G248" s="2" t="s">
-        <v>1383</v>
       </c>
       <c r="H248" s="4" t="s">
         <v>41</v>
@@ -13326,25 +13413,25 @@
     </row>
     <row r="249" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C249" s="2" t="s">
+      <c r="D249" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="E249" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="E249" s="2" t="s">
+      <c r="F249" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="F249" s="2" t="s">
+      <c r="G249" s="2" t="s">
         <v>1388</v>
-      </c>
-      <c r="G249" s="2" t="s">
-        <v>1389</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>41</v>
@@ -13352,25 +13439,25 @@
     </row>
     <row r="250" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="E250" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="E250" s="2" t="s">
+      <c r="F250" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="F250" s="2" t="s">
+      <c r="G250" s="2" t="s">
         <v>1394</v>
-      </c>
-      <c r="G250" s="2" t="s">
-        <v>1395</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>41</v>
@@ -13378,25 +13465,25 @@
     </row>
     <row r="251" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>1397</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="F251" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="E251" s="2" t="s">
+      <c r="G251" s="2" t="s">
         <v>1399</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="G251" s="2" t="s">
-        <v>1401</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>41</v>
@@ -13404,25 +13491,25 @@
     </row>
     <row r="252" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>1403</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="F252" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="E252" s="2" t="s">
+      <c r="G252" s="2" t="s">
         <v>1405</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G252" s="2" t="s">
-        <v>1407</v>
       </c>
       <c r="H252" s="4" t="s">
         <v>41</v>
@@ -13430,25 +13517,25 @@
     </row>
     <row r="253" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="F253" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="E253" s="2" t="s">
+      <c r="G253" s="2" t="s">
         <v>1411</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G253" s="2" t="s">
-        <v>1413</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>41</v>
@@ -13456,25 +13543,25 @@
     </row>
     <row r="254" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="D254" s="2" t="s">
+      <c r="F254" s="2" t="s">
         <v>1416</v>
       </c>
-      <c r="E254" s="2" t="s">
+      <c r="G254" s="2" t="s">
         <v>1417</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G254" s="2" t="s">
-        <v>1419</v>
       </c>
       <c r="H254" s="4" t="s">
         <v>41</v>
@@ -13482,25 +13569,25 @@
     </row>
     <row r="255" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>1421</v>
       </c>
-      <c r="E255" s="2" t="s">
+      <c r="F255" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="F255" s="2" t="s">
+      <c r="G255" s="2" t="s">
         <v>1423</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>1424</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>41</v>
@@ -13508,25 +13595,25 @@
     </row>
     <row r="256" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C256" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>1426</v>
       </c>
-      <c r="D256" s="2" t="s">
+      <c r="E256" s="2" t="s">
         <v>1427</v>
       </c>
-      <c r="E256" s="2" t="s">
+      <c r="F256" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="F256" s="2" t="s">
+      <c r="G256" s="2" t="s">
         <v>1429</v>
-      </c>
-      <c r="G256" s="2" t="s">
-        <v>1430</v>
       </c>
       <c r="H256" s="4" t="s">
         <v>41</v>
@@ -13534,25 +13621,25 @@
     </row>
     <row r="257" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="D257" s="2" t="s">
+      <c r="E257" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="E257" s="2" t="s">
+      <c r="F257" s="2" t="s">
         <v>1434</v>
       </c>
-      <c r="F257" s="2" t="s">
+      <c r="G257" s="2" t="s">
         <v>1435</v>
-      </c>
-      <c r="G257" s="2" t="s">
-        <v>1436</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>41</v>
@@ -13560,25 +13647,25 @@
     </row>
     <row r="258" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="F258" s="2" t="s">
         <v>1439</v>
       </c>
-      <c r="E258" s="2" t="s">
+      <c r="G258" s="2" t="s">
         <v>1440</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>1441</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>1442</v>
       </c>
       <c r="H258" s="4" t="s">
         <v>41</v>
@@ -13586,25 +13673,25 @@
     </row>
     <row r="259" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>1444</v>
       </c>
-      <c r="D259" s="2" t="s">
+      <c r="F259" s="2" t="s">
         <v>1445</v>
       </c>
-      <c r="E259" s="2" t="s">
+      <c r="G259" s="2" t="s">
         <v>1446</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>1448</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>41</v>
@@ -13612,25 +13699,25 @@
     </row>
     <row r="260" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C260" s="2" t="s">
+      <c r="E260" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="D260" s="2" t="s">
+      <c r="F260" s="2" t="s">
         <v>1451</v>
       </c>
-      <c r="E260" s="2" t="s">
+      <c r="G260" s="2" t="s">
         <v>1452</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>1454</v>
       </c>
       <c r="H260" s="4" t="s">
         <v>41</v>
@@ -13638,32 +13725,110 @@
     </row>
     <row r="261" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C261" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>1456</v>
       </c>
-      <c r="D261" s="2" t="s">
+      <c r="F261" s="2" t="s">
         <v>1457</v>
       </c>
-      <c r="E261" s="2" t="s">
+      <c r="G261" s="2" t="s">
         <v>1458</v>
       </c>
-      <c r="F261" s="2" t="s">
+      <c r="H261" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
         <v>1459</v>
       </c>
-      <c r="G261" s="2" t="s">
+      <c r="B262" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>1460</v>
       </c>
-      <c r="H261" s="4" t="s">
+      <c r="D262" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H264" s="4" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H261"/>
+  <autoFilter ref="A1:H264"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -13671,7 +13836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -13681,43 +13846,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1461</v>
+        <v>1477</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1462</v>
+        <v>1478</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1463</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1464</v>
+        <v>1480</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1465</v>
+        <v>1481</v>
       </c>
       <c r="C2" s="11">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1464</v>
+        <v>1480</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1466</v>
+        <v>1482</v>
       </c>
       <c r="C3" s="11">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1464</v>
+        <v>1480</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1467</v>
+        <v>1483</v>
       </c>
       <c r="C4" s="11">
         <v>11</v>
@@ -13725,18 +13890,18 @@
     </row>
     <row r="6" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>184</v>
       </c>
       <c r="C6" s="12">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>177</v>
@@ -13747,7 +13912,7 @@
     </row>
     <row r="8" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>58</v>
@@ -13758,10 +13923,10 @@
     </row>
     <row r="9" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="C9" s="12">
         <v>31</v>
@@ -13769,18 +13934,18 @@
     </row>
     <row r="10" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="C10" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>9</v>
@@ -13791,7 +13956,7 @@
     </row>
     <row r="12" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>190</v>
@@ -13802,10 +13967,10 @@
     </row>
     <row r="14" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="C14" s="12">
         <v>44</v>
@@ -13813,10 +13978,10 @@
     </row>
     <row r="15" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="C15" s="12">
         <v>31</v>
@@ -13824,32 +13989,32 @@
     </row>
     <row r="16" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="C16" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="C17" s="12">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1474</v>
+        <v>1490</v>
       </c>
       <c r="C18" s="12">
         <v>22</v>
@@ -13857,10 +14022,10 @@
     </row>
     <row r="19" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1475</v>
+        <v>1491</v>
       </c>
       <c r="C19" s="12">
         <v>20</v>
@@ -13868,10 +14033,10 @@
     </row>
     <row r="20" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1476</v>
+        <v>1492</v>
       </c>
       <c r="C20" s="12">
         <v>18</v>
@@ -13879,10 +14044,10 @@
     </row>
     <row r="21" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1477</v>
+        <v>1493</v>
       </c>
       <c r="C21" s="12">
         <v>17</v>
@@ -13890,10 +14055,10 @@
     </row>
     <row r="22" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1478</v>
+        <v>1494</v>
       </c>
       <c r="C22" s="12">
         <v>15</v>
@@ -13901,10 +14066,10 @@
     </row>
     <row r="23" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="C23" s="12">
         <v>10</v>
@@ -13912,10 +14077,10 @@
     </row>
     <row r="24" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1480</v>
+        <v>1496</v>
       </c>
       <c r="C24" s="12">
         <v>9</v>
@@ -13923,10 +14088,10 @@
     </row>
     <row r="25" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1481</v>
+        <v>1497</v>
       </c>
       <c r="C25" s="12">
         <v>9</v>
@@ -13934,10 +14099,10 @@
     </row>
     <row r="26" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1482</v>
+        <v>1498</v>
       </c>
       <c r="C26" s="12">
         <v>5</v>
@@ -13945,10 +14110,10 @@
     </row>
     <row r="27" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1483</v>
+        <v>1499</v>
       </c>
       <c r="C27" s="12">
         <v>5</v>
@@ -13956,10 +14121,10 @@
     </row>
     <row r="28" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1484</v>
+        <v>1500</v>
       </c>
       <c r="C28" s="12">
         <v>3</v>
@@ -13967,10 +14132,10 @@
     </row>
     <row r="29" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1485</v>
+        <v>1501</v>
       </c>
       <c r="C29" s="12">
         <v>2</v>
@@ -13978,7 +14143,7 @@
     </row>
     <row r="31" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>10</v>
@@ -13989,7 +14154,7 @@
     </row>
     <row r="32" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>96</v>
@@ -14000,7 +14165,7 @@
     </row>
     <row r="33" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>314</v>
@@ -14011,10 +14176,10 @@
     </row>
     <row r="34" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>612</v>
+        <v>503</v>
       </c>
       <c r="C34" s="12">
         <v>5</v>
@@ -14022,21 +14187,21 @@
     </row>
     <row r="35" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>59</v>
+        <v>622</v>
       </c>
       <c r="C35" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="C36" s="12">
         <v>4</v>
@@ -14044,10 +14209,10 @@
     </row>
     <row r="37" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>432</v>
+        <v>139</v>
       </c>
       <c r="C37" s="12">
         <v>4</v>
@@ -14055,10 +14220,10 @@
     </row>
     <row r="38" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>543</v>
+        <v>432</v>
       </c>
       <c r="C38" s="12">
         <v>4</v>
@@ -14066,10 +14231,10 @@
     </row>
     <row r="39" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>591</v>
+        <v>553</v>
       </c>
       <c r="C39" s="12">
         <v>4</v>
@@ -14077,10 +14242,10 @@
     </row>
     <row r="40" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>637</v>
+        <v>601</v>
       </c>
       <c r="C40" s="12">
         <v>4</v>
@@ -14088,10 +14253,10 @@
     </row>
     <row r="41" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>731</v>
+        <v>647</v>
       </c>
       <c r="C41" s="12">
         <v>4</v>
@@ -14099,10 +14264,10 @@
     </row>
     <row r="42" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1030</v>
+        <v>741</v>
       </c>
       <c r="C42" s="12">
         <v>4</v>
@@ -14110,21 +14275,21 @@
     </row>
     <row r="43" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>43</v>
+        <v>1046</v>
       </c>
       <c r="C43" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C44" s="12">
         <v>3</v>
@@ -14132,10 +14297,10 @@
     </row>
     <row r="45" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="C45" s="12">
         <v>3</v>
@@ -14143,10 +14308,10 @@
     </row>
     <row r="46" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C46" s="12">
         <v>3</v>
@@ -14154,10 +14319,10 @@
     </row>
     <row r="47" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="C47" s="12">
         <v>3</v>
@@ -14165,10 +14330,10 @@
     </row>
     <row r="48" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>422</v>
+        <v>241</v>
       </c>
       <c r="C48" s="12">
         <v>3</v>
@@ -14176,10 +14341,10 @@
     </row>
     <row r="49" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="C49" s="12">
         <v>3</v>
@@ -14187,10 +14352,10 @@
     </row>
     <row r="50" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>503</v>
+        <v>463</v>
       </c>
       <c r="C50" s="12">
         <v>3</v>
@@ -14198,10 +14363,10 @@
     </row>
     <row r="51" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="C51" s="12">
         <v>3</v>
@@ -14209,10 +14374,10 @@
     </row>
     <row r="52" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C52" s="12">
         <v>3</v>
@@ -14220,10 +14385,10 @@
     </row>
     <row r="53" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="C53" s="12">
         <v>3</v>
@@ -14231,10 +14396,10 @@
     </row>
     <row r="54" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="C54" s="12">
         <v>3</v>
@@ -14242,10 +14407,10 @@
     </row>
     <row r="55" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C55" s="12">
         <v>3</v>
@@ -14253,10 +14418,10 @@
     </row>
     <row r="56" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>1115</v>
+        <v>1131</v>
       </c>
       <c r="C56" s="12">
         <v>3</v>
@@ -14264,10 +14429,10 @@
     </row>
     <row r="57" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="C57" s="12">
         <v>3</v>
@@ -14275,7 +14440,7 @@
     </row>
     <row r="58" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>128</v>
@@ -14286,7 +14451,7 @@
     </row>
     <row r="59" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>160</v>
@@ -14297,7 +14462,7 @@
     </row>
     <row r="60" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>212</v>
@@ -14308,7 +14473,7 @@
     </row>
     <row r="61" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>224</v>
@@ -14319,7 +14484,7 @@
     </row>
     <row r="62" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>293</v>
@@ -14330,7 +14495,7 @@
     </row>
     <row r="63" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>304</v>
@@ -14341,7 +14506,7 @@
     </row>
     <row r="64" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>349</v>
@@ -14352,7 +14517,7 @@
     </row>
     <row r="65" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>360</v>
@@ -14363,7 +14528,7 @@
     </row>
     <row r="66" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>411</v>
@@ -14374,10 +14539,10 @@
     </row>
     <row r="67" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C67" s="12">
         <v>2</v>
@@ -14385,10 +14550,10 @@
     </row>
     <row r="68" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="C68" s="12">
         <v>2</v>
@@ -14396,10 +14561,10 @@
     </row>
     <row r="69" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="C69" s="12">
         <v>2</v>
@@ -14407,10 +14572,10 @@
     </row>
     <row r="70" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="C70" s="12">
         <v>2</v>
@@ -14418,10 +14583,10 @@
     </row>
     <row r="71" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="C71" s="12">
         <v>2</v>
@@ -14429,10 +14594,10 @@
     </row>
     <row r="72" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="C72" s="12">
         <v>2</v>
@@ -14440,10 +14605,10 @@
     </row>
     <row r="73" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="C73" s="12">
         <v>2</v>
@@ -14451,10 +14616,10 @@
     </row>
     <row r="74" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="C74" s="12">
         <v>2</v>
@@ -14462,10 +14627,10 @@
     </row>
     <row r="75" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="C75" s="12">
         <v>2</v>
@@ -14473,10 +14638,10 @@
     </row>
     <row r="76" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="C76" s="12">
         <v>2</v>
@@ -14484,10 +14649,10 @@
     </row>
     <row r="77" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="C77" s="12">
         <v>2</v>
@@ -14495,10 +14660,10 @@
     </row>
     <row r="78" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="C78" s="12">
         <v>2</v>
@@ -14506,10 +14671,10 @@
     </row>
     <row r="79" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>938</v>
+        <v>954</v>
       </c>
       <c r="C79" s="12">
         <v>2</v>
@@ -14517,10 +14682,10 @@
     </row>
     <row r="80" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="C80" s="12">
         <v>2</v>
@@ -14528,10 +14693,10 @@
     </row>
     <row r="81" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="C81" s="12">
         <v>2</v>
@@ -14539,10 +14704,10 @@
     </row>
     <row r="82" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="C82" s="12">
         <v>2</v>
@@ -14550,10 +14715,10 @@
     </row>
     <row r="83" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>1051</v>
+        <v>1067</v>
       </c>
       <c r="C83" s="12">
         <v>2</v>
@@ -14561,10 +14726,10 @@
     </row>
     <row r="84" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>1227</v>
+        <v>1243</v>
       </c>
       <c r="C84" s="12">
         <v>2</v>
@@ -14572,10 +14737,10 @@
     </row>
     <row r="85" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>1374</v>
+        <v>1390</v>
       </c>
       <c r="C85" s="12">
         <v>2</v>
@@ -14583,10 +14748,10 @@
     </row>
     <row r="86" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>1415</v>
+        <v>1431</v>
       </c>
       <c r="C86" s="12">
         <v>2</v>
@@ -14594,7 +14759,7 @@
     </row>
     <row r="87" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>122</v>
@@ -14605,7 +14770,7 @@
     </row>
     <row r="88" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>171</v>
@@ -14616,7 +14781,7 @@
     </row>
     <row r="89" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>235</v>
@@ -14627,7 +14792,7 @@
     </row>
     <row r="90" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>257</v>
@@ -14638,7 +14803,7 @@
     </row>
     <row r="91" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>263</v>
@@ -14649,7 +14814,7 @@
     </row>
     <row r="92" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>269</v>
@@ -14660,7 +14825,7 @@
     </row>
     <row r="93" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>275</v>
@@ -14671,7 +14836,7 @@
     </row>
     <row r="94" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>281</v>
@@ -14682,7 +14847,7 @@
     </row>
     <row r="95" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>287</v>
@@ -14693,7 +14858,7 @@
     </row>
     <row r="96" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>337</v>
@@ -14704,7 +14869,7 @@
     </row>
     <row r="97" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>343</v>
@@ -14715,7 +14880,7 @@
     </row>
     <row r="98" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>370</v>
@@ -14726,7 +14891,7 @@
     </row>
     <row r="99" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>376</v>
@@ -14737,7 +14902,7 @@
     </row>
     <row r="100" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>382</v>
@@ -14748,7 +14913,7 @@
     </row>
     <row r="101" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>388</v>
@@ -14759,7 +14924,7 @@
     </row>
     <row r="102" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>394</v>
@@ -14770,7 +14935,7 @@
     </row>
     <row r="103" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>399</v>
@@ -14781,7 +14946,7 @@
     </row>
     <row r="104" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>405</v>
@@ -14792,7 +14957,7 @@
     </row>
     <row r="105" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>458</v>
@@ -14803,7 +14968,7 @@
     </row>
     <row r="106" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>479</v>
@@ -14814,7 +14979,7 @@
     </row>
     <row r="107" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>485</v>
@@ -14825,7 +14990,7 @@
     </row>
     <row r="108" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>491</v>
@@ -14836,7 +15001,7 @@
     </row>
     <row r="109" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>497</v>
@@ -14847,7 +15012,7 @@
     </row>
     <row r="110" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>519</v>
@@ -14858,7 +15023,7 @@
     </row>
     <row r="111" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>525</v>
@@ -14869,7 +15034,7 @@
     </row>
     <row r="112" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>531</v>
@@ -14880,7 +15045,7 @@
     </row>
     <row r="113" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>537</v>
@@ -14891,10 +15056,10 @@
     </row>
     <row r="114" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="C114" s="12">
         <v>1</v>
@@ -14902,10 +15067,10 @@
     </row>
     <row r="115" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="C115" s="12">
         <v>1</v>
@@ -14913,10 +15078,10 @@
     </row>
     <row r="116" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="C116" s="12">
         <v>1</v>
@@ -14924,10 +15089,10 @@
     </row>
     <row r="117" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="C117" s="12">
         <v>1</v>
@@ -14935,10 +15100,10 @@
     </row>
     <row r="118" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="C118" s="12">
         <v>1</v>
@@ -14946,10 +15111,10 @@
     </row>
     <row r="119" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C119" s="12">
         <v>1</v>
@@ -14957,10 +15122,10 @@
     </row>
     <row r="120" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="C120" s="12">
         <v>1</v>
@@ -14968,10 +15133,10 @@
     </row>
     <row r="121" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="C121" s="12">
         <v>1</v>
@@ -14979,10 +15144,10 @@
     </row>
     <row r="122" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="C122" s="12">
         <v>1</v>
@@ -14990,10 +15155,10 @@
     </row>
     <row r="123" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="C123" s="12">
         <v>1</v>
@@ -15001,10 +15166,10 @@
     </row>
     <row r="124" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="C124" s="12">
         <v>1</v>
@@ -15012,10 +15177,10 @@
     </row>
     <row r="125" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="C125" s="12">
         <v>1</v>
@@ -15023,10 +15188,10 @@
     </row>
     <row r="126" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="C126" s="12">
         <v>1</v>
@@ -15034,10 +15199,10 @@
     </row>
     <row r="127" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="C127" s="12">
         <v>1</v>
@@ -15045,10 +15210,10 @@
     </row>
     <row r="128" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C128" s="12">
         <v>1</v>
@@ -15056,10 +15221,10 @@
     </row>
     <row r="129" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="C129" s="12">
         <v>1</v>
@@ -15067,10 +15232,10 @@
     </row>
     <row r="130" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C130" s="12">
         <v>1</v>
@@ -15078,10 +15243,10 @@
     </row>
     <row r="131" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C131" s="12">
         <v>1</v>
@@ -15089,10 +15254,10 @@
     </row>
     <row r="132" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C132" s="12">
         <v>1</v>
@@ -15100,10 +15265,10 @@
     </row>
     <row r="133" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="C133" s="12">
         <v>1</v>
@@ -15111,10 +15276,10 @@
     </row>
     <row r="134" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="C134" s="12">
         <v>1</v>
@@ -15122,10 +15287,10 @@
     </row>
     <row r="135" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="C135" s="12">
         <v>1</v>
@@ -15133,10 +15298,10 @@
     </row>
     <row r="136" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="C136" s="12">
         <v>1</v>
@@ -15144,10 +15309,10 @@
     </row>
     <row r="137" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
       <c r="C137" s="12">
         <v>1</v>
@@ -15155,10 +15320,10 @@
     </row>
     <row r="138" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="C138" s="12">
         <v>1</v>
@@ -15166,10 +15331,10 @@
     </row>
     <row r="139" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="C139" s="12">
         <v>1</v>
@@ -15177,10 +15342,10 @@
     </row>
     <row r="140" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="C140" s="12">
         <v>1</v>
@@ -15188,10 +15353,10 @@
     </row>
     <row r="141" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="C141" s="12">
         <v>1</v>
@@ -15199,10 +15364,10 @@
     </row>
     <row r="142" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="C142" s="12">
         <v>1</v>
@@ -15210,10 +15375,10 @@
     </row>
     <row r="143" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="C143" s="12">
         <v>1</v>
@@ -15221,10 +15386,10 @@
     </row>
     <row r="144" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="C144" s="12">
         <v>1</v>
@@ -15232,10 +15397,10 @@
     </row>
     <row r="145" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="C145" s="12">
         <v>1</v>
@@ -15243,10 +15408,10 @@
     </row>
     <row r="146" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="C146" s="12">
         <v>1</v>
@@ -15254,10 +15419,10 @@
     </row>
     <row r="147" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="C147" s="12">
         <v>1</v>
@@ -15265,10 +15430,10 @@
     </row>
     <row r="148" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="C148" s="12">
         <v>1</v>
@@ -15276,10 +15441,10 @@
     </row>
     <row r="149" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="C149" s="12">
         <v>1</v>
@@ -15287,10 +15452,10 @@
     </row>
     <row r="150" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C150" s="12">
         <v>1</v>
@@ -15298,10 +15463,10 @@
     </row>
     <row r="151" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="C151" s="12">
         <v>1</v>
@@ -15309,10 +15474,10 @@
     </row>
     <row r="152" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="C152" s="12">
         <v>1</v>
@@ -15320,10 +15485,10 @@
     </row>
     <row r="153" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="C153" s="12">
         <v>1</v>
@@ -15331,10 +15496,10 @@
     </row>
     <row r="154" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="C154" s="12">
         <v>1</v>
@@ -15342,10 +15507,10 @@
     </row>
     <row r="155" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="C155" s="12">
         <v>1</v>
@@ -15353,10 +15518,10 @@
     </row>
     <row r="156" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="C156" s="12">
         <v>1</v>
@@ -15364,10 +15529,10 @@
     </row>
     <row r="157" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="C157" s="12">
         <v>1</v>
@@ -15375,10 +15540,10 @@
     </row>
     <row r="158" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="C158" s="12">
         <v>1</v>
@@ -15386,10 +15551,10 @@
     </row>
     <row r="159" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C159" s="12">
         <v>1</v>
@@ -15397,10 +15562,10 @@
     </row>
     <row r="160" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C160" s="12">
         <v>1</v>
@@ -15408,10 +15573,10 @@
     </row>
     <row r="161" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="C161" s="12">
         <v>1</v>
@@ -15419,10 +15584,10 @@
     </row>
     <row r="162" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="C162" s="12">
         <v>1</v>
@@ -15430,10 +15595,10 @@
     </row>
     <row r="163" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="C163" s="12">
         <v>1</v>
@@ -15441,10 +15606,10 @@
     </row>
     <row r="164" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
       <c r="C164" s="12">
         <v>1</v>
@@ -15452,10 +15617,10 @@
     </row>
     <row r="165" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="C165" s="12">
         <v>1</v>
@@ -15463,10 +15628,10 @@
     </row>
     <row r="166" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="C166" s="12">
         <v>1</v>
@@ -15474,10 +15639,10 @@
     </row>
     <row r="167" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="C167" s="12">
         <v>1</v>
@@ -15485,10 +15650,10 @@
     </row>
     <row r="168" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="C168" s="12">
         <v>1</v>
@@ -15496,10 +15661,10 @@
     </row>
     <row r="169" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="C169" s="12">
         <v>1</v>
@@ -15507,10 +15672,10 @@
     </row>
     <row r="170" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="C170" s="12">
         <v>1</v>
@@ -15518,10 +15683,10 @@
     </row>
     <row r="171" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="C171" s="12">
         <v>1</v>
@@ -15529,10 +15694,10 @@
     </row>
     <row r="172" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="C172" s="12">
         <v>1</v>
@@ -15540,10 +15705,10 @@
     </row>
     <row r="173" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="C173" s="12">
         <v>1</v>
@@ -15551,10 +15716,10 @@
     </row>
     <row r="174" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="C174" s="12">
         <v>1</v>
@@ -15562,10 +15727,10 @@
     </row>
     <row r="175" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="C175" s="12">
         <v>1</v>
@@ -15573,10 +15738,10 @@
     </row>
     <row r="176" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="C176" s="12">
         <v>1</v>
@@ -15584,10 +15749,10 @@
     </row>
     <row r="177" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="C177" s="12">
         <v>1</v>
@@ -15595,10 +15760,10 @@
     </row>
     <row r="178" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="C178" s="12">
         <v>1</v>
@@ -15606,10 +15771,10 @@
     </row>
     <row r="179" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
       <c r="C179" s="12">
         <v>1</v>
@@ -15617,10 +15782,10 @@
     </row>
     <row r="180" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C180" s="12">
         <v>1</v>
@@ -15628,10 +15793,10 @@
     </row>
     <row r="181" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="C181" s="12">
         <v>1</v>
@@ -15639,10 +15804,10 @@
     </row>
     <row r="182" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="C182" s="12">
         <v>1</v>
@@ -15650,10 +15815,10 @@
     </row>
     <row r="183" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="C183" s="12">
         <v>1</v>
@@ -15661,10 +15826,10 @@
     </row>
     <row r="184" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="C184" s="12">
         <v>1</v>
@@ -15672,10 +15837,10 @@
     </row>
     <row r="185" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C185" s="12">
         <v>1</v>
@@ -15683,10 +15848,10 @@
     </row>
     <row r="186" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="C186" s="12">
         <v>1</v>
@@ -15694,10 +15859,10 @@
     </row>
     <row r="187" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
       <c r="C187" s="12">
         <v>1</v>
@@ -15705,10 +15870,10 @@
     </row>
     <row r="188" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="C188" s="12">
         <v>1</v>
@@ -15716,10 +15881,10 @@
     </row>
     <row r="189" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="C189" s="12">
         <v>1</v>
@@ -15727,12 +15892,23 @@
     </row>
     <row r="190" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="C190" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="12" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C191" s="12">
         <v>1</v>
       </c>
     </row>
@@ -15761,10 +15937,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1487</v>
+        <v>1503</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1488</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15772,13 +15948,13 @@
         <v>75</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1489</v>
+        <v>1505</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1490</v>
+        <v>1506</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1491</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15786,13 +15962,13 @@
         <v>75</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1484</v>
+        <v>1500</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1492</v>
+        <v>1508</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1493</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15800,13 +15976,13 @@
         <v>75</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1494</v>
+        <v>1510</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1495</v>
+        <v>1511</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1496</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15814,13 +15990,13 @@
         <v>75</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1498</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15828,13 +16004,13 @@
         <v>190</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1499</v>
+        <v>1515</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1500</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15842,13 +16018,13 @@
         <v>190</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1501</v>
+        <v>1517</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1503</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15856,13 +16032,13 @@
         <v>190</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1505</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15870,13 +16046,13 @@
         <v>177</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1506</v>
+        <v>1522</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1507</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15884,13 +16060,13 @@
         <v>177</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1508</v>
+        <v>1524</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1509</v>
+        <v>1525</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1510</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15898,13 +16074,13 @@
         <v>177</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1511</v>
+        <v>1527</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1512</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15912,13 +16088,13 @@
         <v>177</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1513</v>
+        <v>1529</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1514</v>
+        <v>1530</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>1515</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15926,13 +16102,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1516</v>
+        <v>1532</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1517</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15940,13 +16116,13 @@
         <v>184</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>1518</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1502</v>
-      </c>
       <c r="D14" s="13" t="s">
-        <v>1519</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15954,13 +16130,13 @@
         <v>184</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1520</v>
+        <v>1536</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1521</v>
+        <v>1537</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>1522</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15968,13 +16144,13 @@
         <v>184</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1523</v>
+        <v>1539</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15982,13 +16158,13 @@
         <v>58</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1525</v>
+        <v>1541</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1526</v>
+        <v>1542</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1527</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -15996,13 +16172,13 @@
         <v>58</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1528</v>
+        <v>1544</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1529</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16010,55 +16186,55 @@
         <v>58</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1530</v>
+        <v>1546</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1531</v>
+        <v>1547</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1532</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>1533</v>
+        <v>1549</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1485</v>
+        <v>1501</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>1534</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>1533</v>
+        <v>1549</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1535</v>
+        <v>1551</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1536</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>1537</v>
+        <v>1553</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1538</v>
+        <v>1554</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1539</v>
+        <v>1555</v>
       </c>
     </row>
   </sheetData>
@@ -16084,424 +16260,424 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1540</v>
+        <v>1556</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1543</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1544</v>
+        <v>1560</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1546</v>
+        <v>1562</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1547</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1548</v>
+        <v>1564</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1549</v>
+        <v>1565</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1550</v>
+        <v>1566</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1551</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1554</v>
+        <v>1570</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1555</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1556</v>
+        <v>1572</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1557</v>
+        <v>1573</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1558</v>
+        <v>1574</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1559</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1560</v>
+        <v>1576</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1561</v>
+        <v>1577</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>149</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1564</v>
+        <v>1580</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1565</v>
+        <v>1581</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1566</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1567</v>
+        <v>1583</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1569</v>
+        <v>1585</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>1570</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>1475</v>
+        <v>1491</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1571</v>
+        <v>1587</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1572</v>
+        <v>1588</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>1573</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>1475</v>
+        <v>1491</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1574</v>
+        <v>1590</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>342</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1577</v>
+        <v>1593</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1578</v>
+        <v>1594</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>1579</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>1581</v>
+        <v>1597</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>1582</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>1585</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1586</v>
+        <v>1602</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>1588</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1589</v>
+        <v>1605</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1591</v>
+        <v>1607</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1592</v>
+        <v>1608</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1593</v>
+        <v>1609</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1594</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1595</v>
+        <v>1611</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1596</v>
+        <v>1612</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1597</v>
+        <v>1613</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>1598</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1599</v>
+        <v>1615</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1600</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1601</v>
+        <v>1617</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>1602</v>
+        <v>1618</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>1603</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>1604</v>
+        <v>1620</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1605</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1606</v>
+        <v>1622</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1607</v>
+        <v>1623</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1608</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1609</v>
+        <v>1625</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1610</v>
+        <v>1626</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>1611</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1612</v>
+        <v>1628</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>1613</v>
+        <v>1629</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>1614</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1615</v>
+        <v>1631</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1616</v>
+        <v>1632</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>1617</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>1618</v>
+        <v>1634</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1619</v>
+        <v>1635</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1620</v>
+        <v>1636</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1621</v>
+        <v>1637</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1622</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16509,16 +16685,16 @@
         <v>58</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1623</v>
+        <v>1639</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1624</v>
+        <v>1640</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1625</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16526,118 +16702,118 @@
         <v>58</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1626</v>
+        <v>1642</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1627</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>1484</v>
+        <v>1500</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1628</v>
+        <v>1644</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>1629</v>
+        <v>1645</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1630</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>1477</v>
+        <v>1493</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1631</v>
+        <v>1647</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1632</v>
+        <v>1648</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>1633</v>
+        <v>1649</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1634</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>1478</v>
+        <v>1494</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>1635</v>
+        <v>1651</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>1638</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>1535</v>
+        <v>1551</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1639</v>
+        <v>1655</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1640</v>
+        <v>1656</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1641</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>1481</v>
+        <v>1497</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>1642</v>
+        <v>1658</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>1643</v>
+        <v>1659</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1644</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>1481</v>
+        <v>1497</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1645</v>
+        <v>1661</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>1646</v>
+        <v>1662</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>1208</v>
+        <v>1224</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1647</v>
+        <v>1663</v>
       </c>
     </row>
   </sheetData>
@@ -16661,12 +16837,12 @@
     </row>
     <row r="2" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>1648</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>1649</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16676,17 +16852,17 @@
     </row>
     <row r="5" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>1650</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>1651</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>1652</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16696,22 +16872,22 @@
     </row>
     <row r="9" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1653</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>1654</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>1655</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="12" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>1656</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16721,17 +16897,17 @@
     </row>
     <row r="14" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1657</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="15" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>1658</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>1659</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16741,17 +16917,17 @@
     </row>
     <row r="18" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1660</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>1661</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>1662</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16761,32 +16937,32 @@
     </row>
     <row r="22" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>1663</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>1664</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1665</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>1666</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>1667</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>1668</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16796,22 +16972,22 @@
     </row>
     <row r="29" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>1669</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>1670</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>1671</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>1672</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="33" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -16821,12 +16997,12 @@
     </row>
     <row r="34" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>1673</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="35" spans="1:1" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>1674</v>
+        <v>1690</v>
       </c>
     </row>
   </sheetData>
@@ -16837,7 +17013,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -16850,10 +17026,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1675</v>
+        <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1676</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16864,7 +17040,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1677</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16875,7 +17051,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>1678</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16886,7 +17062,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1679</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16897,7 +17073,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1680</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16908,7 +17084,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1681</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16919,7 +17095,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1682</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16930,7 +17106,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1683</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16941,7 +17117,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1684</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16952,7 +17128,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1685</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16963,7 +17139,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1686</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16974,7 +17150,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1687</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16985,7 +17161,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1688</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -16996,7 +17172,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1689</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17007,7 +17183,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1690</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17018,7 +17194,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1691</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17029,29 +17205,29 @@
         <v>15</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1692</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1693</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>1694</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17062,7 +17238,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1695</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17073,7 +17249,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>1696</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17084,7 +17260,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1697</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17095,18 +17271,18 @@
         <v>15</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>1698</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>1208</v>
+        <v>1224</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1699</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17117,7 +17293,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>1700</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17128,7 +17304,7 @@
         <v>15</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>1701</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -17139,161 +17315,249 @@
         <v>15</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>1702</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>1703</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>1704</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>1705</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>1706</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>1707</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="33" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>1708</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="34" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>1709</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>1710</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="36" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>1711</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="37" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>1712</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>1114</v>
+        <v>1130</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>1713</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="39" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>1714</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>1125</v>
+        <v>1141</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>1716</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>1717</v>
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>842</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>930</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>1741</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -10,13 +10,14 @@
     <sheet sheetId="4" name="Feature Coverage" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Read Me First" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="1770">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -6448,12 +6449,96 @@
   <si>
     <t>47 of 263 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 216 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
   </si>
+  <si>
+    <t>What the automated run did</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): all four clinic roles sign in and land in the workspace</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): unknown username is refused without revealing it does not exist</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a wrong password gives the identical message</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): empty fields are blocked before any request</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a suspended account is refused after the password is checked</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): signing out ends the session and protected pages stay unreachable</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): anonymous visits to protected pages redirect to login</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a deep link is not restored after signing in</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor sees clinical items and no money or staff items</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist sees the money screens but not the scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager sees neither staff nor expenses</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor cannot reach staff management by URL</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist is bounced from every restricted screen</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager cannot reach staff, expenses or profit and loss</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a clinic admin cannot enter the company panel</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist cannot reach the voice scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager opens the scribe page but is offered no recorder</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with every field completed</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with only the two mandatory fields</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a name</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a phone number</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): search finds a patient by name and filters the rest out</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a search with no matches shows an empty state rather than an error</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): another clinic's patient cannot be opened by id</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor can read patients but is offered no create control</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-05 20:47. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -6497,11 +6582,15 @@
       <sz val="12"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <b/>
+      <color rgb="FF1B6B38"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1B6B38"/>
+      <i/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
     </font>
     <font>
       <i/>
@@ -6557,7 +6646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6609,6 +6698,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8367,7 +8459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>303</v>
       </c>
@@ -8390,10 +8482,10 @@
         <v>308</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>309</v>
       </c>
@@ -8416,10 +8508,10 @@
         <v>312</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>313</v>
       </c>
@@ -8442,10 +8534,10 @@
         <v>318</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>319</v>
       </c>
@@ -8468,7 +8560,7 @@
         <v>322</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -8601,7 +8693,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>348</v>
       </c>
@@ -8624,10 +8716,10 @@
         <v>353</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>354</v>
       </c>
@@ -8650,7 +8742,7 @@
         <v>358</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -8731,7 +8823,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>375</v>
       </c>
@@ -8754,7 +8846,7 @@
         <v>380</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17032,532 +17124,845 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="13" t="s">
         <v>1693</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>1694</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>1696</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="13" t="s">
         <v>1697</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>1698</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>1699</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="13" t="s">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="13" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="13" t="s">
         <v>1702</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="13" t="s">
         <v>1703</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="13" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="13" t="s">
         <v>1705</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>1706</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="13" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>1708</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="13" t="s">
         <v>1709</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="13" t="s">
         <v>1710</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="13" t="s">
         <v>1711</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="13" t="s">
         <v>1712</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="13" t="s">
         <v>1713</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="13" t="s">
         <v>1714</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>1224</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="13" t="s">
         <v>1715</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>490</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="13" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="13" t="s">
         <v>1717</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="13" t="s">
         <v>1718</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>919</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="13" t="s">
         <v>1719</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+    <row r="29" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>925</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="13" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>790</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>1721</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>784</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="13" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="13" t="s">
         <v>1723</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+    <row r="33" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="13" t="s">
         <v>1724</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="13" t="s">
         <v>1725</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="13" t="s">
         <v>1726</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>853</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="13" t="s">
         <v>1727</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+    <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>1072</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="13" t="s">
         <v>1728</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+    <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>1130</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="13" t="s">
         <v>1729</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+    <row r="39" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>1136</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="13" t="s">
         <v>1730</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+    <row r="40" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>1141</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="13" t="s">
         <v>1731</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="13" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+    <row r="42" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="13" t="s">
         <v>1733</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+    <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>847</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="13" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>930</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>1735</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+    <row r="45" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="13" t="s">
         <v>1736</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+    <row r="46" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>1259</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+    <row r="47" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="13" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+    <row r="48" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="13" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
+    <row r="50" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
         <v>1740</v>
       </c>
-      <c r="B50" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="18" t="s">
+      <c r="B50" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>1741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>563</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>1769</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -9,15 +9,15 @@
     <sheet sheetId="3" name="Role Coverage" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Feature Coverage" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Read Me First" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId10"/>
+    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="1770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="1785">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -6300,9 +6300,123 @@
     <t>Result</t>
   </si>
   <si>
+    <t>What the automated run did</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): all four clinic roles sign in and land in the workspace</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): unknown username is refused without revealing it does not exist</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a wrong password gives the identical message</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): empty fields are blocked before any request</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a suspended account is refused after the password is checked</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): signing out ends the session and protected pages stay unreachable</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): anonymous visits to protected pages redirect to login</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a deep link is not restored after signing in</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor sees clinical items and no money or staff items</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist sees the money screens but not the scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager sees neither staff nor expenses</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor cannot reach staff management by URL</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist is bounced from every restricted screen</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager cannot reach staff, expenses or profit and loss</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a clinic admin cannot enter the company panel</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist cannot reach the voice scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager opens the scribe page but is offered no recorder</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with every field completed</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with only the two mandatory fields</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a name</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a phone number</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): search finds a patient by name and filters the rest out</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a search with no matches shows an empty state rather than an error</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): another clinic's patient cannot be opened by id</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor can read patients but is offered no create control</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-05 20:47. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
+  </si>
+  <si>
     <t>What was observed</t>
   </si>
   <si>
+    <t>receptionist -&gt; /clinic/scribe = /clinic (scribe unreachable)</t>
+  </si>
+  <si>
+    <t>manager opens the page, sees the no-permission card, and no Start recording button is rendered</t>
+  </si>
+  <si>
+    <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
+  </si>
+  <si>
+    <t>with fee Rs 5,000, without Rs 2,000 — difference Rs 3,000 equals the consultation fee exactly</t>
+  </si>
+  <si>
+    <t>amount 500 -&gt; Rs 4,500; percent 20 of subtotal 5000 -&gt; discount Rs 1,000, net Rs 4,000; percent 150 clamped to 100 giving net Rs 0; negative rejected: "Discount can't be negative."</t>
+  </si>
+  <si>
+    <t>a Rs 1,000 discount on a Rs 3,000 visit is HELD: status "pending", 1 approval row(s), and the bill still reads Rs 3,000 — the full amount. This is the workflow working, not a calculation error</t>
+  </si>
+  <si>
+    <t>Automated (e2e): appointments CSV → text/csv + footer + header; appointments CSV is clinic-scoped (A's patient, not B's) (11 lines for from=2026-09-06&amp;to=2026-11-05); the date filter reaches the export (empty range → no rows) (status=200)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): another clinic's appointment cannot be opened by id (status=200 title=FlexicaAI)</t>
+  </si>
+  <si>
+    <t>a REJECTED discount leaves the bill at Rs 3,000 — the patient is charged in full, which is the only safe reading of a refusal</t>
+  </si>
+  <si>
+    <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
+  </si>
+  <si>
     <t>all four clinic roles land on /clinic (admin-&gt;/clinic, manager-&gt;/clinic, doctor-&gt;/clinic, receptionist-&gt;/clinic)</t>
   </si>
   <si>
@@ -6321,13 +6435,76 @@
     <t>correct password still refused while locked: "Too many attempts. Please try again in 15 minutes."</t>
   </si>
   <si>
+    <t>sign out left /clinic -&gt; /login; protected page after sign-out -&gt; /login</t>
+  </si>
+  <si>
+    <t>Automated (e2e): suspended user's session is rejected → redirect</t>
+  </si>
+  <si>
     <t>anonymous hits redirect to /login (/login, /login, /login)</t>
   </si>
   <si>
     <t>deep link is NOT restored — landed on /clinic rather than /clinic/payments (documented behaviour)</t>
   </si>
   <si>
-    <t>sign out left /clinic -&gt; /login; protected page after sign-out -&gt; /login</t>
+    <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
+  </si>
+  <si>
+    <t>partial Rs 1,000 then Rs 2,000 recorded as 2 rows totalling Rs 3,000 against a Rs 3,000 bill</t>
+  </si>
+  <si>
+    <t>zero -&gt; "Enter an amount greater than zero.", negative -&gt; refused, NaN -&gt; refused; none created a payment row</t>
+  </si>
+  <si>
+    <t>paid Rs 2,500 against a Rs 2,000 bill — patient credit is now Rs 500, so the excess is retained rather than discarded</t>
+  </si>
+  <si>
+    <t>payment voided; the row is SOFT-deleted (recoverable from Trash) rather than erased, so the audit trail survives</t>
+  </si>
+  <si>
+    <t>refund of Rs 5,000 against Rs 2,000 collected refused ("Can't refund more than collected (Rs 2000)."); a Rs 500 refund succeeded</t>
+  </si>
+  <si>
+    <t>receipt number 2 allocated on the first payment and UNCHANGED after a second (2); both payments (2) are listed against the one receipt — a visit has one receipt, not one per payment</t>
+  </si>
+  <si>
+    <t>before any collection the visit has NO receipt number; after Rs 1,000 was collected it has one (RCP-2026-0000001) — the receipt is proof of payment, so it cannot predate one</t>
+  </si>
+  <si>
+    <t>a paid visit had NO invoice until one was requested, then got INV-2026-0000001. The receipt number appears automatically on payment; the invoice number only when someone asks — which is why "where is the invoice number" is usually "nobody pressed the button"</t>
+  </si>
+  <si>
+    <t>three invoices issued -&gt; numbers 1, 2, 3 (unique: true, sequential: true)</t>
+  </si>
+  <si>
+    <t>across 48 fee/line/discount combinations, gross minus discount equals net every time and net never goes below zero or above gross</t>
+  </si>
+  <si>
+    <t>line 1000 less 200 = Rs 800, then 10% of the SUBTOTAL = Rs 80, net Rs 720 (Rs 720 proves the line discount applies first; Rs 700 would mean the order is wrong)</t>
+  </si>
+  <si>
+    <t>the same visit carries receipt #4 and invoice #2 from two SEPARATE counters — a bill is what is owed, a receipt is proof of payment, and they must never share a sequence</t>
+  </si>
+  <si>
+    <t>Automated (e2e): valid signed link → 200 PDF; tampered token → 404; expired token → 404</t>
+  </si>
+  <si>
+    <t>Automated (e2e): every cron endpoint without a secret → 401 (8 endpoints)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): a user session is not a cron credential → 401 (receptionist=401, clinic admin=401, super admin=401)</t>
+  </si>
+  <si>
+    <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
+  </si>
+  <si>
+    <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
+  </si>
+  <si>
+    <t>export contains own patient=true, contains other clinic's patient=false | Automated (e2e): patients CSV → text/csv + footer + header; patients CSV is clinic-scoped (has A patient, not B)</t>
+  </si>
+  <si>
+    <t>own patient page=/clinic/patients/b4080348-1c3f-400e-9060-a066f6cab133; other clinic's patient page=/clinic/patients/50a36617-af68-4ac2-a98c-3993db6972b1; name leaked=false | Automated (e2e): another clinic's patient cannot be opened by id (status=200)</t>
   </si>
   <si>
     <t>doctor nav = Dashboard|Appointments|Patients|Voice scribe|Revenue shares|Reports|Discount approvals|Doctor schedule|No-shows|Recalls|Settings|Trash|QDQA Doctor|QD|QDqarunt0yh clinic|Patients1Registered</t>
@@ -6348,64 +6525,22 @@
     <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic</t>
   </si>
   <si>
-    <t>clinic admin bounced from the company panel: /admin-&gt;/clinic, /admin/team-&gt;/clinic, /admin/overview-&gt;/clinic</t>
-  </si>
-  <si>
-    <t>receptionist -&gt; /clinic/scribe = /clinic (scribe unreachable)</t>
-  </si>
-  <si>
-    <t>manager opens the page, sees the no-permission card, and no Start recording button is rendered</t>
-  </si>
-  <si>
-    <t>anonymous API: patients=401 basic, finance=401 basic</t>
+    <t>clinic admin bounced from the company panel: /admin-&gt;/clinic, /admin/team-&gt;/clinic, /admin/overview-&gt;/clinic | Automated (e2e): clinic admin reaches no /admin URL and sees no cross-clinic data (5 URLs); …and neither does a doctor</t>
+  </si>
+  <si>
+    <t>Automated (e2e): super admin at /clinic is returned to the admin panel (status=307 → /admin/overview)</t>
   </si>
   <si>
     <t>doctor API: finance=403 basic, staff=403 basic, body=Forbidden</t>
   </si>
   <si>
-    <t>own patient page=/clinic/patients/b4080348-1c3f-400e-9060-a066f6cab133; other clinic's patient page=/clinic/patients/50a36617-af68-4ac2-a98c-3993db6972b1; name leaked=false</t>
-  </si>
-  <si>
-    <t>export contains own patient=true, contains other clinic's patient=false</t>
-  </si>
-  <si>
-    <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
-  </si>
-  <si>
-    <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
-  </si>
-  <si>
-    <t>with fee Rs 5,000, without Rs 2,000 — difference Rs 3,000 equals the consultation fee exactly</t>
-  </si>
-  <si>
-    <t>amount 500 -&gt; Rs 4,500; percent 20 of subtotal 5000 -&gt; discount Rs 1,000, net Rs 4,000; percent 150 clamped to 100 giving net Rs 0; negative rejected: "Discount can't be negative."</t>
-  </si>
-  <si>
-    <t>across 48 fee/line/discount combinations, gross minus discount equals net every time and net never goes below zero or above gross</t>
-  </si>
-  <si>
-    <t>line 1000 less 200 = Rs 800, then 10% of the SUBTOTAL = Rs 80, net Rs 720 (Rs 720 proves the line discount applies first; Rs 700 would mean the order is wrong)</t>
-  </si>
-  <si>
-    <t>partial Rs 1,000 then Rs 2,000 recorded as 2 rows totalling Rs 3,000 against a Rs 3,000 bill</t>
-  </si>
-  <si>
-    <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
-  </si>
-  <si>
-    <t>zero -&gt; "Enter an amount greater than zero.", negative -&gt; refused, NaN -&gt; refused; none created a payment row</t>
-  </si>
-  <si>
-    <t>paid Rs 2,500 against a Rs 2,000 bill — patient credit is now Rs 500, so the excess is retained rather than discarded</t>
-  </si>
-  <si>
-    <t>payment voided; the row is SOFT-deleted (recoverable from Trash) rather than erased, so the audit trail survives</t>
-  </si>
-  <si>
-    <t>refund of Rs 5,000 against Rs 2,000 collected refused ("Can't refund more than collected (Rs 2000)."); a Rs 500 refund succeeded</t>
-  </si>
-  <si>
-    <t>three invoices issued -&gt; numbers 1, 2, 3 (unique: true, sequential: true)</t>
+    <t>anonymous API: patients=401 basic, finance=401 basic | Automated (e2e): unauthenticated API callers get 401 "Not signed in." (/api/patients/export=401+msg, /api/appointments/export=401+msg, /api/finance/export=401+msg)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): support can still open a suspended clinic (status=200)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): SUSPENDED clinic bounces its staff out of the workspace (status=307); …and no patient data renders on the way out (status=307); reactivating restores the workspace with its data (status=200)</t>
   </si>
   <si>
     <t>a month four months ago is still priced at Rs 5,000 after a rise to Rs 8,000 — history is NOT re-priced (the clinic whose price never moved reads Rs 5,000 for the same month)</t>
@@ -6420,118 +6555,28 @@
     <t>Rs 15,000 covers 3 months at a flat Rs 5,000 and 3 on the re-priced clinic — the early months are charged at what they actually cost, not at today's figure</t>
   </si>
   <si>
-    <t>before any collection the visit has NO receipt number; after Rs 1,000 was collected it has one (RCP-2026-0000001) — the receipt is proof of payment, so it cannot predate one</t>
-  </si>
-  <si>
-    <t>receipt number 2 allocated on the first payment and UNCHANGED after a second (2); both payments (2) are listed against the one receipt — a visit has one receipt, not one per payment</t>
-  </si>
-  <si>
-    <t>a paid visit had NO invoice until one was requested, then got INV-2026-0000001. The receipt number appears automatically on payment; the invoice number only when someone asks — which is why "where is the invoice number" is usually "nobody pressed the button"</t>
-  </si>
-  <si>
-    <t>the same visit carries receipt #4 and invoice #2 from two SEPARATE counters — a bill is what is owed, a receipt is proof of payment, and they must never share a sequence</t>
-  </si>
-  <si>
-    <t>a Rs 1,000 discount on a Rs 3,000 visit is HELD: status "pending", 1 approval row(s), and the bill still reads Rs 3,000 — the full amount. This is the workflow working, not a calculation error</t>
-  </si>
-  <si>
-    <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
-  </si>
-  <si>
-    <t>a REJECTED discount leaves the bill at Rs 3,000 — the patient is charged in full, which is the only safe reading of a refusal</t>
-  </si>
-  <si>
-    <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
+    <t>Automated (e2e): receptionist GET /clinic/whatsapp → 200 + inbound msg; manager and clinic admin reach the same screen (manager=200 admin=200); doctor holds no WhatsApp permission — no messages, item hidden (status=200 workspace=true)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook with no token and with a wrong token → 401 "Unauthorized." (none=401 wrong=401); …and neither attempt stored anything (rows=0)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook inbound (valid token) → 200 + logged &amp; patient-matched; an UNKNOWN number is stored but left unattributed (status=200 stored=true patient=null)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook replay is idempotent → still one row (rows=1); a redelivered 'book …' books the patient exactly once (first=200 replay=200 appointments on 2026-10-17=1)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook reschedule reply moves the appointment (rescheduled=true hour=14)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook 'book …' creates a new appointment (booked=true); …marked source=whatsapp, so staff can tell it apart (source=2); …and stays 'scheduled' rather than arriving confirmed (status=1)</t>
   </si>
   <si>
     <t>SCOPE</t>
   </si>
   <si>
-    <t>47 of 263 cases were executed automatically against the running application on 2026-10-05 and carry an observed result. The remaining 216 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
-  </si>
-  <si>
-    <t>What the automated run did</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): all four clinic roles sign in and land in the workspace</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): unknown username is refused without revealing it does not exist</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a wrong password gives the identical message</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): empty fields are blocked before any request</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a suspended account is refused after the password is checked</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): signing out ends the session and protected pages stay unreachable</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): anonymous visits to protected pages redirect to login</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a deep link is not restored after signing in</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor sees clinical items and no money or staff items</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist sees the money screens but not the scribe</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager sees neither staff nor expenses</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor cannot reach staff management by URL</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist is bounced from every restricted screen</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager cannot reach staff, expenses or profit and loss</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a clinic admin cannot enter the company panel</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist cannot reach the voice scribe</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager opens the scribe page but is offered no recorder</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): create a patient with every field completed</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): create a patient with only the two mandatory fields</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a patient cannot be saved without a name</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a patient cannot be saved without a phone number</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): search finds a patient by name and filters the rest out</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a search with no matches shows an empty state rather than an error</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): another clinic's patient cannot be opened by id</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor can read patients but is offered no create control</t>
-  </si>
-  <si>
-    <t>SOURCE</t>
-  </si>
-  <si>
-    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-05 20:47. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
+    <t>69 of 263 cases carry an observed automated result as of 2026-10-06 — 62 of them written by this run (results.json (47) + e2e-results.json (19)), the rest by the Playwright UI suite. The remaining 194 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
   </si>
 </sst>
 </file>
@@ -7783,7 +7828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>154</v>
       </c>
@@ -7806,7 +7851,7 @@
         <v>158</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8069,7 +8114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>217</v>
       </c>
@@ -8092,7 +8137,7 @@
         <v>221</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8433,7 +8478,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>298</v>
       </c>
@@ -8456,7 +8501,7 @@
         <v>302</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9551,7 +9596,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>530</v>
       </c>
@@ -9574,10 +9619,10 @@
         <v>535</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>536</v>
       </c>
@@ -9600,7 +9645,7 @@
         <v>541</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11683,7 +11728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>976</v>
       </c>
@@ -11706,7 +11751,7 @@
         <v>980</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -11917,7 +11962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="188" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>1027</v>
       </c>
@@ -11940,7 +11985,7 @@
         <v>1032</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -13087,7 +13132,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="233" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>1289</v>
       </c>
@@ -13110,7 +13155,7 @@
         <v>1294</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13191,7 +13236,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="237" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>1313</v>
       </c>
@@ -13214,10 +13259,10 @@
         <v>1318</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>1319</v>
       </c>
@@ -13240,10 +13285,10 @@
         <v>1324</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>1325</v>
       </c>
@@ -13266,7 +13311,7 @@
         <v>1330</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="240" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13347,7 +13392,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="243" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>1349</v>
       </c>
@@ -13370,7 +13415,7 @@
         <v>1354</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13399,7 +13444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="245" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>1360</v>
       </c>
@@ -13422,7 +13467,7 @@
         <v>1364</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13529,7 +13574,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="250" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>1389</v>
       </c>
@@ -13552,7 +13597,7 @@
         <v>1394</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -13893,7 +13938,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="264" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>1471</v>
       </c>
@@ -13916,7 +13961,7 @@
         <v>1476</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -17105,7 +17150,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17121,540 +17166,705 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>8</v>
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>558</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
+      <c r="C2" s="18" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>563</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>21</v>
+      <c r="C3" s="18" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>490</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>26</v>
+      <c r="C4" s="18" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>496</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>31</v>
+      <c r="C5" s="18" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>502</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>42</v>
+      <c r="C6" s="18" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>508</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>159</v>
+      <c r="C7" s="18" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>530</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>165</v>
+      <c r="C8" s="18" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>536</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>138</v>
+      <c r="C9" s="18" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>542</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>176</v>
+      <c r="C10" s="18" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>547</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>183</v>
+      <c r="C11" s="18" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>189</v>
+      <c r="C12" s="18" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>195</v>
+      <c r="C13" s="18" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>201</v>
+      <c r="C14" s="18" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>206</v>
+      <c r="C15" s="18" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>211</v>
+      <c r="C16" s="18" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>558</v>
+      <c r="C17" s="18" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>563</v>
+      <c r="C18" s="18" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>229</v>
+      <c r="C19" s="18" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>159</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>222</v>
+      <c r="C20" s="18" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>398</v>
+      <c r="C21" s="18" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>784</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>387</v>
+      <c r="C22" s="18" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>790</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>1224</v>
+      <c r="C23" s="18" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>795</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>490</v>
+      <c r="C24" s="18" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>801</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>496</v>
+      <c r="C25" s="18" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>818</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>502</v>
+      <c r="C26" s="18" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>824</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>919</v>
+      <c r="C27" s="18" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>836</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>925</v>
+      <c r="C28" s="18" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>842</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>790</v>
+      <c r="C29" s="18" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>847</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>784</v>
+      <c r="C30" s="18" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>853</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>795</v>
+      <c r="C31" s="18" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>919</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>801</v>
+      <c r="C32" s="18" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>925</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>818</v>
+      <c r="C33" s="18" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>930</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>824</v>
+      <c r="C34" s="18" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>976</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>853</v>
+      <c r="C35" s="18" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>1389</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>1072</v>
+      <c r="C36" s="18" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>1471</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>1130</v>
+      <c r="C37" s="18" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>1259</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>1136</v>
+      <c r="C38" s="18" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>1224</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>1141</v>
+      <c r="C39" s="18" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>387</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>842</v>
+      <c r="C40" s="18" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>398</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>836</v>
+      <c r="C41" s="18" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>176</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>847</v>
+      <c r="C42" s="18" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>930</v>
+      <c r="C43" s="18" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>508</v>
+      <c r="C44" s="18" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
-        <v>1259</v>
+      <c r="C45" s="18" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>201</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>542</v>
+      <c r="C46" s="18" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>206</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
-        <v>547</v>
+      <c r="C47" s="18" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>211</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>1741</v>
+      <c r="C48" s="18" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="19" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>1784</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -17676,297 +17886,297 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="C2" s="13" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="C3" s="13" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="C4" s="13" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="C5" s="13" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="C6" s="13" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="C7" s="13" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="C8" s="13" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="C9" s="13" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>176</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="C10" s="13" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>183</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="C11" s="13" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>189</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="C12" s="13" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>195</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="C13" s="13" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="C14" s="13" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>206</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="C15" s="13" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>211</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="C16" s="13" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>558</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="C17" s="13" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>563</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="C18" s="13" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>303</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="C19" s="13" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>309</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="C20" s="13" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>313</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="C21" s="13" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>319</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="C22" s="13" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>348</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="C23" s="13" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>354</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="C24" s="13" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>398</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="C25" s="13" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>375</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>1768</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>1769</v>
+      <c r="C26" s="13" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>1719</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -9,8 +9,8 @@
     <sheet sheetId="3" name="Role Coverage" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Feature Coverage" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Read Me First" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId9"/>
-    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId10"/>
+    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -6300,6 +6300,201 @@
     <t>Result</t>
   </si>
   <si>
+    <t>What was observed</t>
+  </si>
+  <si>
+    <t>receptionist -&gt; /clinic/scribe = /clinic (scribe unreachable)</t>
+  </si>
+  <si>
+    <t>manager opens the page, sees the no-permission card, and no Start recording button is rendered</t>
+  </si>
+  <si>
+    <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
+  </si>
+  <si>
+    <t>with fee Rs 5,000, without Rs 2,000 — difference Rs 3,000 equals the consultation fee exactly</t>
+  </si>
+  <si>
+    <t>amount 500 -&gt; Rs 4,500; percent 20 of subtotal 5000 -&gt; discount Rs 1,000, net Rs 4,000; percent 150 clamped to 100 giving net Rs 0; negative rejected: "Discount can't be negative."</t>
+  </si>
+  <si>
+    <t>a Rs 1,000 discount on a Rs 3,000 visit is HELD: status "pending", 1 approval row(s), and the bill still reads Rs 3,000 — the full amount. This is the workflow working, not a calculation error</t>
+  </si>
+  <si>
+    <t>Automated (e2e): appointments CSV → text/csv + footer + header; appointments CSV is clinic-scoped (A's patient, not B's) (11 lines for from=2026-09-06&amp;to=2026-11-05); the date filter reaches the export (empty range → no rows) (status=200)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): another clinic's appointment cannot be opened by id (status=200 title=FlexicaAI)</t>
+  </si>
+  <si>
+    <t>a REJECTED discount leaves the bill at Rs 3,000 — the patient is charged in full, which is the only safe reading of a refusal</t>
+  </si>
+  <si>
+    <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
+  </si>
+  <si>
+    <t>all four clinic roles land on /clinic (admin-&gt;/clinic, manager-&gt;/clinic, doctor-&gt;/clinic, receptionist-&gt;/clinic)</t>
+  </si>
+  <si>
+    <t>unknown username stays on /login, error="Incorrect username or password."</t>
+  </si>
+  <si>
+    <t>wrong password gives the SAME message as unknown user: "Incorrect username or password."</t>
+  </si>
+  <si>
+    <t>empty fields blocked by required validation, still on /login</t>
+  </si>
+  <si>
+    <t>suspended account refused AFTER password check: "Your account has been suspended. Please contact your administrator."</t>
+  </si>
+  <si>
+    <t>correct password still refused while locked: "Too many attempts. Please try again in 15 minutes."</t>
+  </si>
+  <si>
+    <t>sign out left /clinic -&gt; /login; protected page after sign-out -&gt; /login</t>
+  </si>
+  <si>
+    <t>Automated (e2e): suspended user's session is rejected → redirect</t>
+  </si>
+  <si>
+    <t>anonymous hits redirect to /login (/login, /login, /login)</t>
+  </si>
+  <si>
+    <t>deep link is NOT restored — landed on /clinic rather than /clinic/payments (documented behaviour)</t>
+  </si>
+  <si>
+    <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
+  </si>
+  <si>
+    <t>partial Rs 1,000 then Rs 2,000 recorded as 2 rows totalling Rs 3,000 against a Rs 3,000 bill</t>
+  </si>
+  <si>
+    <t>zero -&gt; "Enter an amount greater than zero.", negative -&gt; refused, NaN -&gt; refused; none created a payment row</t>
+  </si>
+  <si>
+    <t>paid Rs 2,500 against a Rs 2,000 bill — patient credit is now Rs 500, so the excess is retained rather than discarded</t>
+  </si>
+  <si>
+    <t>payment voided; the row is SOFT-deleted (recoverable from Trash) rather than erased, so the audit trail survives</t>
+  </si>
+  <si>
+    <t>refund of Rs 5,000 against Rs 2,000 collected refused ("Can't refund more than collected (Rs 2000)."); a Rs 500 refund succeeded</t>
+  </si>
+  <si>
+    <t>receipt number 2 allocated on the first payment and UNCHANGED after a second (2); both payments (2) are listed against the one receipt — a visit has one receipt, not one per payment</t>
+  </si>
+  <si>
+    <t>before any collection the visit has NO receipt number; after Rs 1,000 was collected it has one (RCP-2026-0000001) — the receipt is proof of payment, so it cannot predate one</t>
+  </si>
+  <si>
+    <t>a paid visit had NO invoice until one was requested, then got INV-2026-0000001. The receipt number appears automatically on payment; the invoice number only when someone asks — which is why "where is the invoice number" is usually "nobody pressed the button"</t>
+  </si>
+  <si>
+    <t>three invoices issued -&gt; numbers 1, 2, 3 (unique: true, sequential: true)</t>
+  </si>
+  <si>
+    <t>across 48 fee/line/discount combinations, gross minus discount equals net every time and net never goes below zero or above gross</t>
+  </si>
+  <si>
+    <t>line 1000 less 200 = Rs 800, then 10% of the SUBTOTAL = Rs 80, net Rs 720 (Rs 720 proves the line discount applies first; Rs 700 would mean the order is wrong)</t>
+  </si>
+  <si>
+    <t>the same visit carries receipt #4 and invoice #2 from two SEPARATE counters — a bill is what is owed, a receipt is proof of payment, and they must never share a sequence</t>
+  </si>
+  <si>
+    <t>Automated (e2e): valid signed link → 200 PDF; tampered token → 404; expired token → 404</t>
+  </si>
+  <si>
+    <t>Automated (e2e): every cron endpoint without a secret → 401 (8 endpoints)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): a user session is not a cron credential → 401 (receptionist=401, clinic admin=401, super admin=401)</t>
+  </si>
+  <si>
+    <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
+  </si>
+  <si>
+    <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
+  </si>
+  <si>
+    <t>export contains own patient=true, contains other clinic's patient=false | Automated (e2e): patients CSV → text/csv + footer + header; patients CSV is clinic-scoped (has A patient, not B)</t>
+  </si>
+  <si>
+    <t>own patient page=/clinic/patients/b4080348-1c3f-400e-9060-a066f6cab133; other clinic's patient page=/clinic/patients/50a36617-af68-4ac2-a98c-3993db6972b1; name leaked=false | Automated (e2e): another clinic's patient cannot be opened by id (status=200)</t>
+  </si>
+  <si>
+    <t>doctor nav = Dashboard|Appointments|Patients|Voice scribe|Revenue shares|Reports|Discount approvals|Doctor schedule|No-shows|Recalls|Settings|Trash|QDQA Doctor|QD|QDqarunt0yh clinic|Patients1Registered</t>
+  </si>
+  <si>
+    <t>receptionist nav = Dashboard|Appointments|Patients|Payments|Invoices|Receivables|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QRQA Receptionist|QR|QRqarunt0yh clinic|Day book|Patients1Registered</t>
+  </si>
+  <si>
+    <t>manager nav = Dashboard|Appointments|Patients|Voice scribe|Sales|Payments|Invoices|Receivables|Discounts|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QMQA Manager|QM|QMqarunt0yh clinic|Day book|Patients1Registered</t>
+  </si>
+  <si>
+    <t>doctor -&gt; /clinic/staff = /clinic, /clinic/staff/new = /clinic</t>
+  </si>
+  <si>
+    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic, /clinic/scribe-&gt;/clinic, /clinic/logs-&gt;/clinic</t>
+  </si>
+  <si>
+    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic</t>
+  </si>
+  <si>
+    <t>clinic admin bounced from the company panel: /admin-&gt;/clinic, /admin/team-&gt;/clinic, /admin/overview-&gt;/clinic | Automated (e2e): clinic admin reaches no /admin URL and sees no cross-clinic data (5 URLs); …and neither does a doctor</t>
+  </si>
+  <si>
+    <t>Automated (e2e): super admin at /clinic is returned to the admin panel (status=307 → /admin/overview)</t>
+  </si>
+  <si>
+    <t>doctor API: finance=403 basic, staff=403 basic, body=Forbidden</t>
+  </si>
+  <si>
+    <t>anonymous API: patients=401 basic, finance=401 basic | Automated (e2e): unauthenticated API callers get 401 "Not signed in." (/api/patients/export=401+msg, /api/appointments/export=401+msg, /api/finance/export=401+msg)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): support can still open a suspended clinic (status=200)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): SUSPENDED clinic bounces its staff out of the workspace (status=307); …and no patient data renders on the way out (status=307); reactivating restores the workspace with its data (status=200)</t>
+  </si>
+  <si>
+    <t>a month four months ago is still priced at Rs 5,000 after a rise to Rs 8,000 — history is NOT re-priced (the clinic whose price never moved reads Rs 5,000 for the same month)</t>
+  </si>
+  <si>
+    <t>six months accrue to Rs 30,000 whether the unchanged price is recorded or absent (Rs 30,000) — recording a price that never moved is a no-op, which is the safety property the whole feature rests on</t>
+  </si>
+  <si>
+    <t>the re-priced clinic accrues Rs 33,000 over six months — five at Rs 5,000 plus one at Rs 8,000 (Rs 33,000 expected); the rise applies only from its own date forward</t>
+  </si>
+  <si>
+    <t>Rs 15,000 covers 3 months at a flat Rs 5,000 and 3 on the re-priced clinic — the early months are charged at what they actually cost, not at today's figure</t>
+  </si>
+  <si>
+    <t>Automated (e2e): receptionist GET /clinic/whatsapp → 200 + inbound msg; manager and clinic admin reach the same screen (manager=200 admin=200); doctor holds no WhatsApp permission — no messages, item hidden (status=200 workspace=true)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook with no token and with a wrong token → 401 "Unauthorized." (none=401 wrong=401); …and neither attempt stored anything (rows=0)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook inbound (valid token) → 200 + logged &amp; patient-matched; an UNKNOWN number is stored but left unattributed (status=200 stored=true patient=null)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook replay is idempotent → still one row (rows=1); a redelivered 'book …' books the patient exactly once (first=200 replay=200 appointments on 2026-10-17=1)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook reschedule reply moves the appointment (rescheduled=true hour=14)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): webhook 'book …' creates a new appointment (booked=true); …marked source=whatsapp, so staff can tell it apart (source=2); …and stays 'scheduled' rather than arriving confirmed (status=1)</t>
+  </si>
+  <si>
+    <t>SCOPE</t>
+  </si>
+  <si>
+    <t>69 of 263 cases carry an observed automated result as of 2026-10-06 — 62 of them written by this run (results.json (47) + e2e-results.json (19)), the rest by the Playwright UI suite. The remaining 194 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
+  </si>
+  <si>
     <t>What the automated run did</t>
   </si>
   <si>
@@ -6381,202 +6576,7 @@
     <t>SOURCE</t>
   </si>
   <si>
-    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-05 20:47. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
-  </si>
-  <si>
-    <t>What was observed</t>
-  </si>
-  <si>
-    <t>receptionist -&gt; /clinic/scribe = /clinic (scribe unreachable)</t>
-  </si>
-  <si>
-    <t>manager opens the page, sees the no-permission card, and no Start recording button is rendered</t>
-  </si>
-  <si>
-    <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
-  </si>
-  <si>
-    <t>with fee Rs 5,000, without Rs 2,000 — difference Rs 3,000 equals the consultation fee exactly</t>
-  </si>
-  <si>
-    <t>amount 500 -&gt; Rs 4,500; percent 20 of subtotal 5000 -&gt; discount Rs 1,000, net Rs 4,000; percent 150 clamped to 100 giving net Rs 0; negative rejected: "Discount can't be negative."</t>
-  </si>
-  <si>
-    <t>a Rs 1,000 discount on a Rs 3,000 visit is HELD: status "pending", 1 approval row(s), and the bill still reads Rs 3,000 — the full amount. This is the workflow working, not a calculation error</t>
-  </si>
-  <si>
-    <t>Automated (e2e): appointments CSV → text/csv + footer + header; appointments CSV is clinic-scoped (A's patient, not B's) (11 lines for from=2026-09-06&amp;to=2026-11-05); the date filter reaches the export (empty range → no rows) (status=200)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): another clinic's appointment cannot be opened by id (status=200 title=FlexicaAI)</t>
-  </si>
-  <si>
-    <t>a REJECTED discount leaves the bill at Rs 3,000 — the patient is charged in full, which is the only safe reading of a refusal</t>
-  </si>
-  <si>
-    <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
-  </si>
-  <si>
-    <t>all four clinic roles land on /clinic (admin-&gt;/clinic, manager-&gt;/clinic, doctor-&gt;/clinic, receptionist-&gt;/clinic)</t>
-  </si>
-  <si>
-    <t>unknown username stays on /login, error="Incorrect username or password."</t>
-  </si>
-  <si>
-    <t>wrong password gives the SAME message as unknown user: "Incorrect username or password."</t>
-  </si>
-  <si>
-    <t>empty fields blocked by required validation, still on /login</t>
-  </si>
-  <si>
-    <t>suspended account refused AFTER password check: "Your account has been suspended. Please contact your administrator."</t>
-  </si>
-  <si>
-    <t>correct password still refused while locked: "Too many attempts. Please try again in 15 minutes."</t>
-  </si>
-  <si>
-    <t>sign out left /clinic -&gt; /login; protected page after sign-out -&gt; /login</t>
-  </si>
-  <si>
-    <t>Automated (e2e): suspended user's session is rejected → redirect</t>
-  </si>
-  <si>
-    <t>anonymous hits redirect to /login (/login, /login, /login)</t>
-  </si>
-  <si>
-    <t>deep link is NOT restored — landed on /clinic rather than /clinic/payments (documented behaviour)</t>
-  </si>
-  <si>
-    <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
-  </si>
-  <si>
-    <t>partial Rs 1,000 then Rs 2,000 recorded as 2 rows totalling Rs 3,000 against a Rs 3,000 bill</t>
-  </si>
-  <si>
-    <t>zero -&gt; "Enter an amount greater than zero.", negative -&gt; refused, NaN -&gt; refused; none created a payment row</t>
-  </si>
-  <si>
-    <t>paid Rs 2,500 against a Rs 2,000 bill — patient credit is now Rs 500, so the excess is retained rather than discarded</t>
-  </si>
-  <si>
-    <t>payment voided; the row is SOFT-deleted (recoverable from Trash) rather than erased, so the audit trail survives</t>
-  </si>
-  <si>
-    <t>refund of Rs 5,000 against Rs 2,000 collected refused ("Can't refund more than collected (Rs 2000)."); a Rs 500 refund succeeded</t>
-  </si>
-  <si>
-    <t>receipt number 2 allocated on the first payment and UNCHANGED after a second (2); both payments (2) are listed against the one receipt — a visit has one receipt, not one per payment</t>
-  </si>
-  <si>
-    <t>before any collection the visit has NO receipt number; after Rs 1,000 was collected it has one (RCP-2026-0000001) — the receipt is proof of payment, so it cannot predate one</t>
-  </si>
-  <si>
-    <t>a paid visit had NO invoice until one was requested, then got INV-2026-0000001. The receipt number appears automatically on payment; the invoice number only when someone asks — which is why "where is the invoice number" is usually "nobody pressed the button"</t>
-  </si>
-  <si>
-    <t>three invoices issued -&gt; numbers 1, 2, 3 (unique: true, sequential: true)</t>
-  </si>
-  <si>
-    <t>across 48 fee/line/discount combinations, gross minus discount equals net every time and net never goes below zero or above gross</t>
-  </si>
-  <si>
-    <t>line 1000 less 200 = Rs 800, then 10% of the SUBTOTAL = Rs 80, net Rs 720 (Rs 720 proves the line discount applies first; Rs 700 would mean the order is wrong)</t>
-  </si>
-  <si>
-    <t>the same visit carries receipt #4 and invoice #2 from two SEPARATE counters — a bill is what is owed, a receipt is proof of payment, and they must never share a sequence</t>
-  </si>
-  <si>
-    <t>Automated (e2e): valid signed link → 200 PDF; tampered token → 404; expired token → 404</t>
-  </si>
-  <si>
-    <t>Automated (e2e): every cron endpoint without a secret → 401 (8 endpoints)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): a user session is not a cron credential → 401 (receptionist=401, clinic admin=401, super admin=401)</t>
-  </si>
-  <si>
-    <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
-  </si>
-  <si>
-    <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
-  </si>
-  <si>
-    <t>export contains own patient=true, contains other clinic's patient=false | Automated (e2e): patients CSV → text/csv + footer + header; patients CSV is clinic-scoped (has A patient, not B)</t>
-  </si>
-  <si>
-    <t>own patient page=/clinic/patients/b4080348-1c3f-400e-9060-a066f6cab133; other clinic's patient page=/clinic/patients/50a36617-af68-4ac2-a98c-3993db6972b1; name leaked=false | Automated (e2e): another clinic's patient cannot be opened by id (status=200)</t>
-  </si>
-  <si>
-    <t>doctor nav = Dashboard|Appointments|Patients|Voice scribe|Revenue shares|Reports|Discount approvals|Doctor schedule|No-shows|Recalls|Settings|Trash|QDQA Doctor|QD|QDqarunt0yh clinic|Patients1Registered</t>
-  </si>
-  <si>
-    <t>receptionist nav = Dashboard|Appointments|Patients|Payments|Invoices|Receivables|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QRQA Receptionist|QR|QRqarunt0yh clinic|Day book|Patients1Registered</t>
-  </si>
-  <si>
-    <t>manager nav = Dashboard|Appointments|Patients|Voice scribe|Sales|Payments|Invoices|Receivables|Discounts|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QMQA Manager|QM|QMqarunt0yh clinic|Day book|Patients1Registered</t>
-  </si>
-  <si>
-    <t>doctor -&gt; /clinic/staff = /clinic, /clinic/staff/new = /clinic</t>
-  </si>
-  <si>
-    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic, /clinic/scribe-&gt;/clinic, /clinic/logs-&gt;/clinic</t>
-  </si>
-  <si>
-    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic</t>
-  </si>
-  <si>
-    <t>clinic admin bounced from the company panel: /admin-&gt;/clinic, /admin/team-&gt;/clinic, /admin/overview-&gt;/clinic | Automated (e2e): clinic admin reaches no /admin URL and sees no cross-clinic data (5 URLs); …and neither does a doctor</t>
-  </si>
-  <si>
-    <t>Automated (e2e): super admin at /clinic is returned to the admin panel (status=307 → /admin/overview)</t>
-  </si>
-  <si>
-    <t>doctor API: finance=403 basic, staff=403 basic, body=Forbidden</t>
-  </si>
-  <si>
-    <t>anonymous API: patients=401 basic, finance=401 basic | Automated (e2e): unauthenticated API callers get 401 "Not signed in." (/api/patients/export=401+msg, /api/appointments/export=401+msg, /api/finance/export=401+msg)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): support can still open a suspended clinic (status=200)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): SUSPENDED clinic bounces its staff out of the workspace (status=307); …and no patient data renders on the way out (status=307); reactivating restores the workspace with its data (status=200)</t>
-  </si>
-  <si>
-    <t>a month four months ago is still priced at Rs 5,000 after a rise to Rs 8,000 — history is NOT re-priced (the clinic whose price never moved reads Rs 5,000 for the same month)</t>
-  </si>
-  <si>
-    <t>six months accrue to Rs 30,000 whether the unchanged price is recorded or absent (Rs 30,000) — recording a price that never moved is a no-op, which is the safety property the whole feature rests on</t>
-  </si>
-  <si>
-    <t>the re-priced clinic accrues Rs 33,000 over six months — five at Rs 5,000 plus one at Rs 8,000 (Rs 33,000 expected); the rise applies only from its own date forward</t>
-  </si>
-  <si>
-    <t>Rs 15,000 covers 3 months at a flat Rs 5,000 and 3 on the re-priced clinic — the early months are charged at what they actually cost, not at today's figure</t>
-  </si>
-  <si>
-    <t>Automated (e2e): receptionist GET /clinic/whatsapp → 200 + inbound msg; manager and clinic admin reach the same screen (manager=200 admin=200); doctor holds no WhatsApp permission — no messages, item hidden (status=200 workspace=true)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): webhook with no token and with a wrong token → 401 "Unauthorized." (none=401 wrong=401); …and neither attempt stored anything (rows=0)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): webhook inbound (valid token) → 200 + logged &amp; patient-matched; an UNKNOWN number is stored but left unattributed (status=200 stored=true patient=null)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): webhook replay is idempotent → still one row (rows=1); a redelivered 'book …' books the patient exactly once (first=200 replay=200 appointments on 2026-10-17=1)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): webhook reschedule reply moves the appointment (rescheduled=true hour=14)</t>
-  </si>
-  <si>
-    <t>Automated (e2e): webhook 'book …' creates a new appointment (booked=true); …marked source=whatsapp, so staff can tell it apart (source=2); …and stays 'scheduled' rather than arriving confirmed (status=1)</t>
-  </si>
-  <si>
-    <t>SCOPE</t>
-  </si>
-  <si>
-    <t>69 of 263 cases carry an observed automated result as of 2026-10-06 — 62 of them written by this run (results.json (47) + e2e-results.json (19)), the rest by the Playwright UI suite. The remaining 194 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
+    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-06 18:31. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
   </si>
 </sst>
 </file>
@@ -17166,705 +17166,705 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>558</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="C2" s="13" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>563</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="C3" s="13" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>490</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="C4" s="13" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>496</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="C5" s="13" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>502</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="C6" s="13" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>508</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="C7" s="13" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>530</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="C8" s="13" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>536</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="C9" s="13" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>542</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="C10" s="13" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>547</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="C11" s="13" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="C12" s="13" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="C13" s="13" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="C14" s="13" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="C15" s="13" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="C16" s="13" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="C17" s="13" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="C18" s="13" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>154</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="C19" s="13" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="C20" s="13" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="C21" s="13" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>784</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="C22" s="13" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>790</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="C23" s="13" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>795</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="C24" s="13" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>801</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="C25" s="13" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>818</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="C26" s="13" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>824</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="C27" s="13" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>836</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="C28" s="13" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>842</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="C29" s="13" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>847</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="C30" s="13" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>853</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="C31" s="13" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>919</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="C32" s="13" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>925</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="18" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="C33" s="13" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>930</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="18" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="C34" s="13" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>976</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+      <c r="C35" s="13" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>1389</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="18" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
+      <c r="C36" s="13" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>1471</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="C37" s="13" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>1259</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="C38" s="13" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>1224</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="18" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
+      <c r="C39" s="13" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>387</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="18" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
+      <c r="C40" s="13" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>398</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
+      <c r="C41" s="13" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>176</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="18" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="C42" s="13" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>183</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="C43" s="13" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>189</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="18" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+      <c r="C44" s="13" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>195</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="18" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
+      <c r="C45" s="13" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>201</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="18" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
+      <c r="C46" s="13" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>206</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="18" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
+      <c r="C47" s="13" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>211</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="18" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
+      <c r="C48" s="13" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
         <v>217</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
+      <c r="C49" s="13" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
         <v>222</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="18" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
+      <c r="C50" s="13" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
         <v>229</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="18" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
+      <c r="C51" s="13" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
         <v>298</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="18" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
+      <c r="C52" s="13" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>1027</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="18" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
+      <c r="C53" s="13" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
         <v>1072</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="18" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
+      <c r="C54" s="13" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>1130</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="18" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
+      <c r="C55" s="13" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>1136</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="18" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
+      <c r="C56" s="13" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>1141</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="18" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
+      <c r="C57" s="13" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
         <v>1289</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="18" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="s">
+      <c r="C58" s="13" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>1313</v>
       </c>
       <c r="B59" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="18" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="s">
+      <c r="C59" s="13" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
         <v>1319</v>
       </c>
       <c r="B60" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="18" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
+      <c r="C60" s="13" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
         <v>1325</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="18" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
+      <c r="C61" s="13" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
         <v>1349</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="18" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
+      <c r="C62" s="13" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>1360</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="18" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="19" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>1784</v>
+      <c r="C63" s="13" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>1756</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -17886,297 +17886,297 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="C2" s="18" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="C3" s="18" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="C4" s="18" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="C5" s="18" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="C6" s="18" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>138</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="C7" s="18" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>159</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="C8" s="18" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>165</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="C9" s="18" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>176</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="C10" s="18" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>183</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="C11" s="18" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>189</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="C12" s="18" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>195</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="C13" s="18" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="C14" s="18" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>206</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="C15" s="18" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>211</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="C16" s="18" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>558</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="C17" s="18" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
         <v>563</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="C18" s="18" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>303</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="C19" s="18" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
         <v>309</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="C20" s="18" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>313</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="C21" s="18" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
         <v>319</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="C22" s="18" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
         <v>348</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="C23" s="18" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
         <v>354</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="C24" s="18" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
         <v>398</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="C25" s="18" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
         <v>375</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>1718</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>1719</v>
+      <c r="C26" s="18" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>1784</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
+++ b/docs/qa/Clinic_Management_Complete_QA_Test_Cases.xlsx
@@ -9,15 +9,15 @@
     <sheet sheetId="3" name="Role Coverage" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Feature Coverage" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Read Me First" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId10"/>
+    <sheet sheetId="7" name="Playwright Run" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="Automated Run" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="1785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1769">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -6300,15 +6300,96 @@
     <t>Result</t>
   </si>
   <si>
+    <t>What the automated run did</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): all four clinic roles sign in and land in the workspace</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): unknown username is refused without revealing it does not exist</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a wrong password gives the identical message</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): empty fields are blocked before any request</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a suspended account is refused after the password is checked</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): five failed attempts lock the username, even for the right password</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): signing out ends the session and protected pages stay unreachable</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): anonymous visits to protected pages redirect to login</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a deep link is not restored after signing in</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor sees clinical items and no money or staff items</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist sees the money screens but not the scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager sees neither staff nor expenses</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor cannot reach staff management by URL</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist is bounced from every restricted screen</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager cannot reach staff, expenses or profit and loss</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a clinic admin cannot enter the company panel</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): receptionist cannot reach the voice scribe</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): manager opens the scribe page but is offered no recorder</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with every field completed</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): create a patient with only the two mandatory fields</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a name</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a patient cannot be saved without a phone number</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): search finds a patient by name and filters the rest out</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): a search with no matches shows an empty state rather than an error</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): another clinic's patient cannot be opened by id</t>
+  </si>
+  <si>
+    <t>Automated (Playwright): doctor can read patients but is offered no create control</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-06 18:52. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
+  </si>
+  <si>
     <t>What was observed</t>
   </si>
   <si>
-    <t>receptionist -&gt; /clinic/scribe = /clinic (scribe unreachable)</t>
-  </si>
-  <si>
-    <t>manager opens the page, sees the no-permission card, and no Start recording button is rendered</t>
-  </si>
-  <si>
     <t>fee 3000 + (2000x2) + (1500x1) -&gt; procedures Rs 5,500, net Rs 8,500 (expected Rs 5,500 / Rs 8,500)</t>
   </si>
   <si>
@@ -6333,36 +6414,9 @@
     <t>with approval switched off the discount applies immediately: status "none", no approval rows created, bill Rs 2,000 — behaviour is unchanged for a clinic that never turned the workflow on</t>
   </si>
   <si>
-    <t>all four clinic roles land on /clinic (admin-&gt;/clinic, manager-&gt;/clinic, doctor-&gt;/clinic, receptionist-&gt;/clinic)</t>
-  </si>
-  <si>
-    <t>unknown username stays on /login, error="Incorrect username or password."</t>
-  </si>
-  <si>
-    <t>wrong password gives the SAME message as unknown user: "Incorrect username or password."</t>
-  </si>
-  <si>
-    <t>empty fields blocked by required validation, still on /login</t>
-  </si>
-  <si>
-    <t>suspended account refused AFTER password check: "Your account has been suspended. Please contact your administrator."</t>
-  </si>
-  <si>
-    <t>correct password still refused while locked: "Too many attempts. Please try again in 15 minutes."</t>
-  </si>
-  <si>
-    <t>sign out left /clinic -&gt; /login; protected page after sign-out -&gt; /login</t>
-  </si>
-  <si>
     <t>Automated (e2e): suspended user's session is rejected → redirect</t>
   </si>
   <si>
-    <t>anonymous hits redirect to /login (/login, /login, /login)</t>
-  </si>
-  <si>
-    <t>deep link is NOT restored — landed on /clinic rather than /clinic/payments (documented behaviour)</t>
-  </si>
-  <si>
     <t>the visit reaches fully paid once collections equal the bill (Rs 3,000 of Rs 3,000)</t>
   </si>
   <si>
@@ -6414,43 +6468,25 @@
     <t>bill before approval Rs 3,000, after approval Rs 2,000 — the discount applies the moment it is approved, and only then</t>
   </si>
   <si>
-    <t>unknown /clinic path returns HTTP 200 (200 is the documented, deliberate behaviour)</t>
-  </si>
-  <si>
-    <t>export contains own patient=true, contains other clinic's patient=false | Automated (e2e): patients CSV → text/csv + footer + header; patients CSV is clinic-scoped (has A patient, not B)</t>
-  </si>
-  <si>
-    <t>own patient page=/clinic/patients/b4080348-1c3f-400e-9060-a066f6cab133; other clinic's patient page=/clinic/patients/50a36617-af68-4ac2-a98c-3993db6972b1; name leaked=false | Automated (e2e): another clinic's patient cannot be opened by id (status=200)</t>
-  </si>
-  <si>
-    <t>doctor nav = Dashboard|Appointments|Patients|Voice scribe|Revenue shares|Reports|Discount approvals|Doctor schedule|No-shows|Recalls|Settings|Trash|QDQA Doctor|QD|QDqarunt0yh clinic|Patients1Registered</t>
-  </si>
-  <si>
-    <t>receptionist nav = Dashboard|Appointments|Patients|Payments|Invoices|Receivables|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QRQA Receptionist|QR|QRqarunt0yh clinic|Day book|Patients1Registered</t>
-  </si>
-  <si>
-    <t>manager nav = Dashboard|Appointments|Patients|Voice scribe|Sales|Payments|Invoices|Receivables|Discounts|Petty cash|Reports|History|Procedures|Doctor schedule|No-shows|WhatsApp|Recalls|Settings|Trash|QMQA Manager|QM|QMqarunt0yh clinic|Day book|Patients1Registered</t>
-  </si>
-  <si>
-    <t>doctor -&gt; /clinic/staff = /clinic, /clinic/staff/new = /clinic</t>
-  </si>
-  <si>
-    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic, /clinic/scribe-&gt;/clinic, /clinic/logs-&gt;/clinic</t>
-  </si>
-  <si>
-    <t>/clinic/staff-&gt;/clinic, /clinic/expenses-&gt;/clinic, /clinic/pl-&gt;/clinic</t>
-  </si>
-  <si>
-    <t>clinic admin bounced from the company panel: /admin-&gt;/clinic, /admin/team-&gt;/clinic, /admin/overview-&gt;/clinic | Automated (e2e): clinic admin reaches no /admin URL and sees no cross-clinic data (5 URLs); …and neither does a doctor</t>
+    <t>Automated (e2e): an unknown clinic URL shows a not-found page with a way back (status=200 notFound=true link=true); an unknown admin URL shows a not-found page with a way back (status=200 notFound=true link=true)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): patients CSV → text/csv + footer + header; patients CSV is clinic-scoped (has A patient, not B)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): another clinic's patient cannot be opened by id (status=200)</t>
+  </si>
+  <si>
+    <t>Automated (e2e): clinic admin reaches no /admin URL and sees no cross-clinic data (5 URLs); …and neither does a doctor</t>
   </si>
   <si>
     <t>Automated (e2e): super admin at /clinic is returned to the admin panel (status=307 → /admin/overview)</t>
   </si>
   <si>
-    <t>doctor API: finance=403 basic, staff=403 basic, body=Forbidden</t>
-  </si>
-  <si>
-    <t>anonymous API: patients=401 basic, finance=401 basic | Automated (e2e): unauthenticated API callers get 401 "Not signed in." (/api/patients/export=401+msg, /api/appointments/export=401+msg, /api/finance/export=401+msg)</t>
+    <t>Automated (e2e): a signed-in caller without the grant is refused 403 with no data (/api/finance/export=403 "Forbidden", /api/staff/export=403 "{"error":"Not permit")</t>
+  </si>
+  <si>
+    <t>Automated (e2e): unauthenticated API callers get 401 "Not signed in." (/api/patients/export=401+msg, /api/appointments/export=401+msg, /api/finance/export=401+msg)</t>
   </si>
   <si>
     <t>Automated (e2e): support can still open a suspended clinic (status=200)</t>
@@ -6492,91 +6528,7 @@
     <t>SCOPE</t>
   </si>
   <si>
-    <t>69 of 263 cases carry an observed automated result as of 2026-10-06 — 62 of them written by this run (results.json (47) + e2e-results.json (19)), the rest by the Playwright UI suite. The remaining 194 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
-  </si>
-  <si>
-    <t>What the automated run did</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): all four clinic roles sign in and land in the workspace</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): unknown username is refused without revealing it does not exist</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a wrong password gives the identical message</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): empty fields are blocked before any request</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a suspended account is refused after the password is checked</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): signing out ends the session and protected pages stay unreachable</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): anonymous visits to protected pages redirect to login</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a deep link is not restored after signing in</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor sees clinical items and no money or staff items</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist sees the money screens but not the scribe</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager sees neither staff nor expenses</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor cannot reach staff management by URL</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist is bounced from every restricted screen</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager cannot reach staff, expenses or profit and loss</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a clinic admin cannot enter the company panel</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): receptionist cannot reach the voice scribe</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): manager opens the scribe page but is offered no recorder</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): create a patient with every field completed</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): create a patient with only the two mandatory fields</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a patient cannot be saved without a name</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a patient cannot be saved without a phone number</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): search finds a patient by name and filters the rest out</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): a search with no matches shows an empty state rather than an error</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): another clinic's patient cannot be opened by id</t>
-  </si>
-  <si>
-    <t>Automated (Playwright): doctor can read patients but is offered no create control</t>
-  </si>
-  <si>
-    <t>SOURCE</t>
-  </si>
-  <si>
-    <t>Produced by the Playwright suite in D:\flexicaai-qa on 2026-10-06 18:31. Full evidence — traces, screenshots and video for any failure — is in reports/html; open it with "npm run report". Rows with no result are NOT failures: they need a human, and are deliberately left blank.</t>
+    <t>69 of 263 cases carry an observed automated result as of 2026-10-06 — 45 of them written by this run (results.json (24) + e2e-results.json (21)), the rest by the Playwright UI suite. The remaining 194 are left BLANK deliberately: they need a human to judge the outcome, test data this run did not create, or a credential this environment does not have. A result nobody observed would be worse than an empty cell.</t>
   </si>
 </sst>
 </file>
@@ -17150,7 +17102,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17166,711 +17118,524 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>558</v>
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>490</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>563</v>
+      <c r="C2" s="18" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>496</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>490</v>
+      <c r="C3" s="18" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>502</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>496</v>
+      <c r="C4" s="18" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>508</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>502</v>
+      <c r="C5" s="18" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>530</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>508</v>
+      <c r="C6" s="18" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>536</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>530</v>
+      <c r="C7" s="18" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>542</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>536</v>
+      <c r="C8" s="18" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>547</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>542</v>
+      <c r="C9" s="18" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>547</v>
+      <c r="C10" s="18" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>784</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>8</v>
+      <c r="C11" s="18" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>790</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>16</v>
+      <c r="C12" s="18" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>795</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>21</v>
+      <c r="C13" s="18" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>801</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>26</v>
+      <c r="C14" s="18" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>818</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>31</v>
+      <c r="C15" s="18" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>824</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>42</v>
+      <c r="C16" s="18" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>836</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>138</v>
+      <c r="C17" s="18" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>842</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>154</v>
+      <c r="C18" s="18" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>847</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>159</v>
+      <c r="C19" s="18" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>853</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>165</v>
+      <c r="C20" s="18" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>919</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>784</v>
+      <c r="C21" s="18" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>925</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>790</v>
+      <c r="C22" s="18" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>930</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>795</v>
+      <c r="C23" s="18" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>976</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>801</v>
+      <c r="C24" s="18" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>1389</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>818</v>
+      <c r="C25" s="18" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>1471</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>824</v>
+      <c r="C26" s="18" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>1259</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>836</v>
+      <c r="C27" s="18" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>1224</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>842</v>
+      <c r="C28" s="18" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>387</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>847</v>
+      <c r="C29" s="18" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>398</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>853</v>
+      <c r="C30" s="18" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>211</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>919</v>
+      <c r="C31" s="18" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>217</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>925</v>
+      <c r="C32" s="18" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>222</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>930</v>
+      <c r="C33" s="18" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>229</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>976</v>
+      <c r="C34" s="18" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>298</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>1389</v>
+      <c r="C35" s="18" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>1027</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>1471</v>
+      <c r="C36" s="18" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>1072</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>1259</v>
+      <c r="C37" s="18" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>1130</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>1224</v>
+      <c r="C38" s="18" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>1136</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>387</v>
+      <c r="C39" s="18" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>1141</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>398</v>
+      <c r="C40" s="18" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>1289</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>176</v>
+      <c r="C41" s="18" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>1313</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>183</v>
+      <c r="C42" s="18" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>1319</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>189</v>
+      <c r="C43" s="18" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>1325</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>195</v>
+      <c r="C44" s="18" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>1349</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
-        <v>201</v>
+      <c r="C45" s="18" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>1360</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>1349</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
-        <v>1360</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
-        <v>1755</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>1756</v>
+      <c r="C46" s="18" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>1768</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -17886,297 +17651,308 @@
         <v>1691</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="C2" s="13" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="C3" s="13" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="C4" s="13" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="C5" s="13" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>138</v>
+      <c r="C6" s="13" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>159</v>
+      <c r="C7" s="13" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>165</v>
+      <c r="C8" s="13" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>159</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>176</v>
+      <c r="C9" s="13" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>183</v>
+      <c r="C10" s="13" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>189</v>
+      <c r="C11" s="13" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>195</v>
+      <c r="C12" s="13" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>201</v>
+      <c r="C13" s="13" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>195</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>206</v>
+      <c r="C14" s="13" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>201</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>211</v>
+      <c r="C15" s="13" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>206</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>558</v>
+      <c r="C16" s="13" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>563</v>
+      <c r="C17" s="13" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>558</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>303</v>
+      <c r="C18" s="13" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>563</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>309</v>
+      <c r="C19" s="13" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>313</v>
+      <c r="C20" s="13" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>309</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>319</v>
+      <c r="C21" s="13" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>313</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>348</v>
+      <c r="C22" s="13" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>319</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>354</v>
+      <c r="C23" s="13" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>348</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>398</v>
+      <c r="C24" s="13" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>354</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>375</v>
+      <c r="C25" s="13" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>398</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>1784</v>
+      <c r="C26" s="13" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1720</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>